--- a/public/watheq-template.xlsx
+++ b/public/watheq-template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t xml:space="preserve">اسم المستأجر</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">الدفعات المسدّدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العقار (اختياري)</t>
   </si>
   <si>
     <t xml:space="preserve">ملاحظة (لا تُستورد)</t>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t xml:space="preserve">• الدفعات المسدّدة: للعقود القائمة فقط — كم دفعة سُدّدت منذ بداية العقد حتى اليوم. عقد شهري من يناير مدفوع حتى أغسطس → 8. بدونها يظهر العقد كأنه لم يُسدَّد منه شيء.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• العقار (اختياري): اسم العقار كما هو في وثيق بالضبط — فيذهب الصف إليه، وترفع كل عقاراتك من ملف واحد. الفارغ يذهب للعقار المختار عند الرفع.</t>
   </si>
   <si>
     <t xml:space="preserve">• الجوال ورقم الهوية: خانات نصية عمدًا حتى لا يحذف إكسل الصفر الأول. الأرقام العربية (٠٥…) مقبولة.</t>
@@ -299,7 +305,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -337,10 +343,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -612,7 +614,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J300"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -621,7 +623,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -655,99 +658,105 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>2500</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
+      <c r="J2" s="6"/>
+      <c r="K2" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>18000</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
+      <c r="J3" s="6"/>
+      <c r="K3" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>60000</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>16</v>
+      <c r="J4" s="6"/>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -759,8 +768,9 @@
       <c r="F5" s="7"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
@@ -771,8 +781,9 @@
       <c r="F6" s="7"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
@@ -783,8 +794,9 @@
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
@@ -795,8 +807,9 @@
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
@@ -807,8 +820,9 @@
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
@@ -819,8 +833,9 @@
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
@@ -831,8 +846,9 @@
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
@@ -843,8 +859,9 @@
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
@@ -855,8 +872,9 @@
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
@@ -867,8 +885,9 @@
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
@@ -879,8 +898,9 @@
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
@@ -891,8 +911,9 @@
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
@@ -903,8 +924,9 @@
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
@@ -915,8 +937,9 @@
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
@@ -927,8 +950,9 @@
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
@@ -939,8 +963,9 @@
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
@@ -951,8 +976,9 @@
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
@@ -963,8 +989,9 @@
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
@@ -975,8 +1002,9 @@
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
@@ -987,8 +1015,9 @@
       <c r="F24" s="7"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
@@ -999,8 +1028,9 @@
       <c r="F25" s="7"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
@@ -1011,8 +1041,9 @@
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
@@ -1023,8 +1054,9 @@
       <c r="F27" s="7"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
@@ -1035,8 +1067,9 @@
       <c r="F28" s="7"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
@@ -1047,8 +1080,9 @@
       <c r="F29" s="7"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
@@ -1059,8 +1093,9 @@
       <c r="F30" s="7"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
@@ -1071,8 +1106,9 @@
       <c r="F31" s="7"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
@@ -1083,8 +1119,9 @@
       <c r="F32" s="7"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
@@ -1095,8 +1132,9 @@
       <c r="F33" s="7"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
@@ -1107,8 +1145,9 @@
       <c r="F34" s="7"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
@@ -1119,8 +1158,9 @@
       <c r="F35" s="7"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
@@ -1131,8 +1171,9 @@
       <c r="F36" s="7"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
@@ -1143,8 +1184,9 @@
       <c r="F37" s="7"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
@@ -1155,8 +1197,9 @@
       <c r="F38" s="7"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
@@ -1167,8 +1210,9 @@
       <c r="F39" s="7"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
@@ -1179,8 +1223,9 @@
       <c r="F40" s="7"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
@@ -1191,8 +1236,9 @@
       <c r="F41" s="7"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
@@ -1203,8 +1249,9 @@
       <c r="F42" s="7"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
@@ -1215,8 +1262,9 @@
       <c r="F43" s="7"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
@@ -1227,8 +1275,9 @@
       <c r="F44" s="7"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
@@ -1239,8 +1288,9 @@
       <c r="F45" s="7"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
@@ -1251,8 +1301,9 @@
       <c r="F46" s="7"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="7"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
@@ -1263,8 +1314,9 @@
       <c r="F47" s="7"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
@@ -1275,8 +1327,9 @@
       <c r="F48" s="7"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
@@ -1287,8 +1340,9 @@
       <c r="F49" s="7"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
@@ -1299,8 +1353,9 @@
       <c r="F50" s="7"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
@@ -1311,8 +1366,9 @@
       <c r="F51" s="7"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
@@ -1323,8 +1379,9 @@
       <c r="F52" s="7"/>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
@@ -1335,8 +1392,9 @@
       <c r="F53" s="7"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
@@ -1347,8 +1405,9 @@
       <c r="F54" s="7"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
@@ -1359,8 +1418,9 @@
       <c r="F55" s="7"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
@@ -1371,8 +1431,9 @@
       <c r="F56" s="7"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
@@ -1383,8 +1444,9 @@
       <c r="F57" s="7"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
@@ -1395,8 +1457,9 @@
       <c r="F58" s="7"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
@@ -1407,8 +1470,9 @@
       <c r="F59" s="7"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
@@ -1419,8 +1483,9 @@
       <c r="F60" s="7"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
@@ -1431,8 +1496,9 @@
       <c r="F61" s="7"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
@@ -1443,8 +1509,9 @@
       <c r="F62" s="7"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
@@ -1455,8 +1522,9 @@
       <c r="F63" s="7"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
@@ -1467,8 +1535,9 @@
       <c r="F64" s="7"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
@@ -1479,8 +1548,9 @@
       <c r="F65" s="7"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="7"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
@@ -1491,8 +1561,9 @@
       <c r="F66" s="7"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
@@ -1503,8 +1574,9 @@
       <c r="F67" s="7"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="7"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
@@ -1515,8 +1587,9 @@
       <c r="F68" s="7"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
@@ -1527,8 +1600,9 @@
       <c r="F69" s="7"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
@@ -1539,8 +1613,9 @@
       <c r="F70" s="7"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
@@ -1551,8 +1626,9 @@
       <c r="F71" s="7"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
@@ -1563,8 +1639,9 @@
       <c r="F72" s="7"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="7"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
@@ -1575,8 +1652,9 @@
       <c r="F73" s="7"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
@@ -1587,8 +1665,9 @@
       <c r="F74" s="7"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
@@ -1599,8 +1678,9 @@
       <c r="F75" s="7"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
@@ -1611,8 +1691,9 @@
       <c r="F76" s="7"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
@@ -1623,8 +1704,9 @@
       <c r="F77" s="7"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
@@ -1635,8 +1717,9 @@
       <c r="F78" s="7"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="7"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
@@ -1647,8 +1730,9 @@
       <c r="F79" s="7"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
@@ -1659,8 +1743,9 @@
       <c r="F80" s="7"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
@@ -1671,8 +1756,9 @@
       <c r="F81" s="7"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="7"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
@@ -1683,8 +1769,9 @@
       <c r="F82" s="7"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="7"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
@@ -1695,8 +1782,9 @@
       <c r="F83" s="7"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="7"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
@@ -1707,8 +1795,9 @@
       <c r="F84" s="7"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="7"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
@@ -1719,8 +1808,9 @@
       <c r="F85" s="7"/>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="7"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
@@ -1731,8 +1821,9 @@
       <c r="F86" s="7"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>
@@ -1743,8 +1834,9 @@
       <c r="F87" s="7"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="7"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7"/>
@@ -1755,8 +1847,9 @@
       <c r="F88" s="7"/>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="7"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="7"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7"/>
@@ -1767,8 +1860,9 @@
       <c r="F89" s="7"/>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="7"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7"/>
@@ -1779,8 +1873,9 @@
       <c r="F90" s="7"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="7"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="7"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7"/>
@@ -1791,8 +1886,9 @@
       <c r="F91" s="7"/>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="7"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7"/>
@@ -1803,8 +1899,9 @@
       <c r="F92" s="7"/>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="7"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
@@ -1815,8 +1912,9 @@
       <c r="F93" s="7"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="7"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
@@ -1827,8 +1925,9 @@
       <c r="F94" s="7"/>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="7"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
@@ -1839,8 +1938,9 @@
       <c r="F95" s="7"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="7"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
@@ -1851,8 +1951,9 @@
       <c r="F96" s="7"/>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="7"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
@@ -1863,8 +1964,9 @@
       <c r="F97" s="7"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="7"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
@@ -1875,8 +1977,9 @@
       <c r="F98" s="7"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="7"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
@@ -1887,8 +1990,9 @@
       <c r="F99" s="7"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="7"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
@@ -1899,8 +2003,9 @@
       <c r="F100" s="7"/>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="7"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7"/>
@@ -1911,8 +2016,9 @@
       <c r="F101" s="7"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="7"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7"/>
@@ -1923,8 +2029,9 @@
       <c r="F102" s="7"/>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
-      <c r="I102" s="10"/>
-      <c r="J102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7"/>
@@ -1935,8 +2042,9 @@
       <c r="F103" s="7"/>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="7"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7"/>
@@ -1947,8 +2055,9 @@
       <c r="F104" s="7"/>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="7"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7"/>
@@ -1959,8 +2068,9 @@
       <c r="F105" s="7"/>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="7"/>
@@ -1971,8 +2081,9 @@
       <c r="F106" s="7"/>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="7"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="7"/>
@@ -1983,8 +2094,9 @@
       <c r="F107" s="7"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="7"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="7"/>
@@ -1995,8 +2107,9 @@
       <c r="F108" s="7"/>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="7"/>
+      <c r="I108" s="7"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7"/>
@@ -2007,8 +2120,9 @@
       <c r="F109" s="7"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
@@ -2019,8 +2133,9 @@
       <c r="F110" s="7"/>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="7"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
@@ -2031,8 +2146,9 @@
       <c r="F111" s="7"/>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="7"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
@@ -2043,8 +2159,9 @@
       <c r="F112" s="7"/>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="7"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
@@ -2055,8 +2172,9 @@
       <c r="F113" s="7"/>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="7"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
@@ -2067,8 +2185,9 @@
       <c r="F114" s="7"/>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="7"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
@@ -2079,8 +2198,9 @@
       <c r="F115" s="7"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
-      <c r="I115" s="10"/>
-      <c r="J115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="7"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
@@ -2091,8 +2211,9 @@
       <c r="F116" s="7"/>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
-      <c r="I116" s="10"/>
-      <c r="J116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="7"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
@@ -2103,8 +2224,9 @@
       <c r="F117" s="7"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
-      <c r="I117" s="10"/>
-      <c r="J117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="7"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="7"/>
@@ -2115,8 +2237,9 @@
       <c r="F118" s="7"/>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
-      <c r="I118" s="10"/>
-      <c r="J118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="8"/>
+      <c r="K118" s="7"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="7"/>
@@ -2127,8 +2250,9 @@
       <c r="F119" s="7"/>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="7"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="7"/>
@@ -2139,8 +2263,9 @@
       <c r="F120" s="7"/>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
-      <c r="I120" s="10"/>
-      <c r="J120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="7"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="7"/>
@@ -2151,8 +2276,9 @@
       <c r="F121" s="7"/>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
-      <c r="I121" s="10"/>
-      <c r="J121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="7"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="7"/>
@@ -2163,8 +2289,9 @@
       <c r="F122" s="7"/>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
-      <c r="I122" s="10"/>
-      <c r="J122" s="7"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="7"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="7"/>
@@ -2175,8 +2302,9 @@
       <c r="F123" s="7"/>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
-      <c r="I123" s="10"/>
-      <c r="J123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="7"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="7"/>
@@ -2187,8 +2315,9 @@
       <c r="F124" s="7"/>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="7"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="7"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="7"/>
@@ -2199,8 +2328,9 @@
       <c r="F125" s="7"/>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
-      <c r="I125" s="10"/>
-      <c r="J125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="7"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="7"/>
@@ -2211,8 +2341,9 @@
       <c r="F126" s="7"/>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="7"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="7"/>
@@ -2223,8 +2354,9 @@
       <c r="F127" s="7"/>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
-      <c r="I127" s="10"/>
-      <c r="J127" s="7"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="7"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="7"/>
@@ -2235,8 +2367,9 @@
       <c r="F128" s="7"/>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
-      <c r="I128" s="10"/>
-      <c r="J128" s="7"/>
+      <c r="I128" s="7"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="7"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="7"/>
@@ -2247,8 +2380,9 @@
       <c r="F129" s="7"/>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
-      <c r="I129" s="10"/>
-      <c r="J129" s="7"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="7"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="7"/>
@@ -2259,8 +2393,9 @@
       <c r="F130" s="7"/>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
-      <c r="I130" s="10"/>
-      <c r="J130" s="7"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="7"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="7"/>
@@ -2271,8 +2406,9 @@
       <c r="F131" s="7"/>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
-      <c r="I131" s="10"/>
-      <c r="J131" s="7"/>
+      <c r="I131" s="7"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="7"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="7"/>
@@ -2283,8 +2419,9 @@
       <c r="F132" s="7"/>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
-      <c r="I132" s="10"/>
-      <c r="J132" s="7"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="7"/>
@@ -2295,8 +2432,9 @@
       <c r="F133" s="7"/>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="7"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="7"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="7"/>
@@ -2307,8 +2445,9 @@
       <c r="F134" s="7"/>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="7"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="7"/>
@@ -2319,8 +2458,9 @@
       <c r="F135" s="7"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
-      <c r="I135" s="10"/>
-      <c r="J135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="7"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="7"/>
@@ -2331,8 +2471,9 @@
       <c r="F136" s="7"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="7"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="7"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="7"/>
@@ -2343,8 +2484,9 @@
       <c r="F137" s="7"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
-      <c r="I137" s="10"/>
-      <c r="J137" s="7"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="7"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="7"/>
@@ -2355,8 +2497,9 @@
       <c r="F138" s="7"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="7"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="7"/>
@@ -2367,8 +2510,9 @@
       <c r="F139" s="7"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
-      <c r="I139" s="10"/>
-      <c r="J139" s="7"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="7"/>
@@ -2379,8 +2523,9 @@
       <c r="F140" s="7"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="7"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="7"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="7"/>
@@ -2391,8 +2536,9 @@
       <c r="F141" s="7"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
-      <c r="I141" s="10"/>
-      <c r="J141" s="7"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="7"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="7"/>
@@ -2403,8 +2549,9 @@
       <c r="F142" s="7"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
-      <c r="I142" s="10"/>
-      <c r="J142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="7"/>
@@ -2415,8 +2562,9 @@
       <c r="F143" s="7"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
-      <c r="I143" s="10"/>
-      <c r="J143" s="7"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="7"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="7"/>
@@ -2427,8 +2575,9 @@
       <c r="F144" s="7"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
-      <c r="I144" s="10"/>
-      <c r="J144" s="7"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="7"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="7"/>
@@ -2439,8 +2588,9 @@
       <c r="F145" s="7"/>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
-      <c r="I145" s="10"/>
-      <c r="J145" s="7"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="8"/>
+      <c r="K145" s="7"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="7"/>
@@ -2451,8 +2601,9 @@
       <c r="F146" s="7"/>
       <c r="G146" s="8"/>
       <c r="H146" s="8"/>
-      <c r="I146" s="10"/>
-      <c r="J146" s="7"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="8"/>
+      <c r="K146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="7"/>
@@ -2463,8 +2614,9 @@
       <c r="F147" s="7"/>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
-      <c r="I147" s="10"/>
-      <c r="J147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="8"/>
+      <c r="K147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="7"/>
@@ -2475,8 +2627,9 @@
       <c r="F148" s="7"/>
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
-      <c r="I148" s="10"/>
-      <c r="J148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="8"/>
+      <c r="K148" s="7"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="7"/>
@@ -2487,8 +2640,9 @@
       <c r="F149" s="7"/>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
-      <c r="I149" s="10"/>
-      <c r="J149" s="7"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="8"/>
+      <c r="K149" s="7"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="7"/>
@@ -2499,8 +2653,9 @@
       <c r="F150" s="7"/>
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
-      <c r="I150" s="10"/>
-      <c r="J150" s="7"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="8"/>
+      <c r="K150" s="7"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="7"/>
@@ -2511,8 +2666,9 @@
       <c r="F151" s="7"/>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="8"/>
+      <c r="K151" s="7"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="7"/>
@@ -2523,8 +2679,9 @@
       <c r="F152" s="7"/>
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
-      <c r="I152" s="10"/>
-      <c r="J152" s="7"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="8"/>
+      <c r="K152" s="7"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="7"/>
@@ -2535,8 +2692,9 @@
       <c r="F153" s="7"/>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
-      <c r="I153" s="10"/>
-      <c r="J153" s="7"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="8"/>
+      <c r="K153" s="7"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="7"/>
@@ -2547,8 +2705,9 @@
       <c r="F154" s="7"/>
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
-      <c r="I154" s="10"/>
-      <c r="J154" s="7"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="8"/>
+      <c r="K154" s="7"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="7"/>
@@ -2559,8 +2718,9 @@
       <c r="F155" s="7"/>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="7"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="8"/>
+      <c r="K155" s="7"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="7"/>
@@ -2571,8 +2731,9 @@
       <c r="F156" s="7"/>
       <c r="G156" s="8"/>
       <c r="H156" s="8"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="8"/>
+      <c r="K156" s="7"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="7"/>
@@ -2583,8 +2744,9 @@
       <c r="F157" s="7"/>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="8"/>
+      <c r="K157" s="7"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="7"/>
@@ -2595,8 +2757,9 @@
       <c r="F158" s="7"/>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
-      <c r="I158" s="10"/>
-      <c r="J158" s="7"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="8"/>
+      <c r="K158" s="7"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="7"/>
@@ -2607,8 +2770,9 @@
       <c r="F159" s="7"/>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="7"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="8"/>
+      <c r="K159" s="7"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="7"/>
@@ -2619,8 +2783,9 @@
       <c r="F160" s="7"/>
       <c r="G160" s="8"/>
       <c r="H160" s="8"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="7"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="8"/>
+      <c r="K160" s="7"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="7"/>
@@ -2631,8 +2796,9 @@
       <c r="F161" s="7"/>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
-      <c r="I161" s="10"/>
-      <c r="J161" s="7"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="8"/>
+      <c r="K161" s="7"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="7"/>
@@ -2643,8 +2809,9 @@
       <c r="F162" s="7"/>
       <c r="G162" s="8"/>
       <c r="H162" s="8"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="7"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="8"/>
+      <c r="K162" s="7"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="7"/>
@@ -2655,8 +2822,9 @@
       <c r="F163" s="7"/>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="7"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="8"/>
+      <c r="K163" s="7"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="7"/>
@@ -2667,8 +2835,9 @@
       <c r="F164" s="7"/>
       <c r="G164" s="8"/>
       <c r="H164" s="8"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="7"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="8"/>
+      <c r="K164" s="7"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="7"/>
@@ -2679,8 +2848,9 @@
       <c r="F165" s="7"/>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="7"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="8"/>
+      <c r="K165" s="7"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="7"/>
@@ -2691,8 +2861,9 @@
       <c r="F166" s="7"/>
       <c r="G166" s="8"/>
       <c r="H166" s="8"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="7"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="8"/>
+      <c r="K166" s="7"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="7"/>
@@ -2703,8 +2874,9 @@
       <c r="F167" s="7"/>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="7"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="8"/>
+      <c r="K167" s="7"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="7"/>
@@ -2715,8 +2887,9 @@
       <c r="F168" s="7"/>
       <c r="G168" s="8"/>
       <c r="H168" s="8"/>
-      <c r="I168" s="10"/>
-      <c r="J168" s="7"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="8"/>
+      <c r="K168" s="7"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="7"/>
@@ -2727,8 +2900,9 @@
       <c r="F169" s="7"/>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="7"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="8"/>
+      <c r="K169" s="7"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="7"/>
@@ -2739,8 +2913,9 @@
       <c r="F170" s="7"/>
       <c r="G170" s="8"/>
       <c r="H170" s="8"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="7"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="8"/>
+      <c r="K170" s="7"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="7"/>
@@ -2751,8 +2926,9 @@
       <c r="F171" s="7"/>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="7"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="8"/>
+      <c r="K171" s="7"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="7"/>
@@ -2763,8 +2939,9 @@
       <c r="F172" s="7"/>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
-      <c r="I172" s="10"/>
-      <c r="J172" s="7"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="8"/>
+      <c r="K172" s="7"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="7"/>
@@ -2775,8 +2952,9 @@
       <c r="F173" s="7"/>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="7"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="8"/>
+      <c r="K173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="7"/>
@@ -2787,8 +2965,9 @@
       <c r="F174" s="7"/>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
-      <c r="I174" s="10"/>
-      <c r="J174" s="7"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="8"/>
+      <c r="K174" s="7"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="7"/>
@@ -2799,8 +2978,9 @@
       <c r="F175" s="7"/>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
-      <c r="I175" s="10"/>
-      <c r="J175" s="7"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="8"/>
+      <c r="K175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="7"/>
@@ -2811,8 +2991,9 @@
       <c r="F176" s="7"/>
       <c r="G176" s="8"/>
       <c r="H176" s="8"/>
-      <c r="I176" s="10"/>
-      <c r="J176" s="7"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="8"/>
+      <c r="K176" s="7"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="7"/>
@@ -2823,8 +3004,9 @@
       <c r="F177" s="7"/>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
-      <c r="I177" s="10"/>
-      <c r="J177" s="7"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="8"/>
+      <c r="K177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="7"/>
@@ -2835,8 +3017,9 @@
       <c r="F178" s="7"/>
       <c r="G178" s="8"/>
       <c r="H178" s="8"/>
-      <c r="I178" s="10"/>
-      <c r="J178" s="7"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="7"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="7"/>
@@ -2847,8 +3030,9 @@
       <c r="F179" s="7"/>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
-      <c r="I179" s="10"/>
-      <c r="J179" s="7"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="8"/>
+      <c r="K179" s="7"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="7"/>
@@ -2859,8 +3043,9 @@
       <c r="F180" s="7"/>
       <c r="G180" s="8"/>
       <c r="H180" s="8"/>
-      <c r="I180" s="10"/>
-      <c r="J180" s="7"/>
+      <c r="I180" s="7"/>
+      <c r="J180" s="8"/>
+      <c r="K180" s="7"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="7"/>
@@ -2871,8 +3056,9 @@
       <c r="F181" s="7"/>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
-      <c r="I181" s="10"/>
-      <c r="J181" s="7"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="8"/>
+      <c r="K181" s="7"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="7"/>
@@ -2883,8 +3069,9 @@
       <c r="F182" s="7"/>
       <c r="G182" s="8"/>
       <c r="H182" s="8"/>
-      <c r="I182" s="10"/>
-      <c r="J182" s="7"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="8"/>
+      <c r="K182" s="7"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="7"/>
@@ -2895,8 +3082,9 @@
       <c r="F183" s="7"/>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
-      <c r="I183" s="10"/>
-      <c r="J183" s="7"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="8"/>
+      <c r="K183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="7"/>
@@ -2907,8 +3095,9 @@
       <c r="F184" s="7"/>
       <c r="G184" s="8"/>
       <c r="H184" s="8"/>
-      <c r="I184" s="10"/>
-      <c r="J184" s="7"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="8"/>
+      <c r="K184" s="7"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="7"/>
@@ -2919,8 +3108,9 @@
       <c r="F185" s="7"/>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
-      <c r="I185" s="10"/>
-      <c r="J185" s="7"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="8"/>
+      <c r="K185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="7"/>
@@ -2931,8 +3121,9 @@
       <c r="F186" s="7"/>
       <c r="G186" s="8"/>
       <c r="H186" s="8"/>
-      <c r="I186" s="10"/>
-      <c r="J186" s="7"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="8"/>
+      <c r="K186" s="7"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="7"/>
@@ -2943,8 +3134,9 @@
       <c r="F187" s="7"/>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
-      <c r="I187" s="10"/>
-      <c r="J187" s="7"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="8"/>
+      <c r="K187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="7"/>
@@ -2955,8 +3147,9 @@
       <c r="F188" s="7"/>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
-      <c r="I188" s="10"/>
-      <c r="J188" s="7"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="8"/>
+      <c r="K188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="7"/>
@@ -2967,8 +3160,9 @@
       <c r="F189" s="7"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
-      <c r="I189" s="10"/>
-      <c r="J189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="8"/>
+      <c r="K189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="7"/>
@@ -2979,8 +3173,9 @@
       <c r="F190" s="7"/>
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
-      <c r="I190" s="10"/>
-      <c r="J190" s="7"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="8"/>
+      <c r="K190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="7"/>
@@ -2991,8 +3186,9 @@
       <c r="F191" s="7"/>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
-      <c r="I191" s="10"/>
-      <c r="J191" s="7"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="7"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="7"/>
@@ -3003,8 +3199,9 @@
       <c r="F192" s="7"/>
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
-      <c r="I192" s="10"/>
-      <c r="J192" s="7"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="8"/>
+      <c r="K192" s="7"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="7"/>
@@ -3015,8 +3212,9 @@
       <c r="F193" s="7"/>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
-      <c r="I193" s="10"/>
-      <c r="J193" s="7"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="8"/>
+      <c r="K193" s="7"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="7"/>
@@ -3027,8 +3225,9 @@
       <c r="F194" s="7"/>
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
-      <c r="I194" s="10"/>
-      <c r="J194" s="7"/>
+      <c r="I194" s="7"/>
+      <c r="J194" s="8"/>
+      <c r="K194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="7"/>
@@ -3039,8 +3238,9 @@
       <c r="F195" s="7"/>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
-      <c r="I195" s="10"/>
-      <c r="J195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="8"/>
+      <c r="K195" s="7"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="7"/>
@@ -3051,8 +3251,9 @@
       <c r="F196" s="7"/>
       <c r="G196" s="8"/>
       <c r="H196" s="8"/>
-      <c r="I196" s="10"/>
-      <c r="J196" s="7"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="8"/>
+      <c r="K196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="7"/>
@@ -3063,8 +3264,9 @@
       <c r="F197" s="7"/>
       <c r="G197" s="8"/>
       <c r="H197" s="8"/>
-      <c r="I197" s="10"/>
-      <c r="J197" s="7"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="8"/>
+      <c r="K197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="7"/>
@@ -3075,8 +3277,9 @@
       <c r="F198" s="7"/>
       <c r="G198" s="8"/>
       <c r="H198" s="8"/>
-      <c r="I198" s="10"/>
-      <c r="J198" s="7"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="8"/>
+      <c r="K198" s="7"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="7"/>
@@ -3087,8 +3290,9 @@
       <c r="F199" s="7"/>
       <c r="G199" s="8"/>
       <c r="H199" s="8"/>
-      <c r="I199" s="10"/>
-      <c r="J199" s="7"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="8"/>
+      <c r="K199" s="7"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="7"/>
@@ -3099,8 +3303,9 @@
       <c r="F200" s="7"/>
       <c r="G200" s="8"/>
       <c r="H200" s="8"/>
-      <c r="I200" s="10"/>
-      <c r="J200" s="7"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="8"/>
+      <c r="K200" s="7"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="7"/>
@@ -3111,8 +3316,9 @@
       <c r="F201" s="7"/>
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
-      <c r="I201" s="10"/>
-      <c r="J201" s="7"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="8"/>
+      <c r="K201" s="7"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="7"/>
@@ -3123,8 +3329,9 @@
       <c r="F202" s="7"/>
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
-      <c r="I202" s="10"/>
-      <c r="J202" s="7"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="8"/>
+      <c r="K202" s="7"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="7"/>
@@ -3135,8 +3342,9 @@
       <c r="F203" s="7"/>
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
-      <c r="I203" s="10"/>
-      <c r="J203" s="7"/>
+      <c r="I203" s="7"/>
+      <c r="J203" s="8"/>
+      <c r="K203" s="7"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="7"/>
@@ -3147,8 +3355,9 @@
       <c r="F204" s="7"/>
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
-      <c r="I204" s="10"/>
-      <c r="J204" s="7"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="8"/>
+      <c r="K204" s="7"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="7"/>
@@ -3159,8 +3368,9 @@
       <c r="F205" s="7"/>
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
-      <c r="I205" s="10"/>
-      <c r="J205" s="7"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="8"/>
+      <c r="K205" s="7"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="7"/>
@@ -3171,8 +3381,9 @@
       <c r="F206" s="7"/>
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
-      <c r="I206" s="10"/>
-      <c r="J206" s="7"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="8"/>
+      <c r="K206" s="7"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="7"/>
@@ -3183,8 +3394,9 @@
       <c r="F207" s="7"/>
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
-      <c r="I207" s="10"/>
-      <c r="J207" s="7"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="8"/>
+      <c r="K207" s="7"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="7"/>
@@ -3195,8 +3407,9 @@
       <c r="F208" s="7"/>
       <c r="G208" s="8"/>
       <c r="H208" s="8"/>
-      <c r="I208" s="10"/>
-      <c r="J208" s="7"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="8"/>
+      <c r="K208" s="7"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="7"/>
@@ -3207,8 +3420,9 @@
       <c r="F209" s="7"/>
       <c r="G209" s="8"/>
       <c r="H209" s="8"/>
-      <c r="I209" s="10"/>
-      <c r="J209" s="7"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="8"/>
+      <c r="K209" s="7"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="7"/>
@@ -3219,8 +3433,9 @@
       <c r="F210" s="7"/>
       <c r="G210" s="8"/>
       <c r="H210" s="8"/>
-      <c r="I210" s="10"/>
-      <c r="J210" s="7"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="7"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="7"/>
@@ -3231,8 +3446,9 @@
       <c r="F211" s="7"/>
       <c r="G211" s="8"/>
       <c r="H211" s="8"/>
-      <c r="I211" s="10"/>
-      <c r="J211" s="7"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="7"/>
@@ -3243,8 +3459,9 @@
       <c r="F212" s="7"/>
       <c r="G212" s="8"/>
       <c r="H212" s="8"/>
-      <c r="I212" s="10"/>
-      <c r="J212" s="7"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="8"/>
+      <c r="K212" s="7"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="7"/>
@@ -3255,8 +3472,9 @@
       <c r="F213" s="7"/>
       <c r="G213" s="8"/>
       <c r="H213" s="8"/>
-      <c r="I213" s="10"/>
-      <c r="J213" s="7"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="8"/>
+      <c r="K213" s="7"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="7"/>
@@ -3267,8 +3485,9 @@
       <c r="F214" s="7"/>
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
-      <c r="I214" s="10"/>
-      <c r="J214" s="7"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="8"/>
+      <c r="K214" s="7"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="7"/>
@@ -3279,8 +3498,9 @@
       <c r="F215" s="7"/>
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
-      <c r="I215" s="10"/>
-      <c r="J215" s="7"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="8"/>
+      <c r="K215" s="7"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="7"/>
@@ -3291,8 +3511,9 @@
       <c r="F216" s="7"/>
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
-      <c r="I216" s="10"/>
-      <c r="J216" s="7"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="8"/>
+      <c r="K216" s="7"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="7"/>
@@ -3303,8 +3524,9 @@
       <c r="F217" s="7"/>
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
-      <c r="I217" s="10"/>
-      <c r="J217" s="7"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="8"/>
+      <c r="K217" s="7"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="7"/>
@@ -3315,8 +3537,9 @@
       <c r="F218" s="7"/>
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
-      <c r="I218" s="10"/>
-      <c r="J218" s="7"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="7"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="7"/>
@@ -3327,8 +3550,9 @@
       <c r="F219" s="7"/>
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
-      <c r="I219" s="10"/>
-      <c r="J219" s="7"/>
+      <c r="I219" s="7"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="7"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="7"/>
@@ -3339,8 +3563,9 @@
       <c r="F220" s="7"/>
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
-      <c r="I220" s="10"/>
-      <c r="J220" s="7"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="7"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="7"/>
@@ -3351,8 +3576,9 @@
       <c r="F221" s="7"/>
       <c r="G221" s="8"/>
       <c r="H221" s="8"/>
-      <c r="I221" s="10"/>
-      <c r="J221" s="7"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="7"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="7"/>
@@ -3363,8 +3589,9 @@
       <c r="F222" s="7"/>
       <c r="G222" s="8"/>
       <c r="H222" s="8"/>
-      <c r="I222" s="10"/>
-      <c r="J222" s="7"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="8"/>
+      <c r="K222" s="7"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="7"/>
@@ -3375,8 +3602,9 @@
       <c r="F223" s="7"/>
       <c r="G223" s="8"/>
       <c r="H223" s="8"/>
-      <c r="I223" s="10"/>
-      <c r="J223" s="7"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="8"/>
+      <c r="K223" s="7"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="7"/>
@@ -3387,8 +3615,9 @@
       <c r="F224" s="7"/>
       <c r="G224" s="8"/>
       <c r="H224" s="8"/>
-      <c r="I224" s="10"/>
-      <c r="J224" s="7"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="8"/>
+      <c r="K224" s="7"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="7"/>
@@ -3399,8 +3628,9 @@
       <c r="F225" s="7"/>
       <c r="G225" s="8"/>
       <c r="H225" s="8"/>
-      <c r="I225" s="10"/>
-      <c r="J225" s="7"/>
+      <c r="I225" s="7"/>
+      <c r="J225" s="8"/>
+      <c r="K225" s="7"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="7"/>
@@ -3411,8 +3641,9 @@
       <c r="F226" s="7"/>
       <c r="G226" s="8"/>
       <c r="H226" s="8"/>
-      <c r="I226" s="10"/>
-      <c r="J226" s="7"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="8"/>
+      <c r="K226" s="7"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="7"/>
@@ -3423,8 +3654,9 @@
       <c r="F227" s="7"/>
       <c r="G227" s="8"/>
       <c r="H227" s="8"/>
-      <c r="I227" s="10"/>
-      <c r="J227" s="7"/>
+      <c r="I227" s="7"/>
+      <c r="J227" s="8"/>
+      <c r="K227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="7"/>
@@ -3435,8 +3667,9 @@
       <c r="F228" s="7"/>
       <c r="G228" s="8"/>
       <c r="H228" s="8"/>
-      <c r="I228" s="10"/>
-      <c r="J228" s="7"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="8"/>
+      <c r="K228" s="7"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="7"/>
@@ -3447,8 +3680,9 @@
       <c r="F229" s="7"/>
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
-      <c r="I229" s="10"/>
-      <c r="J229" s="7"/>
+      <c r="I229" s="7"/>
+      <c r="J229" s="8"/>
+      <c r="K229" s="7"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="7"/>
@@ -3459,8 +3693,9 @@
       <c r="F230" s="7"/>
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
-      <c r="I230" s="10"/>
-      <c r="J230" s="7"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="8"/>
+      <c r="K230" s="7"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="7"/>
@@ -3471,8 +3706,9 @@
       <c r="F231" s="7"/>
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
-      <c r="I231" s="10"/>
-      <c r="J231" s="7"/>
+      <c r="I231" s="7"/>
+      <c r="J231" s="8"/>
+      <c r="K231" s="7"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="7"/>
@@ -3483,8 +3719,9 @@
       <c r="F232" s="7"/>
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
-      <c r="I232" s="10"/>
-      <c r="J232" s="7"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="8"/>
+      <c r="K232" s="7"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="7"/>
@@ -3495,8 +3732,9 @@
       <c r="F233" s="7"/>
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
-      <c r="I233" s="10"/>
-      <c r="J233" s="7"/>
+      <c r="I233" s="7"/>
+      <c r="J233" s="8"/>
+      <c r="K233" s="7"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="7"/>
@@ -3507,8 +3745,9 @@
       <c r="F234" s="7"/>
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
-      <c r="I234" s="10"/>
-      <c r="J234" s="7"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="8"/>
+      <c r="K234" s="7"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="7"/>
@@ -3519,8 +3758,9 @@
       <c r="F235" s="7"/>
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
-      <c r="I235" s="10"/>
-      <c r="J235" s="7"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="8"/>
+      <c r="K235" s="7"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="7"/>
@@ -3531,8 +3771,9 @@
       <c r="F236" s="7"/>
       <c r="G236" s="8"/>
       <c r="H236" s="8"/>
-      <c r="I236" s="10"/>
-      <c r="J236" s="7"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="8"/>
+      <c r="K236" s="7"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="7"/>
@@ -3543,8 +3784,9 @@
       <c r="F237" s="7"/>
       <c r="G237" s="8"/>
       <c r="H237" s="8"/>
-      <c r="I237" s="10"/>
-      <c r="J237" s="7"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="8"/>
+      <c r="K237" s="7"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="7"/>
@@ -3555,8 +3797,9 @@
       <c r="F238" s="7"/>
       <c r="G238" s="8"/>
       <c r="H238" s="8"/>
-      <c r="I238" s="10"/>
-      <c r="J238" s="7"/>
+      <c r="I238" s="7"/>
+      <c r="J238" s="8"/>
+      <c r="K238" s="7"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="7"/>
@@ -3567,8 +3810,9 @@
       <c r="F239" s="7"/>
       <c r="G239" s="8"/>
       <c r="H239" s="8"/>
-      <c r="I239" s="10"/>
-      <c r="J239" s="7"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="8"/>
+      <c r="K239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="7"/>
@@ -3579,8 +3823,9 @@
       <c r="F240" s="7"/>
       <c r="G240" s="8"/>
       <c r="H240" s="8"/>
-      <c r="I240" s="10"/>
-      <c r="J240" s="7"/>
+      <c r="I240" s="7"/>
+      <c r="J240" s="8"/>
+      <c r="K240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="7"/>
@@ -3591,8 +3836,9 @@
       <c r="F241" s="7"/>
       <c r="G241" s="8"/>
       <c r="H241" s="8"/>
-      <c r="I241" s="10"/>
-      <c r="J241" s="7"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="8"/>
+      <c r="K241" s="7"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="7"/>
@@ -3603,8 +3849,9 @@
       <c r="F242" s="7"/>
       <c r="G242" s="8"/>
       <c r="H242" s="8"/>
-      <c r="I242" s="10"/>
-      <c r="J242" s="7"/>
+      <c r="I242" s="7"/>
+      <c r="J242" s="8"/>
+      <c r="K242" s="7"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="7"/>
@@ -3615,8 +3862,9 @@
       <c r="F243" s="7"/>
       <c r="G243" s="8"/>
       <c r="H243" s="8"/>
-      <c r="I243" s="10"/>
-      <c r="J243" s="7"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="8"/>
+      <c r="K243" s="7"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="7"/>
@@ -3627,8 +3875,9 @@
       <c r="F244" s="7"/>
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
-      <c r="I244" s="10"/>
-      <c r="J244" s="7"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="8"/>
+      <c r="K244" s="7"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="7"/>
@@ -3639,8 +3888,9 @@
       <c r="F245" s="7"/>
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
-      <c r="I245" s="10"/>
-      <c r="J245" s="7"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="8"/>
+      <c r="K245" s="7"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="7"/>
@@ -3651,8 +3901,9 @@
       <c r="F246" s="7"/>
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
-      <c r="I246" s="10"/>
-      <c r="J246" s="7"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="8"/>
+      <c r="K246" s="7"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="7"/>
@@ -3663,8 +3914,9 @@
       <c r="F247" s="7"/>
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
-      <c r="I247" s="10"/>
-      <c r="J247" s="7"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="8"/>
+      <c r="K247" s="7"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="7"/>
@@ -3675,8 +3927,9 @@
       <c r="F248" s="7"/>
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
-      <c r="I248" s="10"/>
-      <c r="J248" s="7"/>
+      <c r="I248" s="7"/>
+      <c r="J248" s="8"/>
+      <c r="K248" s="7"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="7"/>
@@ -3687,8 +3940,9 @@
       <c r="F249" s="7"/>
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
-      <c r="I249" s="10"/>
-      <c r="J249" s="7"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="7"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="7"/>
@@ -3699,8 +3953,9 @@
       <c r="F250" s="7"/>
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
-      <c r="I250" s="10"/>
-      <c r="J250" s="7"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="7"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="7"/>
@@ -3711,8 +3966,9 @@
       <c r="F251" s="7"/>
       <c r="G251" s="8"/>
       <c r="H251" s="8"/>
-      <c r="I251" s="10"/>
-      <c r="J251" s="7"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="7"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="7"/>
@@ -3723,8 +3979,9 @@
       <c r="F252" s="7"/>
       <c r="G252" s="8"/>
       <c r="H252" s="8"/>
-      <c r="I252" s="10"/>
-      <c r="J252" s="7"/>
+      <c r="I252" s="7"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="7"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="7"/>
@@ -3735,8 +3992,9 @@
       <c r="F253" s="7"/>
       <c r="G253" s="8"/>
       <c r="H253" s="8"/>
-      <c r="I253" s="10"/>
-      <c r="J253" s="7"/>
+      <c r="I253" s="7"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="7"/>
@@ -3747,8 +4005,9 @@
       <c r="F254" s="7"/>
       <c r="G254" s="8"/>
       <c r="H254" s="8"/>
-      <c r="I254" s="10"/>
-      <c r="J254" s="7"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="7"/>
@@ -3759,8 +4018,9 @@
       <c r="F255" s="7"/>
       <c r="G255" s="8"/>
       <c r="H255" s="8"/>
-      <c r="I255" s="10"/>
-      <c r="J255" s="7"/>
+      <c r="I255" s="7"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="7"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="7"/>
@@ -3771,8 +4031,9 @@
       <c r="F256" s="7"/>
       <c r="G256" s="8"/>
       <c r="H256" s="8"/>
-      <c r="I256" s="10"/>
-      <c r="J256" s="7"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="7"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="7"/>
@@ -3783,8 +4044,9 @@
       <c r="F257" s="7"/>
       <c r="G257" s="8"/>
       <c r="H257" s="8"/>
-      <c r="I257" s="10"/>
-      <c r="J257" s="7"/>
+      <c r="I257" s="7"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="7"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="7"/>
@@ -3795,8 +4057,9 @@
       <c r="F258" s="7"/>
       <c r="G258" s="8"/>
       <c r="H258" s="8"/>
-      <c r="I258" s="10"/>
-      <c r="J258" s="7"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="7"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="7"/>
@@ -3807,8 +4070,9 @@
       <c r="F259" s="7"/>
       <c r="G259" s="8"/>
       <c r="H259" s="8"/>
-      <c r="I259" s="10"/>
-      <c r="J259" s="7"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="7"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="7"/>
@@ -3819,8 +4083,9 @@
       <c r="F260" s="7"/>
       <c r="G260" s="8"/>
       <c r="H260" s="8"/>
-      <c r="I260" s="10"/>
-      <c r="J260" s="7"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="7"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="7"/>
@@ -3831,8 +4096,9 @@
       <c r="F261" s="7"/>
       <c r="G261" s="8"/>
       <c r="H261" s="8"/>
-      <c r="I261" s="10"/>
-      <c r="J261" s="7"/>
+      <c r="I261" s="7"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="7"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="7"/>
@@ -3843,8 +4109,9 @@
       <c r="F262" s="7"/>
       <c r="G262" s="8"/>
       <c r="H262" s="8"/>
-      <c r="I262" s="10"/>
-      <c r="J262" s="7"/>
+      <c r="I262" s="7"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="7"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="7"/>
@@ -3855,8 +4122,9 @@
       <c r="F263" s="7"/>
       <c r="G263" s="8"/>
       <c r="H263" s="8"/>
-      <c r="I263" s="10"/>
-      <c r="J263" s="7"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="7"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="7"/>
@@ -3867,8 +4135,9 @@
       <c r="F264" s="7"/>
       <c r="G264" s="8"/>
       <c r="H264" s="8"/>
-      <c r="I264" s="10"/>
-      <c r="J264" s="7"/>
+      <c r="I264" s="7"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="7"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="7"/>
@@ -3879,8 +4148,9 @@
       <c r="F265" s="7"/>
       <c r="G265" s="8"/>
       <c r="H265" s="8"/>
-      <c r="I265" s="10"/>
-      <c r="J265" s="7"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="7"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="7"/>
@@ -3891,8 +4161,9 @@
       <c r="F266" s="7"/>
       <c r="G266" s="8"/>
       <c r="H266" s="8"/>
-      <c r="I266" s="10"/>
-      <c r="J266" s="7"/>
+      <c r="I266" s="7"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="7"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="7"/>
@@ -3903,8 +4174,9 @@
       <c r="F267" s="7"/>
       <c r="G267" s="8"/>
       <c r="H267" s="8"/>
-      <c r="I267" s="10"/>
-      <c r="J267" s="7"/>
+      <c r="I267" s="7"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="7"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="7"/>
@@ -3915,8 +4187,9 @@
       <c r="F268" s="7"/>
       <c r="G268" s="8"/>
       <c r="H268" s="8"/>
-      <c r="I268" s="10"/>
-      <c r="J268" s="7"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="7"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="7"/>
@@ -3927,8 +4200,9 @@
       <c r="F269" s="7"/>
       <c r="G269" s="8"/>
       <c r="H269" s="8"/>
-      <c r="I269" s="10"/>
-      <c r="J269" s="7"/>
+      <c r="I269" s="7"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="7"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="7"/>
@@ -3939,8 +4213,9 @@
       <c r="F270" s="7"/>
       <c r="G270" s="8"/>
       <c r="H270" s="8"/>
-      <c r="I270" s="10"/>
-      <c r="J270" s="7"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="7"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="7"/>
@@ -3951,8 +4226,9 @@
       <c r="F271" s="7"/>
       <c r="G271" s="8"/>
       <c r="H271" s="8"/>
-      <c r="I271" s="10"/>
-      <c r="J271" s="7"/>
+      <c r="I271" s="7"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="7"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="7"/>
@@ -3963,8 +4239,9 @@
       <c r="F272" s="7"/>
       <c r="G272" s="8"/>
       <c r="H272" s="8"/>
-      <c r="I272" s="10"/>
-      <c r="J272" s="7"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="7"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="7"/>
@@ -3975,8 +4252,9 @@
       <c r="F273" s="7"/>
       <c r="G273" s="8"/>
       <c r="H273" s="8"/>
-      <c r="I273" s="10"/>
-      <c r="J273" s="7"/>
+      <c r="I273" s="7"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="7"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="7"/>
@@ -3987,8 +4265,9 @@
       <c r="F274" s="7"/>
       <c r="G274" s="8"/>
       <c r="H274" s="8"/>
-      <c r="I274" s="10"/>
-      <c r="J274" s="7"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="7"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="7"/>
@@ -3999,8 +4278,9 @@
       <c r="F275" s="7"/>
       <c r="G275" s="8"/>
       <c r="H275" s="8"/>
-      <c r="I275" s="10"/>
-      <c r="J275" s="7"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="7"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="7"/>
@@ -4011,8 +4291,9 @@
       <c r="F276" s="7"/>
       <c r="G276" s="8"/>
       <c r="H276" s="8"/>
-      <c r="I276" s="10"/>
-      <c r="J276" s="7"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="7"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="7"/>
@@ -4023,8 +4304,9 @@
       <c r="F277" s="7"/>
       <c r="G277" s="8"/>
       <c r="H277" s="8"/>
-      <c r="I277" s="10"/>
-      <c r="J277" s="7"/>
+      <c r="I277" s="7"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="7"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="7"/>
@@ -4035,8 +4317,9 @@
       <c r="F278" s="7"/>
       <c r="G278" s="8"/>
       <c r="H278" s="8"/>
-      <c r="I278" s="10"/>
-      <c r="J278" s="7"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="7"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="7"/>
@@ -4047,8 +4330,9 @@
       <c r="F279" s="7"/>
       <c r="G279" s="8"/>
       <c r="H279" s="8"/>
-      <c r="I279" s="10"/>
-      <c r="J279" s="7"/>
+      <c r="I279" s="7"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="7"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="7"/>
@@ -4059,8 +4343,9 @@
       <c r="F280" s="7"/>
       <c r="G280" s="8"/>
       <c r="H280" s="8"/>
-      <c r="I280" s="10"/>
-      <c r="J280" s="7"/>
+      <c r="I280" s="7"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="7"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="7"/>
@@ -4071,8 +4356,9 @@
       <c r="F281" s="7"/>
       <c r="G281" s="8"/>
       <c r="H281" s="8"/>
-      <c r="I281" s="10"/>
-      <c r="J281" s="7"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="7"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="7"/>
@@ -4083,8 +4369,9 @@
       <c r="F282" s="7"/>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
-      <c r="I282" s="10"/>
-      <c r="J282" s="7"/>
+      <c r="I282" s="7"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="7"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="7"/>
@@ -4095,8 +4382,9 @@
       <c r="F283" s="7"/>
       <c r="G283" s="8"/>
       <c r="H283" s="8"/>
-      <c r="I283" s="10"/>
-      <c r="J283" s="7"/>
+      <c r="I283" s="7"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="7"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="7"/>
@@ -4107,8 +4395,9 @@
       <c r="F284" s="7"/>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
-      <c r="I284" s="10"/>
-      <c r="J284" s="7"/>
+      <c r="I284" s="7"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="7"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="7"/>
@@ -4119,8 +4408,9 @@
       <c r="F285" s="7"/>
       <c r="G285" s="8"/>
       <c r="H285" s="8"/>
-      <c r="I285" s="10"/>
-      <c r="J285" s="7"/>
+      <c r="I285" s="7"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="7"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="7"/>
@@ -4131,8 +4421,9 @@
       <c r="F286" s="7"/>
       <c r="G286" s="8"/>
       <c r="H286" s="8"/>
-      <c r="I286" s="10"/>
-      <c r="J286" s="7"/>
+      <c r="I286" s="7"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="7"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="7"/>
@@ -4143,8 +4434,9 @@
       <c r="F287" s="7"/>
       <c r="G287" s="8"/>
       <c r="H287" s="8"/>
-      <c r="I287" s="10"/>
-      <c r="J287" s="7"/>
+      <c r="I287" s="7"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="7"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="7"/>
@@ -4155,8 +4447,9 @@
       <c r="F288" s="7"/>
       <c r="G288" s="8"/>
       <c r="H288" s="8"/>
-      <c r="I288" s="10"/>
-      <c r="J288" s="7"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="7"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="7"/>
@@ -4167,8 +4460,9 @@
       <c r="F289" s="7"/>
       <c r="G289" s="8"/>
       <c r="H289" s="8"/>
-      <c r="I289" s="10"/>
-      <c r="J289" s="7"/>
+      <c r="I289" s="7"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="7"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="7"/>
@@ -4179,8 +4473,9 @@
       <c r="F290" s="7"/>
       <c r="G290" s="8"/>
       <c r="H290" s="8"/>
-      <c r="I290" s="10"/>
-      <c r="J290" s="7"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="7"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="7"/>
@@ -4191,8 +4486,9 @@
       <c r="F291" s="7"/>
       <c r="G291" s="8"/>
       <c r="H291" s="8"/>
-      <c r="I291" s="10"/>
-      <c r="J291" s="7"/>
+      <c r="I291" s="7"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="7"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="7"/>
@@ -4203,8 +4499,9 @@
       <c r="F292" s="7"/>
       <c r="G292" s="8"/>
       <c r="H292" s="8"/>
-      <c r="I292" s="10"/>
-      <c r="J292" s="7"/>
+      <c r="I292" s="7"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="7"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="7"/>
@@ -4215,8 +4512,9 @@
       <c r="F293" s="7"/>
       <c r="G293" s="8"/>
       <c r="H293" s="8"/>
-      <c r="I293" s="10"/>
-      <c r="J293" s="7"/>
+      <c r="I293" s="7"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="7"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="7"/>
@@ -4227,8 +4525,9 @@
       <c r="F294" s="7"/>
       <c r="G294" s="8"/>
       <c r="H294" s="8"/>
-      <c r="I294" s="10"/>
-      <c r="J294" s="7"/>
+      <c r="I294" s="7"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="7"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="7"/>
@@ -4239,8 +4538,9 @@
       <c r="F295" s="7"/>
       <c r="G295" s="8"/>
       <c r="H295" s="8"/>
-      <c r="I295" s="10"/>
-      <c r="J295" s="7"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="7"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="7"/>
@@ -4251,8 +4551,9 @@
       <c r="F296" s="7"/>
       <c r="G296" s="8"/>
       <c r="H296" s="8"/>
-      <c r="I296" s="10"/>
-      <c r="J296" s="7"/>
+      <c r="I296" s="7"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="7"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="7"/>
@@ -4263,8 +4564,9 @@
       <c r="F297" s="7"/>
       <c r="G297" s="8"/>
       <c r="H297" s="8"/>
-      <c r="I297" s="10"/>
-      <c r="J297" s="7"/>
+      <c r="I297" s="7"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="7"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="7"/>
@@ -4275,8 +4577,9 @@
       <c r="F298" s="7"/>
       <c r="G298" s="8"/>
       <c r="H298" s="8"/>
-      <c r="I298" s="10"/>
-      <c r="J298" s="7"/>
+      <c r="I298" s="7"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="7"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="7"/>
@@ -4287,8 +4590,9 @@
       <c r="F299" s="7"/>
       <c r="G299" s="8"/>
       <c r="H299" s="8"/>
-      <c r="I299" s="10"/>
-      <c r="J299" s="7"/>
+      <c r="I299" s="7"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="7"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="7"/>
@@ -4299,11 +4603,12 @@
       <c r="F300" s="7"/>
       <c r="G300" s="8"/>
       <c r="H300" s="8"/>
-      <c r="I300" s="10"/>
-      <c r="J300" s="7"/>
+      <c r="I300" s="7"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation allowBlank="true" error="اختر قيمة من القائمة المنسدلة" errorStyle="stop" errorTitle="دورة سداد غير معروفة" operator="between" prompt="اختر من القائمة — لا تكتب يدويًا" promptTitle="دورة السداد" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D300" type="list">
       <formula1>"شهري,سنوي,نصف سنوي,كل 3 اشهر,اسبوعي,يومي"</formula1>
       <formula2>0</formula2>
@@ -4328,6 +4633,10 @@
       <formula1>0</formula1>
       <formula2>120</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" prompt="لرفع كل المحفظة من ملف واحد: اكتب اسم العقار كما هو في لوحة وثيق بالضبط. اتركه فارغًا ليذهب الصف للعقار الذي تختاره عند الرفع" promptTitle="العقار" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="J2:J300" type="textLength">
+      <formula1>120</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4344,7 +4653,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B15"/>
+  <dimension ref="B1:B17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -4352,80 +4661,86 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="11" t="s">
-        <v>28</v>
+      <c r="B1" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="12" t="s">
-        <v>29</v>
+      <c r="B2" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
-        <v>30</v>
+      <c r="B3" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="s">
-        <v>31</v>
+      <c r="B4" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
-        <v>32</v>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="s">
-        <v>33</v>
+      <c r="B6" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>34</v>
+      <c r="B7" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
-        <v>35</v>
+      <c r="B8" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
-        <v>36</v>
+      <c r="B9" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="s">
-        <v>37</v>
+      <c r="B10" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
-        <v>38</v>
+      <c r="B11" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
-        <v>39</v>
+      <c r="B12" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/watheq-template.xlsx
+++ b/public/watheq-template.xlsx
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t xml:space="preserve">اسم المستأجر</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t xml:space="preserve">أول استحقاق (اختياري)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الضريبة (اختياري)</t>
   </si>
   <si>
     <t xml:space="preserve">ملاحظة (لا تُستورد)</t>
@@ -438,7 +441,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -471,11 +474,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -492,10 +495,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -767,7 +766,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S300"/>
+  <dimension ref="A1:T300"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -780,11 +779,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -845,31 +845,34 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>2500</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>8</v>
@@ -878,47 +881,48 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
-      <c r="N2" s="8" t="s">
-        <v>25</v>
+      <c r="N2" s="7" t="s">
+        <v>26</v>
       </c>
-      <c r="O2" s="9" t="n">
+      <c r="O2" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P2" s="9" t="n">
+      <c r="P2" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" s="9" t="n">
+      <c r="Q2" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="R2" s="8"/>
-      <c r="S2" s="3" t="s">
-        <v>26</v>
+      <c r="R2" s="7"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>18000</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>2</v>
@@ -927,36 +931,37 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="3" t="s">
-        <v>26</v>
+      <c r="N3" s="7"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>60000</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="6" t="n">
@@ -966,13 +971,14 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="3" t="s">
-        <v>26</v>
+      <c r="N4" s="7"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -989,12 +995,13 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="10"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -1010,12 +1017,13 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="10"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
@@ -1031,12 +1039,13 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="10"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -1052,12 +1061,13 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="10"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
@@ -1073,12 +1083,13 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="10"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -1094,12 +1105,13 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="10"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
@@ -1115,12 +1127,13 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="10"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -1136,12 +1149,13 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="10"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
@@ -1157,12 +1171,13 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="10"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -1178,12 +1193,13 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="10"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
@@ -1199,12 +1215,13 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="10"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -1220,12 +1237,13 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="10"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
@@ -1241,12 +1259,13 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="10"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -1262,12 +1281,13 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="10"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
@@ -1283,12 +1303,13 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="10"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
@@ -1304,12 +1325,13 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="10"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
@@ -1325,12 +1347,13 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="10"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
@@ -1346,12 +1369,13 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="10"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
@@ -1367,12 +1391,13 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="10"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
@@ -1388,12 +1413,13 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="10"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -1409,12 +1435,13 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="10"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
@@ -1430,12 +1457,13 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="10"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -1451,12 +1479,13 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="10"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
@@ -1472,12 +1501,13 @@
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="10"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -1493,12 +1523,13 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="10"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
@@ -1514,12 +1545,13 @@
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="13"/>
-      <c r="S30" s="10"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -1535,12 +1567,13 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="10"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
@@ -1556,12 +1589,13 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="10"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -1577,12 +1611,13 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="13"/>
-      <c r="S33" s="10"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
@@ -1598,12 +1633,13 @@
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="13"/>
-      <c r="S34" s="10"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -1619,12 +1655,13 @@
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="13"/>
-      <c r="S35" s="10"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
@@ -1640,12 +1677,13 @@
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="13"/>
-      <c r="S36" s="10"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -1661,12 +1699,13 @@
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="13"/>
-      <c r="S37" s="10"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
@@ -1682,12 +1721,13 @@
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="13"/>
-      <c r="S38" s="10"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
@@ -1703,12 +1743,13 @@
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="13"/>
-      <c r="S39" s="10"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
@@ -1724,12 +1765,13 @@
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="13"/>
-      <c r="S40" s="10"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
@@ -1745,12 +1787,13 @@
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="13"/>
-      <c r="S41" s="10"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
@@ -1766,12 +1809,13 @@
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="13"/>
-      <c r="S42" s="10"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
@@ -1787,12 +1831,13 @@
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="14"/>
-      <c r="R43" s="13"/>
-      <c r="S43" s="10"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -1808,12 +1853,13 @@
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="13"/>
-      <c r="S44" s="10"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
@@ -1829,12 +1875,13 @@
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="14"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="13"/>
-      <c r="S45" s="10"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -1850,12 +1897,13 @@
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="13"/>
-      <c r="S46" s="10"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
@@ -1871,12 +1919,13 @@
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="13"/>
-      <c r="S47" s="10"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -1892,12 +1941,13 @@
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="13"/>
-      <c r="S48" s="10"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
@@ -1913,12 +1963,13 @@
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="13"/>
-      <c r="S49" s="10"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -1934,12 +1985,13 @@
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
       <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="13"/>
-      <c r="S50" s="10"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
@@ -1955,12 +2007,13 @@
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
       <c r="M51" s="11"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="13"/>
-      <c r="S51" s="10"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -1976,12 +2029,13 @@
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
       <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-      <c r="R52" s="13"/>
-      <c r="S52" s="10"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
@@ -1997,12 +2051,13 @@
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
       <c r="M53" s="11"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
-      <c r="R53" s="13"/>
-      <c r="S53" s="10"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -2018,12 +2073,13 @@
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
       <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="14"/>
-      <c r="Q54" s="14"/>
-      <c r="R54" s="13"/>
-      <c r="S54" s="10"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10"/>
@@ -2039,12 +2095,13 @@
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
       <c r="M55" s="11"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="14"/>
-      <c r="R55" s="13"/>
-      <c r="S55" s="10"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -2060,12 +2117,13 @@
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
       <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="14"/>
-      <c r="P56" s="14"/>
-      <c r="Q56" s="14"/>
-      <c r="R56" s="13"/>
-      <c r="S56" s="10"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10"/>
@@ -2081,12 +2139,13 @@
       <c r="K57" s="11"/>
       <c r="L57" s="11"/>
       <c r="M57" s="11"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="14"/>
-      <c r="P57" s="14"/>
-      <c r="Q57" s="14"/>
-      <c r="R57" s="13"/>
-      <c r="S57" s="10"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="11"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10"/>
@@ -2102,12 +2161,13 @@
       <c r="K58" s="11"/>
       <c r="L58" s="11"/>
       <c r="M58" s="11"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="14"/>
-      <c r="Q58" s="14"/>
-      <c r="R58" s="13"/>
-      <c r="S58" s="10"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="11"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10"/>
@@ -2123,12 +2183,13 @@
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
       <c r="M59" s="11"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="13"/>
-      <c r="S59" s="10"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10"/>
@@ -2144,12 +2205,13 @@
       <c r="K60" s="11"/>
       <c r="L60" s="11"/>
       <c r="M60" s="11"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="13"/>
-      <c r="S60" s="10"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10"/>
@@ -2165,12 +2227,13 @@
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
       <c r="M61" s="11"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="13"/>
-      <c r="S61" s="10"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10"/>
@@ -2186,12 +2249,13 @@
       <c r="K62" s="11"/>
       <c r="L62" s="11"/>
       <c r="M62" s="11"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="13"/>
-      <c r="S62" s="10"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="11"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -2207,12 +2271,13 @@
       <c r="K63" s="11"/>
       <c r="L63" s="11"/>
       <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="13"/>
-      <c r="S63" s="10"/>
+      <c r="N63" s="11"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="11"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10"/>
@@ -2228,12 +2293,13 @@
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>
       <c r="M64" s="11"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="14"/>
-      <c r="Q64" s="14"/>
-      <c r="R64" s="13"/>
-      <c r="S64" s="10"/>
+      <c r="N64" s="11"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="11"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -2249,12 +2315,13 @@
       <c r="K65" s="11"/>
       <c r="L65" s="11"/>
       <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="14"/>
-      <c r="R65" s="13"/>
-      <c r="S65" s="10"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="11"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10"/>
@@ -2270,12 +2337,13 @@
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="13"/>
-      <c r="S66" s="10"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -2291,12 +2359,13 @@
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
       <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
-      <c r="Q67" s="14"/>
-      <c r="R67" s="13"/>
-      <c r="S67" s="10"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="10"/>
@@ -2312,12 +2381,13 @@
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
       <c r="M68" s="11"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="14"/>
-      <c r="Q68" s="14"/>
-      <c r="R68" s="13"/>
-      <c r="S68" s="10"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -2333,12 +2403,13 @@
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>
       <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="14"/>
-      <c r="P69" s="14"/>
-      <c r="Q69" s="14"/>
-      <c r="R69" s="13"/>
-      <c r="S69" s="10"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="10"/>
@@ -2354,12 +2425,13 @@
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
       <c r="M70" s="11"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="14"/>
-      <c r="Q70" s="14"/>
-      <c r="R70" s="13"/>
-      <c r="S70" s="10"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -2375,12 +2447,13 @@
       <c r="K71" s="11"/>
       <c r="L71" s="11"/>
       <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="14"/>
-      <c r="P71" s="14"/>
-      <c r="Q71" s="14"/>
-      <c r="R71" s="13"/>
-      <c r="S71" s="10"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="13"/>
+      <c r="T71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10"/>
@@ -2396,12 +2469,13 @@
       <c r="K72" s="11"/>
       <c r="L72" s="11"/>
       <c r="M72" s="11"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="14"/>
-      <c r="P72" s="14"/>
-      <c r="Q72" s="14"/>
-      <c r="R72" s="13"/>
-      <c r="S72" s="10"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -2417,12 +2491,13 @@
       <c r="K73" s="11"/>
       <c r="L73" s="11"/>
       <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="14"/>
-      <c r="P73" s="14"/>
-      <c r="Q73" s="14"/>
-      <c r="R73" s="13"/>
-      <c r="S73" s="10"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="10"/>
@@ -2438,12 +2513,13 @@
       <c r="K74" s="11"/>
       <c r="L74" s="11"/>
       <c r="M74" s="11"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="14"/>
-      <c r="Q74" s="14"/>
-      <c r="R74" s="13"/>
-      <c r="S74" s="10"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -2459,12 +2535,13 @@
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
       <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
-      <c r="O75" s="14"/>
-      <c r="P75" s="14"/>
-      <c r="Q75" s="14"/>
-      <c r="R75" s="13"/>
-      <c r="S75" s="10"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10"/>
@@ -2480,12 +2557,13 @@
       <c r="K76" s="11"/>
       <c r="L76" s="11"/>
       <c r="M76" s="11"/>
-      <c r="N76" s="13"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="14"/>
-      <c r="Q76" s="14"/>
-      <c r="R76" s="13"/>
-      <c r="S76" s="10"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10"/>
@@ -2501,12 +2579,13 @@
       <c r="K77" s="11"/>
       <c r="L77" s="11"/>
       <c r="M77" s="11"/>
-      <c r="N77" s="13"/>
-      <c r="O77" s="14"/>
-      <c r="P77" s="14"/>
-      <c r="Q77" s="14"/>
-      <c r="R77" s="13"/>
-      <c r="S77" s="10"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="10"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="11"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10"/>
@@ -2522,12 +2601,13 @@
       <c r="K78" s="11"/>
       <c r="L78" s="11"/>
       <c r="M78" s="11"/>
-      <c r="N78" s="13"/>
-      <c r="O78" s="14"/>
-      <c r="P78" s="14"/>
-      <c r="Q78" s="14"/>
-      <c r="R78" s="13"/>
-      <c r="S78" s="10"/>
+      <c r="N78" s="11"/>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="11"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10"/>
@@ -2543,12 +2623,13 @@
       <c r="K79" s="11"/>
       <c r="L79" s="11"/>
       <c r="M79" s="11"/>
-      <c r="N79" s="13"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
-      <c r="R79" s="13"/>
-      <c r="S79" s="10"/>
+      <c r="N79" s="11"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="11"/>
+      <c r="S79" s="13"/>
+      <c r="T79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="10"/>
@@ -2564,12 +2645,13 @@
       <c r="K80" s="11"/>
       <c r="L80" s="11"/>
       <c r="M80" s="11"/>
-      <c r="N80" s="13"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="14"/>
-      <c r="Q80" s="14"/>
-      <c r="R80" s="13"/>
-      <c r="S80" s="10"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="10"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="11"/>
+      <c r="S80" s="13"/>
+      <c r="T80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="10"/>
@@ -2585,12 +2667,13 @@
       <c r="K81" s="11"/>
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
-      <c r="N81" s="13"/>
-      <c r="O81" s="14"/>
-      <c r="P81" s="14"/>
-      <c r="Q81" s="14"/>
-      <c r="R81" s="13"/>
-      <c r="S81" s="10"/>
+      <c r="N81" s="11"/>
+      <c r="O81" s="10"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="11"/>
+      <c r="S81" s="13"/>
+      <c r="T81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="10"/>
@@ -2606,12 +2689,13 @@
       <c r="K82" s="11"/>
       <c r="L82" s="11"/>
       <c r="M82" s="11"/>
-      <c r="N82" s="13"/>
-      <c r="O82" s="14"/>
-      <c r="P82" s="14"/>
-      <c r="Q82" s="14"/>
-      <c r="R82" s="13"/>
-      <c r="S82" s="10"/>
+      <c r="N82" s="11"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="11"/>
+      <c r="S82" s="13"/>
+      <c r="T82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="10"/>
@@ -2627,12 +2711,13 @@
       <c r="K83" s="11"/>
       <c r="L83" s="11"/>
       <c r="M83" s="11"/>
-      <c r="N83" s="13"/>
-      <c r="O83" s="14"/>
-      <c r="P83" s="14"/>
-      <c r="Q83" s="14"/>
-      <c r="R83" s="13"/>
-      <c r="S83" s="10"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="10"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="11"/>
+      <c r="S83" s="13"/>
+      <c r="T83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10"/>
@@ -2648,12 +2733,13 @@
       <c r="K84" s="11"/>
       <c r="L84" s="11"/>
       <c r="M84" s="11"/>
-      <c r="N84" s="13"/>
-      <c r="O84" s="14"/>
-      <c r="P84" s="14"/>
-      <c r="Q84" s="14"/>
-      <c r="R84" s="13"/>
-      <c r="S84" s="10"/>
+      <c r="N84" s="11"/>
+      <c r="O84" s="10"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="11"/>
+      <c r="S84" s="13"/>
+      <c r="T84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10"/>
@@ -2669,12 +2755,13 @@
       <c r="K85" s="11"/>
       <c r="L85" s="11"/>
       <c r="M85" s="11"/>
-      <c r="N85" s="13"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14"/>
-      <c r="Q85" s="14"/>
-      <c r="R85" s="13"/>
-      <c r="S85" s="10"/>
+      <c r="N85" s="11"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="11"/>
+      <c r="S85" s="13"/>
+      <c r="T85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10"/>
@@ -2690,12 +2777,13 @@
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
       <c r="M86" s="11"/>
-      <c r="N86" s="13"/>
-      <c r="O86" s="14"/>
-      <c r="P86" s="14"/>
-      <c r="Q86" s="14"/>
-      <c r="R86" s="13"/>
-      <c r="S86" s="10"/>
+      <c r="N86" s="11"/>
+      <c r="O86" s="10"/>
+      <c r="P86" s="10"/>
+      <c r="Q86" s="10"/>
+      <c r="R86" s="11"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10"/>
@@ -2711,12 +2799,13 @@
       <c r="K87" s="11"/>
       <c r="L87" s="11"/>
       <c r="M87" s="11"/>
-      <c r="N87" s="13"/>
-      <c r="O87" s="14"/>
-      <c r="P87" s="14"/>
-      <c r="Q87" s="14"/>
-      <c r="R87" s="13"/>
-      <c r="S87" s="10"/>
+      <c r="N87" s="11"/>
+      <c r="O87" s="10"/>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="11"/>
+      <c r="S87" s="13"/>
+      <c r="T87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10"/>
@@ -2732,12 +2821,13 @@
       <c r="K88" s="11"/>
       <c r="L88" s="11"/>
       <c r="M88" s="11"/>
-      <c r="N88" s="13"/>
-      <c r="O88" s="14"/>
-      <c r="P88" s="14"/>
-      <c r="Q88" s="14"/>
-      <c r="R88" s="13"/>
-      <c r="S88" s="10"/>
+      <c r="N88" s="11"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="10"/>
+      <c r="R88" s="11"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10"/>
@@ -2753,12 +2843,13 @@
       <c r="K89" s="11"/>
       <c r="L89" s="11"/>
       <c r="M89" s="11"/>
-      <c r="N89" s="13"/>
-      <c r="O89" s="14"/>
-      <c r="P89" s="14"/>
-      <c r="Q89" s="14"/>
-      <c r="R89" s="13"/>
-      <c r="S89" s="10"/>
+      <c r="N89" s="11"/>
+      <c r="O89" s="10"/>
+      <c r="P89" s="10"/>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="11"/>
+      <c r="S89" s="13"/>
+      <c r="T89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="10"/>
@@ -2774,12 +2865,13 @@
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
       <c r="M90" s="11"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="14"/>
-      <c r="P90" s="14"/>
-      <c r="Q90" s="14"/>
-      <c r="R90" s="13"/>
-      <c r="S90" s="10"/>
+      <c r="N90" s="11"/>
+      <c r="O90" s="10"/>
+      <c r="P90" s="10"/>
+      <c r="Q90" s="10"/>
+      <c r="R90" s="11"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10"/>
@@ -2795,12 +2887,13 @@
       <c r="K91" s="11"/>
       <c r="L91" s="11"/>
       <c r="M91" s="11"/>
-      <c r="N91" s="13"/>
-      <c r="O91" s="14"/>
-      <c r="P91" s="14"/>
-      <c r="Q91" s="14"/>
-      <c r="R91" s="13"/>
-      <c r="S91" s="10"/>
+      <c r="N91" s="11"/>
+      <c r="O91" s="10"/>
+      <c r="P91" s="10"/>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="11"/>
+      <c r="S91" s="13"/>
+      <c r="T91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10"/>
@@ -2816,12 +2909,13 @@
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
       <c r="M92" s="11"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="14"/>
-      <c r="P92" s="14"/>
-      <c r="Q92" s="14"/>
-      <c r="R92" s="13"/>
-      <c r="S92" s="10"/>
+      <c r="N92" s="11"/>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="10"/>
+      <c r="R92" s="11"/>
+      <c r="S92" s="13"/>
+      <c r="T92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10"/>
@@ -2837,12 +2931,13 @@
       <c r="K93" s="11"/>
       <c r="L93" s="11"/>
       <c r="M93" s="11"/>
-      <c r="N93" s="13"/>
-      <c r="O93" s="14"/>
-      <c r="P93" s="14"/>
-      <c r="Q93" s="14"/>
-      <c r="R93" s="13"/>
-      <c r="S93" s="10"/>
+      <c r="N93" s="11"/>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="11"/>
+      <c r="S93" s="13"/>
+      <c r="T93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10"/>
@@ -2858,12 +2953,13 @@
       <c r="K94" s="11"/>
       <c r="L94" s="11"/>
       <c r="M94" s="11"/>
-      <c r="N94" s="13"/>
-      <c r="O94" s="14"/>
-      <c r="P94" s="14"/>
-      <c r="Q94" s="14"/>
-      <c r="R94" s="13"/>
-      <c r="S94" s="10"/>
+      <c r="N94" s="11"/>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="11"/>
+      <c r="S94" s="13"/>
+      <c r="T94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10"/>
@@ -2879,12 +2975,13 @@
       <c r="K95" s="11"/>
       <c r="L95" s="11"/>
       <c r="M95" s="11"/>
-      <c r="N95" s="13"/>
-      <c r="O95" s="14"/>
-      <c r="P95" s="14"/>
-      <c r="Q95" s="14"/>
-      <c r="R95" s="13"/>
-      <c r="S95" s="10"/>
+      <c r="N95" s="11"/>
+      <c r="O95" s="10"/>
+      <c r="P95" s="10"/>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="11"/>
+      <c r="S95" s="13"/>
+      <c r="T95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="10"/>
@@ -2900,12 +2997,13 @@
       <c r="K96" s="11"/>
       <c r="L96" s="11"/>
       <c r="M96" s="11"/>
-      <c r="N96" s="13"/>
-      <c r="O96" s="14"/>
-      <c r="P96" s="14"/>
-      <c r="Q96" s="14"/>
-      <c r="R96" s="13"/>
-      <c r="S96" s="10"/>
+      <c r="N96" s="11"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="11"/>
+      <c r="S96" s="13"/>
+      <c r="T96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10"/>
@@ -2921,12 +3019,13 @@
       <c r="K97" s="11"/>
       <c r="L97" s="11"/>
       <c r="M97" s="11"/>
-      <c r="N97" s="13"/>
-      <c r="O97" s="14"/>
-      <c r="P97" s="14"/>
-      <c r="Q97" s="14"/>
-      <c r="R97" s="13"/>
-      <c r="S97" s="10"/>
+      <c r="N97" s="11"/>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="11"/>
+      <c r="S97" s="13"/>
+      <c r="T97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10"/>
@@ -2942,12 +3041,13 @@
       <c r="K98" s="11"/>
       <c r="L98" s="11"/>
       <c r="M98" s="11"/>
-      <c r="N98" s="13"/>
-      <c r="O98" s="14"/>
-      <c r="P98" s="14"/>
-      <c r="Q98" s="14"/>
-      <c r="R98" s="13"/>
-      <c r="S98" s="10"/>
+      <c r="N98" s="11"/>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
+      <c r="Q98" s="10"/>
+      <c r="R98" s="11"/>
+      <c r="S98" s="13"/>
+      <c r="T98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10"/>
@@ -2963,12 +3063,13 @@
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
       <c r="M99" s="11"/>
-      <c r="N99" s="13"/>
-      <c r="O99" s="14"/>
-      <c r="P99" s="14"/>
-      <c r="Q99" s="14"/>
-      <c r="R99" s="13"/>
-      <c r="S99" s="10"/>
+      <c r="N99" s="11"/>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="11"/>
+      <c r="S99" s="13"/>
+      <c r="T99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10"/>
@@ -2984,12 +3085,13 @@
       <c r="K100" s="11"/>
       <c r="L100" s="11"/>
       <c r="M100" s="11"/>
-      <c r="N100" s="13"/>
-      <c r="O100" s="14"/>
-      <c r="P100" s="14"/>
-      <c r="Q100" s="14"/>
-      <c r="R100" s="13"/>
-      <c r="S100" s="10"/>
+      <c r="N100" s="11"/>
+      <c r="O100" s="10"/>
+      <c r="P100" s="10"/>
+      <c r="Q100" s="10"/>
+      <c r="R100" s="11"/>
+      <c r="S100" s="13"/>
+      <c r="T100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10"/>
@@ -3005,12 +3107,13 @@
       <c r="K101" s="11"/>
       <c r="L101" s="11"/>
       <c r="M101" s="11"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="14"/>
-      <c r="P101" s="14"/>
-      <c r="Q101" s="14"/>
-      <c r="R101" s="13"/>
-      <c r="S101" s="10"/>
+      <c r="N101" s="11"/>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="11"/>
+      <c r="S101" s="13"/>
+      <c r="T101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="10"/>
@@ -3026,12 +3129,13 @@
       <c r="K102" s="11"/>
       <c r="L102" s="11"/>
       <c r="M102" s="11"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="14"/>
-      <c r="P102" s="14"/>
-      <c r="Q102" s="14"/>
-      <c r="R102" s="13"/>
-      <c r="S102" s="10"/>
+      <c r="N102" s="11"/>
+      <c r="O102" s="10"/>
+      <c r="P102" s="10"/>
+      <c r="Q102" s="10"/>
+      <c r="R102" s="11"/>
+      <c r="S102" s="13"/>
+      <c r="T102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="10"/>
@@ -3047,12 +3151,13 @@
       <c r="K103" s="11"/>
       <c r="L103" s="11"/>
       <c r="M103" s="11"/>
-      <c r="N103" s="13"/>
-      <c r="O103" s="14"/>
-      <c r="P103" s="14"/>
-      <c r="Q103" s="14"/>
-      <c r="R103" s="13"/>
-      <c r="S103" s="10"/>
+      <c r="N103" s="11"/>
+      <c r="O103" s="10"/>
+      <c r="P103" s="10"/>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="11"/>
+      <c r="S103" s="13"/>
+      <c r="T103" s="10"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10"/>
@@ -3068,12 +3173,13 @@
       <c r="K104" s="11"/>
       <c r="L104" s="11"/>
       <c r="M104" s="11"/>
-      <c r="N104" s="13"/>
-      <c r="O104" s="14"/>
-      <c r="P104" s="14"/>
-      <c r="Q104" s="14"/>
-      <c r="R104" s="13"/>
-      <c r="S104" s="10"/>
+      <c r="N104" s="11"/>
+      <c r="O104" s="10"/>
+      <c r="P104" s="10"/>
+      <c r="Q104" s="10"/>
+      <c r="R104" s="11"/>
+      <c r="S104" s="13"/>
+      <c r="T104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10"/>
@@ -3089,12 +3195,13 @@
       <c r="K105" s="11"/>
       <c r="L105" s="11"/>
       <c r="M105" s="11"/>
-      <c r="N105" s="13"/>
-      <c r="O105" s="14"/>
-      <c r="P105" s="14"/>
-      <c r="Q105" s="14"/>
-      <c r="R105" s="13"/>
-      <c r="S105" s="10"/>
+      <c r="N105" s="11"/>
+      <c r="O105" s="10"/>
+      <c r="P105" s="10"/>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="11"/>
+      <c r="S105" s="13"/>
+      <c r="T105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10"/>
@@ -3110,12 +3217,13 @@
       <c r="K106" s="11"/>
       <c r="L106" s="11"/>
       <c r="M106" s="11"/>
-      <c r="N106" s="13"/>
-      <c r="O106" s="14"/>
-      <c r="P106" s="14"/>
-      <c r="Q106" s="14"/>
-      <c r="R106" s="13"/>
-      <c r="S106" s="10"/>
+      <c r="N106" s="11"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
+      <c r="Q106" s="10"/>
+      <c r="R106" s="11"/>
+      <c r="S106" s="13"/>
+      <c r="T106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10"/>
@@ -3131,12 +3239,13 @@
       <c r="K107" s="11"/>
       <c r="L107" s="11"/>
       <c r="M107" s="11"/>
-      <c r="N107" s="13"/>
-      <c r="O107" s="14"/>
-      <c r="P107" s="14"/>
-      <c r="Q107" s="14"/>
-      <c r="R107" s="13"/>
-      <c r="S107" s="10"/>
+      <c r="N107" s="11"/>
+      <c r="O107" s="10"/>
+      <c r="P107" s="10"/>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="11"/>
+      <c r="S107" s="13"/>
+      <c r="T107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10"/>
@@ -3152,12 +3261,13 @@
       <c r="K108" s="11"/>
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
-      <c r="N108" s="13"/>
-      <c r="O108" s="14"/>
-      <c r="P108" s="14"/>
-      <c r="Q108" s="14"/>
-      <c r="R108" s="13"/>
-      <c r="S108" s="10"/>
+      <c r="N108" s="11"/>
+      <c r="O108" s="10"/>
+      <c r="P108" s="10"/>
+      <c r="Q108" s="10"/>
+      <c r="R108" s="11"/>
+      <c r="S108" s="13"/>
+      <c r="T108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10"/>
@@ -3173,12 +3283,13 @@
       <c r="K109" s="11"/>
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
-      <c r="N109" s="13"/>
-      <c r="O109" s="14"/>
-      <c r="P109" s="14"/>
-      <c r="Q109" s="14"/>
-      <c r="R109" s="13"/>
-      <c r="S109" s="10"/>
+      <c r="N109" s="11"/>
+      <c r="O109" s="10"/>
+      <c r="P109" s="10"/>
+      <c r="Q109" s="10"/>
+      <c r="R109" s="11"/>
+      <c r="S109" s="13"/>
+      <c r="T109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10"/>
@@ -3194,12 +3305,13 @@
       <c r="K110" s="11"/>
       <c r="L110" s="11"/>
       <c r="M110" s="11"/>
-      <c r="N110" s="13"/>
-      <c r="O110" s="14"/>
-      <c r="P110" s="14"/>
-      <c r="Q110" s="14"/>
-      <c r="R110" s="13"/>
-      <c r="S110" s="10"/>
+      <c r="N110" s="11"/>
+      <c r="O110" s="10"/>
+      <c r="P110" s="10"/>
+      <c r="Q110" s="10"/>
+      <c r="R110" s="11"/>
+      <c r="S110" s="13"/>
+      <c r="T110" s="10"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="10"/>
@@ -3215,12 +3327,13 @@
       <c r="K111" s="11"/>
       <c r="L111" s="11"/>
       <c r="M111" s="11"/>
-      <c r="N111" s="13"/>
-      <c r="O111" s="14"/>
-      <c r="P111" s="14"/>
-      <c r="Q111" s="14"/>
-      <c r="R111" s="13"/>
-      <c r="S111" s="10"/>
+      <c r="N111" s="11"/>
+      <c r="O111" s="10"/>
+      <c r="P111" s="10"/>
+      <c r="Q111" s="10"/>
+      <c r="R111" s="11"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="10"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="10"/>
@@ -3236,12 +3349,13 @@
       <c r="K112" s="11"/>
       <c r="L112" s="11"/>
       <c r="M112" s="11"/>
-      <c r="N112" s="13"/>
-      <c r="O112" s="14"/>
-      <c r="P112" s="14"/>
-      <c r="Q112" s="14"/>
-      <c r="R112" s="13"/>
-      <c r="S112" s="10"/>
+      <c r="N112" s="11"/>
+      <c r="O112" s="10"/>
+      <c r="P112" s="10"/>
+      <c r="Q112" s="10"/>
+      <c r="R112" s="11"/>
+      <c r="S112" s="13"/>
+      <c r="T112" s="10"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="10"/>
@@ -3257,12 +3371,13 @@
       <c r="K113" s="11"/>
       <c r="L113" s="11"/>
       <c r="M113" s="11"/>
-      <c r="N113" s="13"/>
-      <c r="O113" s="14"/>
-      <c r="P113" s="14"/>
-      <c r="Q113" s="14"/>
-      <c r="R113" s="13"/>
-      <c r="S113" s="10"/>
+      <c r="N113" s="11"/>
+      <c r="O113" s="10"/>
+      <c r="P113" s="10"/>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="11"/>
+      <c r="S113" s="13"/>
+      <c r="T113" s="10"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="10"/>
@@ -3278,12 +3393,13 @@
       <c r="K114" s="11"/>
       <c r="L114" s="11"/>
       <c r="M114" s="11"/>
-      <c r="N114" s="13"/>
-      <c r="O114" s="14"/>
-      <c r="P114" s="14"/>
-      <c r="Q114" s="14"/>
-      <c r="R114" s="13"/>
-      <c r="S114" s="10"/>
+      <c r="N114" s="11"/>
+      <c r="O114" s="10"/>
+      <c r="P114" s="10"/>
+      <c r="Q114" s="10"/>
+      <c r="R114" s="11"/>
+      <c r="S114" s="13"/>
+      <c r="T114" s="10"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="10"/>
@@ -3299,12 +3415,13 @@
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
       <c r="M115" s="11"/>
-      <c r="N115" s="13"/>
-      <c r="O115" s="14"/>
-      <c r="P115" s="14"/>
-      <c r="Q115" s="14"/>
-      <c r="R115" s="13"/>
-      <c r="S115" s="10"/>
+      <c r="N115" s="11"/>
+      <c r="O115" s="10"/>
+      <c r="P115" s="10"/>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="11"/>
+      <c r="S115" s="13"/>
+      <c r="T115" s="10"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="10"/>
@@ -3320,12 +3437,13 @@
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
       <c r="M116" s="11"/>
-      <c r="N116" s="13"/>
-      <c r="O116" s="14"/>
-      <c r="P116" s="14"/>
-      <c r="Q116" s="14"/>
-      <c r="R116" s="13"/>
-      <c r="S116" s="10"/>
+      <c r="N116" s="11"/>
+      <c r="O116" s="10"/>
+      <c r="P116" s="10"/>
+      <c r="Q116" s="10"/>
+      <c r="R116" s="11"/>
+      <c r="S116" s="13"/>
+      <c r="T116" s="10"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="10"/>
@@ -3341,12 +3459,13 @@
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
       <c r="M117" s="11"/>
-      <c r="N117" s="13"/>
-      <c r="O117" s="14"/>
-      <c r="P117" s="14"/>
-      <c r="Q117" s="14"/>
-      <c r="R117" s="13"/>
-      <c r="S117" s="10"/>
+      <c r="N117" s="11"/>
+      <c r="O117" s="10"/>
+      <c r="P117" s="10"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="11"/>
+      <c r="S117" s="13"/>
+      <c r="T117" s="10"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="10"/>
@@ -3362,12 +3481,13 @@
       <c r="K118" s="11"/>
       <c r="L118" s="11"/>
       <c r="M118" s="11"/>
-      <c r="N118" s="13"/>
-      <c r="O118" s="14"/>
-      <c r="P118" s="14"/>
-      <c r="Q118" s="14"/>
-      <c r="R118" s="13"/>
-      <c r="S118" s="10"/>
+      <c r="N118" s="11"/>
+      <c r="O118" s="10"/>
+      <c r="P118" s="10"/>
+      <c r="Q118" s="10"/>
+      <c r="R118" s="11"/>
+      <c r="S118" s="13"/>
+      <c r="T118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="10"/>
@@ -3383,12 +3503,13 @@
       <c r="K119" s="11"/>
       <c r="L119" s="11"/>
       <c r="M119" s="11"/>
-      <c r="N119" s="13"/>
-      <c r="O119" s="14"/>
-      <c r="P119" s="14"/>
-      <c r="Q119" s="14"/>
-      <c r="R119" s="13"/>
-      <c r="S119" s="10"/>
+      <c r="N119" s="11"/>
+      <c r="O119" s="10"/>
+      <c r="P119" s="10"/>
+      <c r="Q119" s="10"/>
+      <c r="R119" s="11"/>
+      <c r="S119" s="13"/>
+      <c r="T119" s="10"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="10"/>
@@ -3404,12 +3525,13 @@
       <c r="K120" s="11"/>
       <c r="L120" s="11"/>
       <c r="M120" s="11"/>
-      <c r="N120" s="13"/>
-      <c r="O120" s="14"/>
-      <c r="P120" s="14"/>
-      <c r="Q120" s="14"/>
-      <c r="R120" s="13"/>
-      <c r="S120" s="10"/>
+      <c r="N120" s="11"/>
+      <c r="O120" s="10"/>
+      <c r="P120" s="10"/>
+      <c r="Q120" s="10"/>
+      <c r="R120" s="11"/>
+      <c r="S120" s="13"/>
+      <c r="T120" s="10"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="10"/>
@@ -3425,12 +3547,13 @@
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
       <c r="M121" s="11"/>
-      <c r="N121" s="13"/>
-      <c r="O121" s="14"/>
-      <c r="P121" s="14"/>
-      <c r="Q121" s="14"/>
-      <c r="R121" s="13"/>
-      <c r="S121" s="10"/>
+      <c r="N121" s="11"/>
+      <c r="O121" s="10"/>
+      <c r="P121" s="10"/>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="11"/>
+      <c r="S121" s="13"/>
+      <c r="T121" s="10"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="10"/>
@@ -3446,12 +3569,13 @@
       <c r="K122" s="11"/>
       <c r="L122" s="11"/>
       <c r="M122" s="11"/>
-      <c r="N122" s="13"/>
-      <c r="O122" s="14"/>
-      <c r="P122" s="14"/>
-      <c r="Q122" s="14"/>
-      <c r="R122" s="13"/>
-      <c r="S122" s="10"/>
+      <c r="N122" s="11"/>
+      <c r="O122" s="10"/>
+      <c r="P122" s="10"/>
+      <c r="Q122" s="10"/>
+      <c r="R122" s="11"/>
+      <c r="S122" s="13"/>
+      <c r="T122" s="10"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="10"/>
@@ -3467,12 +3591,13 @@
       <c r="K123" s="11"/>
       <c r="L123" s="11"/>
       <c r="M123" s="11"/>
-      <c r="N123" s="13"/>
-      <c r="O123" s="14"/>
-      <c r="P123" s="14"/>
-      <c r="Q123" s="14"/>
-      <c r="R123" s="13"/>
-      <c r="S123" s="10"/>
+      <c r="N123" s="11"/>
+      <c r="O123" s="10"/>
+      <c r="P123" s="10"/>
+      <c r="Q123" s="10"/>
+      <c r="R123" s="11"/>
+      <c r="S123" s="13"/>
+      <c r="T123" s="10"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="10"/>
@@ -3488,12 +3613,13 @@
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
       <c r="M124" s="11"/>
-      <c r="N124" s="13"/>
-      <c r="O124" s="14"/>
-      <c r="P124" s="14"/>
-      <c r="Q124" s="14"/>
-      <c r="R124" s="13"/>
-      <c r="S124" s="10"/>
+      <c r="N124" s="11"/>
+      <c r="O124" s="10"/>
+      <c r="P124" s="10"/>
+      <c r="Q124" s="10"/>
+      <c r="R124" s="11"/>
+      <c r="S124" s="13"/>
+      <c r="T124" s="10"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="10"/>
@@ -3509,12 +3635,13 @@
       <c r="K125" s="11"/>
       <c r="L125" s="11"/>
       <c r="M125" s="11"/>
-      <c r="N125" s="13"/>
-      <c r="O125" s="14"/>
-      <c r="P125" s="14"/>
-      <c r="Q125" s="14"/>
-      <c r="R125" s="13"/>
-      <c r="S125" s="10"/>
+      <c r="N125" s="11"/>
+      <c r="O125" s="10"/>
+      <c r="P125" s="10"/>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="11"/>
+      <c r="S125" s="13"/>
+      <c r="T125" s="10"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="10"/>
@@ -3530,12 +3657,13 @@
       <c r="K126" s="11"/>
       <c r="L126" s="11"/>
       <c r="M126" s="11"/>
-      <c r="N126" s="13"/>
-      <c r="O126" s="14"/>
-      <c r="P126" s="14"/>
-      <c r="Q126" s="14"/>
-      <c r="R126" s="13"/>
-      <c r="S126" s="10"/>
+      <c r="N126" s="11"/>
+      <c r="O126" s="10"/>
+      <c r="P126" s="10"/>
+      <c r="Q126" s="10"/>
+      <c r="R126" s="11"/>
+      <c r="S126" s="13"/>
+      <c r="T126" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="10"/>
@@ -3551,12 +3679,13 @@
       <c r="K127" s="11"/>
       <c r="L127" s="11"/>
       <c r="M127" s="11"/>
-      <c r="N127" s="13"/>
-      <c r="O127" s="14"/>
-      <c r="P127" s="14"/>
-      <c r="Q127" s="14"/>
-      <c r="R127" s="13"/>
-      <c r="S127" s="10"/>
+      <c r="N127" s="11"/>
+      <c r="O127" s="10"/>
+      <c r="P127" s="10"/>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="11"/>
+      <c r="S127" s="13"/>
+      <c r="T127" s="10"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="10"/>
@@ -3572,12 +3701,13 @@
       <c r="K128" s="11"/>
       <c r="L128" s="11"/>
       <c r="M128" s="11"/>
-      <c r="N128" s="13"/>
-      <c r="O128" s="14"/>
-      <c r="P128" s="14"/>
-      <c r="Q128" s="14"/>
-      <c r="R128" s="13"/>
-      <c r="S128" s="10"/>
+      <c r="N128" s="11"/>
+      <c r="O128" s="10"/>
+      <c r="P128" s="10"/>
+      <c r="Q128" s="10"/>
+      <c r="R128" s="11"/>
+      <c r="S128" s="13"/>
+      <c r="T128" s="10"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="10"/>
@@ -3593,12 +3723,13 @@
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
       <c r="M129" s="11"/>
-      <c r="N129" s="13"/>
-      <c r="O129" s="14"/>
-      <c r="P129" s="14"/>
-      <c r="Q129" s="14"/>
-      <c r="R129" s="13"/>
-      <c r="S129" s="10"/>
+      <c r="N129" s="11"/>
+      <c r="O129" s="10"/>
+      <c r="P129" s="10"/>
+      <c r="Q129" s="10"/>
+      <c r="R129" s="11"/>
+      <c r="S129" s="13"/>
+      <c r="T129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="10"/>
@@ -3614,12 +3745,13 @@
       <c r="K130" s="11"/>
       <c r="L130" s="11"/>
       <c r="M130" s="11"/>
-      <c r="N130" s="13"/>
-      <c r="O130" s="14"/>
-      <c r="P130" s="14"/>
-      <c r="Q130" s="14"/>
-      <c r="R130" s="13"/>
-      <c r="S130" s="10"/>
+      <c r="N130" s="11"/>
+      <c r="O130" s="10"/>
+      <c r="P130" s="10"/>
+      <c r="Q130" s="10"/>
+      <c r="R130" s="11"/>
+      <c r="S130" s="13"/>
+      <c r="T130" s="10"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="10"/>
@@ -3635,12 +3767,13 @@
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
       <c r="M131" s="11"/>
-      <c r="N131" s="13"/>
-      <c r="O131" s="14"/>
-      <c r="P131" s="14"/>
-      <c r="Q131" s="14"/>
-      <c r="R131" s="13"/>
-      <c r="S131" s="10"/>
+      <c r="N131" s="11"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="11"/>
+      <c r="S131" s="13"/>
+      <c r="T131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="10"/>
@@ -3656,12 +3789,13 @@
       <c r="K132" s="11"/>
       <c r="L132" s="11"/>
       <c r="M132" s="11"/>
-      <c r="N132" s="13"/>
-      <c r="O132" s="14"/>
-      <c r="P132" s="14"/>
-      <c r="Q132" s="14"/>
-      <c r="R132" s="13"/>
-      <c r="S132" s="10"/>
+      <c r="N132" s="11"/>
+      <c r="O132" s="10"/>
+      <c r="P132" s="10"/>
+      <c r="Q132" s="10"/>
+      <c r="R132" s="11"/>
+      <c r="S132" s="13"/>
+      <c r="T132" s="10"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="10"/>
@@ -3677,12 +3811,13 @@
       <c r="K133" s="11"/>
       <c r="L133" s="11"/>
       <c r="M133" s="11"/>
-      <c r="N133" s="13"/>
-      <c r="O133" s="14"/>
-      <c r="P133" s="14"/>
-      <c r="Q133" s="14"/>
-      <c r="R133" s="13"/>
-      <c r="S133" s="10"/>
+      <c r="N133" s="11"/>
+      <c r="O133" s="10"/>
+      <c r="P133" s="10"/>
+      <c r="Q133" s="10"/>
+      <c r="R133" s="11"/>
+      <c r="S133" s="13"/>
+      <c r="T133" s="10"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="10"/>
@@ -3698,12 +3833,13 @@
       <c r="K134" s="11"/>
       <c r="L134" s="11"/>
       <c r="M134" s="11"/>
-      <c r="N134" s="13"/>
-      <c r="O134" s="14"/>
-      <c r="P134" s="14"/>
-      <c r="Q134" s="14"/>
-      <c r="R134" s="13"/>
-      <c r="S134" s="10"/>
+      <c r="N134" s="11"/>
+      <c r="O134" s="10"/>
+      <c r="P134" s="10"/>
+      <c r="Q134" s="10"/>
+      <c r="R134" s="11"/>
+      <c r="S134" s="13"/>
+      <c r="T134" s="10"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="10"/>
@@ -3719,12 +3855,13 @@
       <c r="K135" s="11"/>
       <c r="L135" s="11"/>
       <c r="M135" s="11"/>
-      <c r="N135" s="13"/>
-      <c r="O135" s="14"/>
-      <c r="P135" s="14"/>
-      <c r="Q135" s="14"/>
-      <c r="R135" s="13"/>
-      <c r="S135" s="10"/>
+      <c r="N135" s="11"/>
+      <c r="O135" s="10"/>
+      <c r="P135" s="10"/>
+      <c r="Q135" s="10"/>
+      <c r="R135" s="11"/>
+      <c r="S135" s="13"/>
+      <c r="T135" s="10"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="10"/>
@@ -3740,12 +3877,13 @@
       <c r="K136" s="11"/>
       <c r="L136" s="11"/>
       <c r="M136" s="11"/>
-      <c r="N136" s="13"/>
-      <c r="O136" s="14"/>
-      <c r="P136" s="14"/>
-      <c r="Q136" s="14"/>
-      <c r="R136" s="13"/>
-      <c r="S136" s="10"/>
+      <c r="N136" s="11"/>
+      <c r="O136" s="10"/>
+      <c r="P136" s="10"/>
+      <c r="Q136" s="10"/>
+      <c r="R136" s="11"/>
+      <c r="S136" s="13"/>
+      <c r="T136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="10"/>
@@ -3761,12 +3899,13 @@
       <c r="K137" s="11"/>
       <c r="L137" s="11"/>
       <c r="M137" s="11"/>
-      <c r="N137" s="13"/>
-      <c r="O137" s="14"/>
-      <c r="P137" s="14"/>
-      <c r="Q137" s="14"/>
-      <c r="R137" s="13"/>
-      <c r="S137" s="10"/>
+      <c r="N137" s="11"/>
+      <c r="O137" s="10"/>
+      <c r="P137" s="10"/>
+      <c r="Q137" s="10"/>
+      <c r="R137" s="11"/>
+      <c r="S137" s="13"/>
+      <c r="T137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="10"/>
@@ -3782,12 +3921,13 @@
       <c r="K138" s="11"/>
       <c r="L138" s="11"/>
       <c r="M138" s="11"/>
-      <c r="N138" s="13"/>
-      <c r="O138" s="14"/>
-      <c r="P138" s="14"/>
-      <c r="Q138" s="14"/>
-      <c r="R138" s="13"/>
-      <c r="S138" s="10"/>
+      <c r="N138" s="11"/>
+      <c r="O138" s="10"/>
+      <c r="P138" s="10"/>
+      <c r="Q138" s="10"/>
+      <c r="R138" s="11"/>
+      <c r="S138" s="13"/>
+      <c r="T138" s="10"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="10"/>
@@ -3803,12 +3943,13 @@
       <c r="K139" s="11"/>
       <c r="L139" s="11"/>
       <c r="M139" s="11"/>
-      <c r="N139" s="13"/>
-      <c r="O139" s="14"/>
-      <c r="P139" s="14"/>
-      <c r="Q139" s="14"/>
-      <c r="R139" s="13"/>
-      <c r="S139" s="10"/>
+      <c r="N139" s="11"/>
+      <c r="O139" s="10"/>
+      <c r="P139" s="10"/>
+      <c r="Q139" s="10"/>
+      <c r="R139" s="11"/>
+      <c r="S139" s="13"/>
+      <c r="T139" s="10"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="10"/>
@@ -3824,12 +3965,13 @@
       <c r="K140" s="11"/>
       <c r="L140" s="11"/>
       <c r="M140" s="11"/>
-      <c r="N140" s="13"/>
-      <c r="O140" s="14"/>
-      <c r="P140" s="14"/>
-      <c r="Q140" s="14"/>
-      <c r="R140" s="13"/>
-      <c r="S140" s="10"/>
+      <c r="N140" s="11"/>
+      <c r="O140" s="10"/>
+      <c r="P140" s="10"/>
+      <c r="Q140" s="10"/>
+      <c r="R140" s="11"/>
+      <c r="S140" s="13"/>
+      <c r="T140" s="10"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="10"/>
@@ -3845,12 +3987,13 @@
       <c r="K141" s="11"/>
       <c r="L141" s="11"/>
       <c r="M141" s="11"/>
-      <c r="N141" s="13"/>
-      <c r="O141" s="14"/>
-      <c r="P141" s="14"/>
-      <c r="Q141" s="14"/>
-      <c r="R141" s="13"/>
-      <c r="S141" s="10"/>
+      <c r="N141" s="11"/>
+      <c r="O141" s="10"/>
+      <c r="P141" s="10"/>
+      <c r="Q141" s="10"/>
+      <c r="R141" s="11"/>
+      <c r="S141" s="13"/>
+      <c r="T141" s="10"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="10"/>
@@ -3866,12 +4009,13 @@
       <c r="K142" s="11"/>
       <c r="L142" s="11"/>
       <c r="M142" s="11"/>
-      <c r="N142" s="13"/>
-      <c r="O142" s="14"/>
-      <c r="P142" s="14"/>
-      <c r="Q142" s="14"/>
-      <c r="R142" s="13"/>
-      <c r="S142" s="10"/>
+      <c r="N142" s="11"/>
+      <c r="O142" s="10"/>
+      <c r="P142" s="10"/>
+      <c r="Q142" s="10"/>
+      <c r="R142" s="11"/>
+      <c r="S142" s="13"/>
+      <c r="T142" s="10"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="10"/>
@@ -3887,12 +4031,13 @@
       <c r="K143" s="11"/>
       <c r="L143" s="11"/>
       <c r="M143" s="11"/>
-      <c r="N143" s="13"/>
-      <c r="O143" s="14"/>
-      <c r="P143" s="14"/>
-      <c r="Q143" s="14"/>
-      <c r="R143" s="13"/>
-      <c r="S143" s="10"/>
+      <c r="N143" s="11"/>
+      <c r="O143" s="10"/>
+      <c r="P143" s="10"/>
+      <c r="Q143" s="10"/>
+      <c r="R143" s="11"/>
+      <c r="S143" s="13"/>
+      <c r="T143" s="10"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="10"/>
@@ -3908,12 +4053,13 @@
       <c r="K144" s="11"/>
       <c r="L144" s="11"/>
       <c r="M144" s="11"/>
-      <c r="N144" s="13"/>
-      <c r="O144" s="14"/>
-      <c r="P144" s="14"/>
-      <c r="Q144" s="14"/>
-      <c r="R144" s="13"/>
-      <c r="S144" s="10"/>
+      <c r="N144" s="11"/>
+      <c r="O144" s="10"/>
+      <c r="P144" s="10"/>
+      <c r="Q144" s="10"/>
+      <c r="R144" s="11"/>
+      <c r="S144" s="13"/>
+      <c r="T144" s="10"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="10"/>
@@ -3929,12 +4075,13 @@
       <c r="K145" s="11"/>
       <c r="L145" s="11"/>
       <c r="M145" s="11"/>
-      <c r="N145" s="13"/>
-      <c r="O145" s="14"/>
-      <c r="P145" s="14"/>
-      <c r="Q145" s="14"/>
-      <c r="R145" s="13"/>
-      <c r="S145" s="10"/>
+      <c r="N145" s="11"/>
+      <c r="O145" s="10"/>
+      <c r="P145" s="10"/>
+      <c r="Q145" s="10"/>
+      <c r="R145" s="11"/>
+      <c r="S145" s="13"/>
+      <c r="T145" s="10"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="10"/>
@@ -3950,12 +4097,13 @@
       <c r="K146" s="11"/>
       <c r="L146" s="11"/>
       <c r="M146" s="11"/>
-      <c r="N146" s="13"/>
-      <c r="O146" s="14"/>
-      <c r="P146" s="14"/>
-      <c r="Q146" s="14"/>
-      <c r="R146" s="13"/>
-      <c r="S146" s="10"/>
+      <c r="N146" s="11"/>
+      <c r="O146" s="10"/>
+      <c r="P146" s="10"/>
+      <c r="Q146" s="10"/>
+      <c r="R146" s="11"/>
+      <c r="S146" s="13"/>
+      <c r="T146" s="10"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="10"/>
@@ -3971,12 +4119,13 @@
       <c r="K147" s="11"/>
       <c r="L147" s="11"/>
       <c r="M147" s="11"/>
-      <c r="N147" s="13"/>
-      <c r="O147" s="14"/>
-      <c r="P147" s="14"/>
-      <c r="Q147" s="14"/>
-      <c r="R147" s="13"/>
-      <c r="S147" s="10"/>
+      <c r="N147" s="11"/>
+      <c r="O147" s="10"/>
+      <c r="P147" s="10"/>
+      <c r="Q147" s="10"/>
+      <c r="R147" s="11"/>
+      <c r="S147" s="13"/>
+      <c r="T147" s="10"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="10"/>
@@ -3992,12 +4141,13 @@
       <c r="K148" s="11"/>
       <c r="L148" s="11"/>
       <c r="M148" s="11"/>
-      <c r="N148" s="13"/>
-      <c r="O148" s="14"/>
-      <c r="P148" s="14"/>
-      <c r="Q148" s="14"/>
-      <c r="R148" s="13"/>
-      <c r="S148" s="10"/>
+      <c r="N148" s="11"/>
+      <c r="O148" s="10"/>
+      <c r="P148" s="10"/>
+      <c r="Q148" s="10"/>
+      <c r="R148" s="11"/>
+      <c r="S148" s="13"/>
+      <c r="T148" s="10"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="10"/>
@@ -4013,12 +4163,13 @@
       <c r="K149" s="11"/>
       <c r="L149" s="11"/>
       <c r="M149" s="11"/>
-      <c r="N149" s="13"/>
-      <c r="O149" s="14"/>
-      <c r="P149" s="14"/>
-      <c r="Q149" s="14"/>
-      <c r="R149" s="13"/>
-      <c r="S149" s="10"/>
+      <c r="N149" s="11"/>
+      <c r="O149" s="10"/>
+      <c r="P149" s="10"/>
+      <c r="Q149" s="10"/>
+      <c r="R149" s="11"/>
+      <c r="S149" s="13"/>
+      <c r="T149" s="10"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="10"/>
@@ -4034,12 +4185,13 @@
       <c r="K150" s="11"/>
       <c r="L150" s="11"/>
       <c r="M150" s="11"/>
-      <c r="N150" s="13"/>
-      <c r="O150" s="14"/>
-      <c r="P150" s="14"/>
-      <c r="Q150" s="14"/>
-      <c r="R150" s="13"/>
-      <c r="S150" s="10"/>
+      <c r="N150" s="11"/>
+      <c r="O150" s="10"/>
+      <c r="P150" s="10"/>
+      <c r="Q150" s="10"/>
+      <c r="R150" s="11"/>
+      <c r="S150" s="13"/>
+      <c r="T150" s="10"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="10"/>
@@ -4055,12 +4207,13 @@
       <c r="K151" s="11"/>
       <c r="L151" s="11"/>
       <c r="M151" s="11"/>
-      <c r="N151" s="13"/>
-      <c r="O151" s="14"/>
-      <c r="P151" s="14"/>
-      <c r="Q151" s="14"/>
-      <c r="R151" s="13"/>
-      <c r="S151" s="10"/>
+      <c r="N151" s="11"/>
+      <c r="O151" s="10"/>
+      <c r="P151" s="10"/>
+      <c r="Q151" s="10"/>
+      <c r="R151" s="11"/>
+      <c r="S151" s="13"/>
+      <c r="T151" s="10"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="10"/>
@@ -4076,12 +4229,13 @@
       <c r="K152" s="11"/>
       <c r="L152" s="11"/>
       <c r="M152" s="11"/>
-      <c r="N152" s="13"/>
-      <c r="O152" s="14"/>
-      <c r="P152" s="14"/>
-      <c r="Q152" s="14"/>
-      <c r="R152" s="13"/>
-      <c r="S152" s="10"/>
+      <c r="N152" s="11"/>
+      <c r="O152" s="10"/>
+      <c r="P152" s="10"/>
+      <c r="Q152" s="10"/>
+      <c r="R152" s="11"/>
+      <c r="S152" s="13"/>
+      <c r="T152" s="10"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="10"/>
@@ -4097,12 +4251,13 @@
       <c r="K153" s="11"/>
       <c r="L153" s="11"/>
       <c r="M153" s="11"/>
-      <c r="N153" s="13"/>
-      <c r="O153" s="14"/>
-      <c r="P153" s="14"/>
-      <c r="Q153" s="14"/>
-      <c r="R153" s="13"/>
-      <c r="S153" s="10"/>
+      <c r="N153" s="11"/>
+      <c r="O153" s="10"/>
+      <c r="P153" s="10"/>
+      <c r="Q153" s="10"/>
+      <c r="R153" s="11"/>
+      <c r="S153" s="13"/>
+      <c r="T153" s="10"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="10"/>
@@ -4118,12 +4273,13 @@
       <c r="K154" s="11"/>
       <c r="L154" s="11"/>
       <c r="M154" s="11"/>
-      <c r="N154" s="13"/>
-      <c r="O154" s="14"/>
-      <c r="P154" s="14"/>
-      <c r="Q154" s="14"/>
-      <c r="R154" s="13"/>
-      <c r="S154" s="10"/>
+      <c r="N154" s="11"/>
+      <c r="O154" s="10"/>
+      <c r="P154" s="10"/>
+      <c r="Q154" s="10"/>
+      <c r="R154" s="11"/>
+      <c r="S154" s="13"/>
+      <c r="T154" s="10"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="10"/>
@@ -4139,12 +4295,13 @@
       <c r="K155" s="11"/>
       <c r="L155" s="11"/>
       <c r="M155" s="11"/>
-      <c r="N155" s="13"/>
-      <c r="O155" s="14"/>
-      <c r="P155" s="14"/>
-      <c r="Q155" s="14"/>
-      <c r="R155" s="13"/>
-      <c r="S155" s="10"/>
+      <c r="N155" s="11"/>
+      <c r="O155" s="10"/>
+      <c r="P155" s="10"/>
+      <c r="Q155" s="10"/>
+      <c r="R155" s="11"/>
+      <c r="S155" s="13"/>
+      <c r="T155" s="10"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="10"/>
@@ -4160,12 +4317,13 @@
       <c r="K156" s="11"/>
       <c r="L156" s="11"/>
       <c r="M156" s="11"/>
-      <c r="N156" s="13"/>
-      <c r="O156" s="14"/>
-      <c r="P156" s="14"/>
-      <c r="Q156" s="14"/>
-      <c r="R156" s="13"/>
-      <c r="S156" s="10"/>
+      <c r="N156" s="11"/>
+      <c r="O156" s="10"/>
+      <c r="P156" s="10"/>
+      <c r="Q156" s="10"/>
+      <c r="R156" s="11"/>
+      <c r="S156" s="13"/>
+      <c r="T156" s="10"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="10"/>
@@ -4181,12 +4339,13 @@
       <c r="K157" s="11"/>
       <c r="L157" s="11"/>
       <c r="M157" s="11"/>
-      <c r="N157" s="13"/>
-      <c r="O157" s="14"/>
-      <c r="P157" s="14"/>
-      <c r="Q157" s="14"/>
-      <c r="R157" s="13"/>
-      <c r="S157" s="10"/>
+      <c r="N157" s="11"/>
+      <c r="O157" s="10"/>
+      <c r="P157" s="10"/>
+      <c r="Q157" s="10"/>
+      <c r="R157" s="11"/>
+      <c r="S157" s="13"/>
+      <c r="T157" s="10"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="10"/>
@@ -4202,12 +4361,13 @@
       <c r="K158" s="11"/>
       <c r="L158" s="11"/>
       <c r="M158" s="11"/>
-      <c r="N158" s="13"/>
-      <c r="O158" s="14"/>
-      <c r="P158" s="14"/>
-      <c r="Q158" s="14"/>
-      <c r="R158" s="13"/>
-      <c r="S158" s="10"/>
+      <c r="N158" s="11"/>
+      <c r="O158" s="10"/>
+      <c r="P158" s="10"/>
+      <c r="Q158" s="10"/>
+      <c r="R158" s="11"/>
+      <c r="S158" s="13"/>
+      <c r="T158" s="10"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="10"/>
@@ -4223,12 +4383,13 @@
       <c r="K159" s="11"/>
       <c r="L159" s="11"/>
       <c r="M159" s="11"/>
-      <c r="N159" s="13"/>
-      <c r="O159" s="14"/>
-      <c r="P159" s="14"/>
-      <c r="Q159" s="14"/>
-      <c r="R159" s="13"/>
-      <c r="S159" s="10"/>
+      <c r="N159" s="11"/>
+      <c r="O159" s="10"/>
+      <c r="P159" s="10"/>
+      <c r="Q159" s="10"/>
+      <c r="R159" s="11"/>
+      <c r="S159" s="13"/>
+      <c r="T159" s="10"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="10"/>
@@ -4244,12 +4405,13 @@
       <c r="K160" s="11"/>
       <c r="L160" s="11"/>
       <c r="M160" s="11"/>
-      <c r="N160" s="13"/>
-      <c r="O160" s="14"/>
-      <c r="P160" s="14"/>
-      <c r="Q160" s="14"/>
-      <c r="R160" s="13"/>
-      <c r="S160" s="10"/>
+      <c r="N160" s="11"/>
+      <c r="O160" s="10"/>
+      <c r="P160" s="10"/>
+      <c r="Q160" s="10"/>
+      <c r="R160" s="11"/>
+      <c r="S160" s="13"/>
+      <c r="T160" s="10"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="10"/>
@@ -4265,12 +4427,13 @@
       <c r="K161" s="11"/>
       <c r="L161" s="11"/>
       <c r="M161" s="11"/>
-      <c r="N161" s="13"/>
-      <c r="O161" s="14"/>
-      <c r="P161" s="14"/>
-      <c r="Q161" s="14"/>
-      <c r="R161" s="13"/>
-      <c r="S161" s="10"/>
+      <c r="N161" s="11"/>
+      <c r="O161" s="10"/>
+      <c r="P161" s="10"/>
+      <c r="Q161" s="10"/>
+      <c r="R161" s="11"/>
+      <c r="S161" s="13"/>
+      <c r="T161" s="10"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="10"/>
@@ -4286,12 +4449,13 @@
       <c r="K162" s="11"/>
       <c r="L162" s="11"/>
       <c r="M162" s="11"/>
-      <c r="N162" s="13"/>
-      <c r="O162" s="14"/>
-      <c r="P162" s="14"/>
-      <c r="Q162" s="14"/>
-      <c r="R162" s="13"/>
-      <c r="S162" s="10"/>
+      <c r="N162" s="11"/>
+      <c r="O162" s="10"/>
+      <c r="P162" s="10"/>
+      <c r="Q162" s="10"/>
+      <c r="R162" s="11"/>
+      <c r="S162" s="13"/>
+      <c r="T162" s="10"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="10"/>
@@ -4307,12 +4471,13 @@
       <c r="K163" s="11"/>
       <c r="L163" s="11"/>
       <c r="M163" s="11"/>
-      <c r="N163" s="13"/>
-      <c r="O163" s="14"/>
-      <c r="P163" s="14"/>
-      <c r="Q163" s="14"/>
-      <c r="R163" s="13"/>
-      <c r="S163" s="10"/>
+      <c r="N163" s="11"/>
+      <c r="O163" s="10"/>
+      <c r="P163" s="10"/>
+      <c r="Q163" s="10"/>
+      <c r="R163" s="11"/>
+      <c r="S163" s="13"/>
+      <c r="T163" s="10"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="10"/>
@@ -4328,12 +4493,13 @@
       <c r="K164" s="11"/>
       <c r="L164" s="11"/>
       <c r="M164" s="11"/>
-      <c r="N164" s="13"/>
-      <c r="O164" s="14"/>
-      <c r="P164" s="14"/>
-      <c r="Q164" s="14"/>
-      <c r="R164" s="13"/>
-      <c r="S164" s="10"/>
+      <c r="N164" s="11"/>
+      <c r="O164" s="10"/>
+      <c r="P164" s="10"/>
+      <c r="Q164" s="10"/>
+      <c r="R164" s="11"/>
+      <c r="S164" s="13"/>
+      <c r="T164" s="10"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="10"/>
@@ -4349,12 +4515,13 @@
       <c r="K165" s="11"/>
       <c r="L165" s="11"/>
       <c r="M165" s="11"/>
-      <c r="N165" s="13"/>
-      <c r="O165" s="14"/>
-      <c r="P165" s="14"/>
-      <c r="Q165" s="14"/>
-      <c r="R165" s="13"/>
-      <c r="S165" s="10"/>
+      <c r="N165" s="11"/>
+      <c r="O165" s="10"/>
+      <c r="P165" s="10"/>
+      <c r="Q165" s="10"/>
+      <c r="R165" s="11"/>
+      <c r="S165" s="13"/>
+      <c r="T165" s="10"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="10"/>
@@ -4370,12 +4537,13 @@
       <c r="K166" s="11"/>
       <c r="L166" s="11"/>
       <c r="M166" s="11"/>
-      <c r="N166" s="13"/>
-      <c r="O166" s="14"/>
-      <c r="P166" s="14"/>
-      <c r="Q166" s="14"/>
-      <c r="R166" s="13"/>
-      <c r="S166" s="10"/>
+      <c r="N166" s="11"/>
+      <c r="O166" s="10"/>
+      <c r="P166" s="10"/>
+      <c r="Q166" s="10"/>
+      <c r="R166" s="11"/>
+      <c r="S166" s="13"/>
+      <c r="T166" s="10"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="10"/>
@@ -4391,12 +4559,13 @@
       <c r="K167" s="11"/>
       <c r="L167" s="11"/>
       <c r="M167" s="11"/>
-      <c r="N167" s="13"/>
-      <c r="O167" s="14"/>
-      <c r="P167" s="14"/>
-      <c r="Q167" s="14"/>
-      <c r="R167" s="13"/>
-      <c r="S167" s="10"/>
+      <c r="N167" s="11"/>
+      <c r="O167" s="10"/>
+      <c r="P167" s="10"/>
+      <c r="Q167" s="10"/>
+      <c r="R167" s="11"/>
+      <c r="S167" s="13"/>
+      <c r="T167" s="10"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="10"/>
@@ -4412,12 +4581,13 @@
       <c r="K168" s="11"/>
       <c r="L168" s="11"/>
       <c r="M168" s="11"/>
-      <c r="N168" s="13"/>
-      <c r="O168" s="14"/>
-      <c r="P168" s="14"/>
-      <c r="Q168" s="14"/>
-      <c r="R168" s="13"/>
-      <c r="S168" s="10"/>
+      <c r="N168" s="11"/>
+      <c r="O168" s="10"/>
+      <c r="P168" s="10"/>
+      <c r="Q168" s="10"/>
+      <c r="R168" s="11"/>
+      <c r="S168" s="13"/>
+      <c r="T168" s="10"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="10"/>
@@ -4433,12 +4603,13 @@
       <c r="K169" s="11"/>
       <c r="L169" s="11"/>
       <c r="M169" s="11"/>
-      <c r="N169" s="13"/>
-      <c r="O169" s="14"/>
-      <c r="P169" s="14"/>
-      <c r="Q169" s="14"/>
-      <c r="R169" s="13"/>
-      <c r="S169" s="10"/>
+      <c r="N169" s="11"/>
+      <c r="O169" s="10"/>
+      <c r="P169" s="10"/>
+      <c r="Q169" s="10"/>
+      <c r="R169" s="11"/>
+      <c r="S169" s="13"/>
+      <c r="T169" s="10"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="10"/>
@@ -4454,12 +4625,13 @@
       <c r="K170" s="11"/>
       <c r="L170" s="11"/>
       <c r="M170" s="11"/>
-      <c r="N170" s="13"/>
-      <c r="O170" s="14"/>
-      <c r="P170" s="14"/>
-      <c r="Q170" s="14"/>
-      <c r="R170" s="13"/>
-      <c r="S170" s="10"/>
+      <c r="N170" s="11"/>
+      <c r="O170" s="10"/>
+      <c r="P170" s="10"/>
+      <c r="Q170" s="10"/>
+      <c r="R170" s="11"/>
+      <c r="S170" s="13"/>
+      <c r="T170" s="10"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="10"/>
@@ -4475,12 +4647,13 @@
       <c r="K171" s="11"/>
       <c r="L171" s="11"/>
       <c r="M171" s="11"/>
-      <c r="N171" s="13"/>
-      <c r="O171" s="14"/>
-      <c r="P171" s="14"/>
-      <c r="Q171" s="14"/>
-      <c r="R171" s="13"/>
-      <c r="S171" s="10"/>
+      <c r="N171" s="11"/>
+      <c r="O171" s="10"/>
+      <c r="P171" s="10"/>
+      <c r="Q171" s="10"/>
+      <c r="R171" s="11"/>
+      <c r="S171" s="13"/>
+      <c r="T171" s="10"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="10"/>
@@ -4496,12 +4669,13 @@
       <c r="K172" s="11"/>
       <c r="L172" s="11"/>
       <c r="M172" s="11"/>
-      <c r="N172" s="13"/>
-      <c r="O172" s="14"/>
-      <c r="P172" s="14"/>
-      <c r="Q172" s="14"/>
-      <c r="R172" s="13"/>
-      <c r="S172" s="10"/>
+      <c r="N172" s="11"/>
+      <c r="O172" s="10"/>
+      <c r="P172" s="10"/>
+      <c r="Q172" s="10"/>
+      <c r="R172" s="11"/>
+      <c r="S172" s="13"/>
+      <c r="T172" s="10"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="10"/>
@@ -4517,12 +4691,13 @@
       <c r="K173" s="11"/>
       <c r="L173" s="11"/>
       <c r="M173" s="11"/>
-      <c r="N173" s="13"/>
-      <c r="O173" s="14"/>
-      <c r="P173" s="14"/>
-      <c r="Q173" s="14"/>
-      <c r="R173" s="13"/>
-      <c r="S173" s="10"/>
+      <c r="N173" s="11"/>
+      <c r="O173" s="10"/>
+      <c r="P173" s="10"/>
+      <c r="Q173" s="10"/>
+      <c r="R173" s="11"/>
+      <c r="S173" s="13"/>
+      <c r="T173" s="10"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="10"/>
@@ -4538,12 +4713,13 @@
       <c r="K174" s="11"/>
       <c r="L174" s="11"/>
       <c r="M174" s="11"/>
-      <c r="N174" s="13"/>
-      <c r="O174" s="14"/>
-      <c r="P174" s="14"/>
-      <c r="Q174" s="14"/>
-      <c r="R174" s="13"/>
-      <c r="S174" s="10"/>
+      <c r="N174" s="11"/>
+      <c r="O174" s="10"/>
+      <c r="P174" s="10"/>
+      <c r="Q174" s="10"/>
+      <c r="R174" s="11"/>
+      <c r="S174" s="13"/>
+      <c r="T174" s="10"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="10"/>
@@ -4559,12 +4735,13 @@
       <c r="K175" s="11"/>
       <c r="L175" s="11"/>
       <c r="M175" s="11"/>
-      <c r="N175" s="13"/>
-      <c r="O175" s="14"/>
-      <c r="P175" s="14"/>
-      <c r="Q175" s="14"/>
-      <c r="R175" s="13"/>
-      <c r="S175" s="10"/>
+      <c r="N175" s="11"/>
+      <c r="O175" s="10"/>
+      <c r="P175" s="10"/>
+      <c r="Q175" s="10"/>
+      <c r="R175" s="11"/>
+      <c r="S175" s="13"/>
+      <c r="T175" s="10"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="10"/>
@@ -4580,12 +4757,13 @@
       <c r="K176" s="11"/>
       <c r="L176" s="11"/>
       <c r="M176" s="11"/>
-      <c r="N176" s="13"/>
-      <c r="O176" s="14"/>
-      <c r="P176" s="14"/>
-      <c r="Q176" s="14"/>
-      <c r="R176" s="13"/>
-      <c r="S176" s="10"/>
+      <c r="N176" s="11"/>
+      <c r="O176" s="10"/>
+      <c r="P176" s="10"/>
+      <c r="Q176" s="10"/>
+      <c r="R176" s="11"/>
+      <c r="S176" s="13"/>
+      <c r="T176" s="10"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="10"/>
@@ -4601,12 +4779,13 @@
       <c r="K177" s="11"/>
       <c r="L177" s="11"/>
       <c r="M177" s="11"/>
-      <c r="N177" s="13"/>
-      <c r="O177" s="14"/>
-      <c r="P177" s="14"/>
-      <c r="Q177" s="14"/>
-      <c r="R177" s="13"/>
-      <c r="S177" s="10"/>
+      <c r="N177" s="11"/>
+      <c r="O177" s="10"/>
+      <c r="P177" s="10"/>
+      <c r="Q177" s="10"/>
+      <c r="R177" s="11"/>
+      <c r="S177" s="13"/>
+      <c r="T177" s="10"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="10"/>
@@ -4622,12 +4801,13 @@
       <c r="K178" s="11"/>
       <c r="L178" s="11"/>
       <c r="M178" s="11"/>
-      <c r="N178" s="13"/>
-      <c r="O178" s="14"/>
-      <c r="P178" s="14"/>
-      <c r="Q178" s="14"/>
-      <c r="R178" s="13"/>
-      <c r="S178" s="10"/>
+      <c r="N178" s="11"/>
+      <c r="O178" s="10"/>
+      <c r="P178" s="10"/>
+      <c r="Q178" s="10"/>
+      <c r="R178" s="11"/>
+      <c r="S178" s="13"/>
+      <c r="T178" s="10"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="10"/>
@@ -4643,12 +4823,13 @@
       <c r="K179" s="11"/>
       <c r="L179" s="11"/>
       <c r="M179" s="11"/>
-      <c r="N179" s="13"/>
-      <c r="O179" s="14"/>
-      <c r="P179" s="14"/>
-      <c r="Q179" s="14"/>
-      <c r="R179" s="13"/>
-      <c r="S179" s="10"/>
+      <c r="N179" s="11"/>
+      <c r="O179" s="10"/>
+      <c r="P179" s="10"/>
+      <c r="Q179" s="10"/>
+      <c r="R179" s="11"/>
+      <c r="S179" s="13"/>
+      <c r="T179" s="10"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="10"/>
@@ -4664,12 +4845,13 @@
       <c r="K180" s="11"/>
       <c r="L180" s="11"/>
       <c r="M180" s="11"/>
-      <c r="N180" s="13"/>
-      <c r="O180" s="14"/>
-      <c r="P180" s="14"/>
-      <c r="Q180" s="14"/>
-      <c r="R180" s="13"/>
-      <c r="S180" s="10"/>
+      <c r="N180" s="11"/>
+      <c r="O180" s="10"/>
+      <c r="P180" s="10"/>
+      <c r="Q180" s="10"/>
+      <c r="R180" s="11"/>
+      <c r="S180" s="13"/>
+      <c r="T180" s="10"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="10"/>
@@ -4685,12 +4867,13 @@
       <c r="K181" s="11"/>
       <c r="L181" s="11"/>
       <c r="M181" s="11"/>
-      <c r="N181" s="13"/>
-      <c r="O181" s="14"/>
-      <c r="P181" s="14"/>
-      <c r="Q181" s="14"/>
-      <c r="R181" s="13"/>
-      <c r="S181" s="10"/>
+      <c r="N181" s="11"/>
+      <c r="O181" s="10"/>
+      <c r="P181" s="10"/>
+      <c r="Q181" s="10"/>
+      <c r="R181" s="11"/>
+      <c r="S181" s="13"/>
+      <c r="T181" s="10"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="10"/>
@@ -4706,12 +4889,13 @@
       <c r="K182" s="11"/>
       <c r="L182" s="11"/>
       <c r="M182" s="11"/>
-      <c r="N182" s="13"/>
-      <c r="O182" s="14"/>
-      <c r="P182" s="14"/>
-      <c r="Q182" s="14"/>
-      <c r="R182" s="13"/>
-      <c r="S182" s="10"/>
+      <c r="N182" s="11"/>
+      <c r="O182" s="10"/>
+      <c r="P182" s="10"/>
+      <c r="Q182" s="10"/>
+      <c r="R182" s="11"/>
+      <c r="S182" s="13"/>
+      <c r="T182" s="10"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="10"/>
@@ -4727,12 +4911,13 @@
       <c r="K183" s="11"/>
       <c r="L183" s="11"/>
       <c r="M183" s="11"/>
-      <c r="N183" s="13"/>
-      <c r="O183" s="14"/>
-      <c r="P183" s="14"/>
-      <c r="Q183" s="14"/>
-      <c r="R183" s="13"/>
-      <c r="S183" s="10"/>
+      <c r="N183" s="11"/>
+      <c r="O183" s="10"/>
+      <c r="P183" s="10"/>
+      <c r="Q183" s="10"/>
+      <c r="R183" s="11"/>
+      <c r="S183" s="13"/>
+      <c r="T183" s="10"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="10"/>
@@ -4748,12 +4933,13 @@
       <c r="K184" s="11"/>
       <c r="L184" s="11"/>
       <c r="M184" s="11"/>
-      <c r="N184" s="13"/>
-      <c r="O184" s="14"/>
-      <c r="P184" s="14"/>
-      <c r="Q184" s="14"/>
-      <c r="R184" s="13"/>
-      <c r="S184" s="10"/>
+      <c r="N184" s="11"/>
+      <c r="O184" s="10"/>
+      <c r="P184" s="10"/>
+      <c r="Q184" s="10"/>
+      <c r="R184" s="11"/>
+      <c r="S184" s="13"/>
+      <c r="T184" s="10"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="10"/>
@@ -4769,12 +4955,13 @@
       <c r="K185" s="11"/>
       <c r="L185" s="11"/>
       <c r="M185" s="11"/>
-      <c r="N185" s="13"/>
-      <c r="O185" s="14"/>
-      <c r="P185" s="14"/>
-      <c r="Q185" s="14"/>
-      <c r="R185" s="13"/>
-      <c r="S185" s="10"/>
+      <c r="N185" s="11"/>
+      <c r="O185" s="10"/>
+      <c r="P185" s="10"/>
+      <c r="Q185" s="10"/>
+      <c r="R185" s="11"/>
+      <c r="S185" s="13"/>
+      <c r="T185" s="10"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="10"/>
@@ -4790,12 +4977,13 @@
       <c r="K186" s="11"/>
       <c r="L186" s="11"/>
       <c r="M186" s="11"/>
-      <c r="N186" s="13"/>
-      <c r="O186" s="14"/>
-      <c r="P186" s="14"/>
-      <c r="Q186" s="14"/>
-      <c r="R186" s="13"/>
-      <c r="S186" s="10"/>
+      <c r="N186" s="11"/>
+      <c r="O186" s="10"/>
+      <c r="P186" s="10"/>
+      <c r="Q186" s="10"/>
+      <c r="R186" s="11"/>
+      <c r="S186" s="13"/>
+      <c r="T186" s="10"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="10"/>
@@ -4811,12 +4999,13 @@
       <c r="K187" s="11"/>
       <c r="L187" s="11"/>
       <c r="M187" s="11"/>
-      <c r="N187" s="13"/>
-      <c r="O187" s="14"/>
-      <c r="P187" s="14"/>
-      <c r="Q187" s="14"/>
-      <c r="R187" s="13"/>
-      <c r="S187" s="10"/>
+      <c r="N187" s="11"/>
+      <c r="O187" s="10"/>
+      <c r="P187" s="10"/>
+      <c r="Q187" s="10"/>
+      <c r="R187" s="11"/>
+      <c r="S187" s="13"/>
+      <c r="T187" s="10"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="10"/>
@@ -4832,12 +5021,13 @@
       <c r="K188" s="11"/>
       <c r="L188" s="11"/>
       <c r="M188" s="11"/>
-      <c r="N188" s="13"/>
-      <c r="O188" s="14"/>
-      <c r="P188" s="14"/>
-      <c r="Q188" s="14"/>
-      <c r="R188" s="13"/>
-      <c r="S188" s="10"/>
+      <c r="N188" s="11"/>
+      <c r="O188" s="10"/>
+      <c r="P188" s="10"/>
+      <c r="Q188" s="10"/>
+      <c r="R188" s="11"/>
+      <c r="S188" s="13"/>
+      <c r="T188" s="10"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="10"/>
@@ -4853,12 +5043,13 @@
       <c r="K189" s="11"/>
       <c r="L189" s="11"/>
       <c r="M189" s="11"/>
-      <c r="N189" s="13"/>
-      <c r="O189" s="14"/>
-      <c r="P189" s="14"/>
-      <c r="Q189" s="14"/>
-      <c r="R189" s="13"/>
-      <c r="S189" s="10"/>
+      <c r="N189" s="11"/>
+      <c r="O189" s="10"/>
+      <c r="P189" s="10"/>
+      <c r="Q189" s="10"/>
+      <c r="R189" s="11"/>
+      <c r="S189" s="13"/>
+      <c r="T189" s="10"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="10"/>
@@ -4874,12 +5065,13 @@
       <c r="K190" s="11"/>
       <c r="L190" s="11"/>
       <c r="M190" s="11"/>
-      <c r="N190" s="13"/>
-      <c r="O190" s="14"/>
-      <c r="P190" s="14"/>
-      <c r="Q190" s="14"/>
-      <c r="R190" s="13"/>
-      <c r="S190" s="10"/>
+      <c r="N190" s="11"/>
+      <c r="O190" s="10"/>
+      <c r="P190" s="10"/>
+      <c r="Q190" s="10"/>
+      <c r="R190" s="11"/>
+      <c r="S190" s="13"/>
+      <c r="T190" s="10"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="10"/>
@@ -4895,12 +5087,13 @@
       <c r="K191" s="11"/>
       <c r="L191" s="11"/>
       <c r="M191" s="11"/>
-      <c r="N191" s="13"/>
-      <c r="O191" s="14"/>
-      <c r="P191" s="14"/>
-      <c r="Q191" s="14"/>
-      <c r="R191" s="13"/>
-      <c r="S191" s="10"/>
+      <c r="N191" s="11"/>
+      <c r="O191" s="10"/>
+      <c r="P191" s="10"/>
+      <c r="Q191" s="10"/>
+      <c r="R191" s="11"/>
+      <c r="S191" s="13"/>
+      <c r="T191" s="10"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="10"/>
@@ -4916,12 +5109,13 @@
       <c r="K192" s="11"/>
       <c r="L192" s="11"/>
       <c r="M192" s="11"/>
-      <c r="N192" s="13"/>
-      <c r="O192" s="14"/>
-      <c r="P192" s="14"/>
-      <c r="Q192" s="14"/>
-      <c r="R192" s="13"/>
-      <c r="S192" s="10"/>
+      <c r="N192" s="11"/>
+      <c r="O192" s="10"/>
+      <c r="P192" s="10"/>
+      <c r="Q192" s="10"/>
+      <c r="R192" s="11"/>
+      <c r="S192" s="13"/>
+      <c r="T192" s="10"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="10"/>
@@ -4937,12 +5131,13 @@
       <c r="K193" s="11"/>
       <c r="L193" s="11"/>
       <c r="M193" s="11"/>
-      <c r="N193" s="13"/>
-      <c r="O193" s="14"/>
-      <c r="P193" s="14"/>
-      <c r="Q193" s="14"/>
-      <c r="R193" s="13"/>
-      <c r="S193" s="10"/>
+      <c r="N193" s="11"/>
+      <c r="O193" s="10"/>
+      <c r="P193" s="10"/>
+      <c r="Q193" s="10"/>
+      <c r="R193" s="11"/>
+      <c r="S193" s="13"/>
+      <c r="T193" s="10"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="10"/>
@@ -4958,12 +5153,13 @@
       <c r="K194" s="11"/>
       <c r="L194" s="11"/>
       <c r="M194" s="11"/>
-      <c r="N194" s="13"/>
-      <c r="O194" s="14"/>
-      <c r="P194" s="14"/>
-      <c r="Q194" s="14"/>
-      <c r="R194" s="13"/>
-      <c r="S194" s="10"/>
+      <c r="N194" s="11"/>
+      <c r="O194" s="10"/>
+      <c r="P194" s="10"/>
+      <c r="Q194" s="10"/>
+      <c r="R194" s="11"/>
+      <c r="S194" s="13"/>
+      <c r="T194" s="10"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="10"/>
@@ -4979,12 +5175,13 @@
       <c r="K195" s="11"/>
       <c r="L195" s="11"/>
       <c r="M195" s="11"/>
-      <c r="N195" s="13"/>
-      <c r="O195" s="14"/>
-      <c r="P195" s="14"/>
-      <c r="Q195" s="14"/>
-      <c r="R195" s="13"/>
-      <c r="S195" s="10"/>
+      <c r="N195" s="11"/>
+      <c r="O195" s="10"/>
+      <c r="P195" s="10"/>
+      <c r="Q195" s="10"/>
+      <c r="R195" s="11"/>
+      <c r="S195" s="13"/>
+      <c r="T195" s="10"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="10"/>
@@ -5000,12 +5197,13 @@
       <c r="K196" s="11"/>
       <c r="L196" s="11"/>
       <c r="M196" s="11"/>
-      <c r="N196" s="13"/>
-      <c r="O196" s="14"/>
-      <c r="P196" s="14"/>
-      <c r="Q196" s="14"/>
-      <c r="R196" s="13"/>
-      <c r="S196" s="10"/>
+      <c r="N196" s="11"/>
+      <c r="O196" s="10"/>
+      <c r="P196" s="10"/>
+      <c r="Q196" s="10"/>
+      <c r="R196" s="11"/>
+      <c r="S196" s="13"/>
+      <c r="T196" s="10"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="10"/>
@@ -5021,12 +5219,13 @@
       <c r="K197" s="11"/>
       <c r="L197" s="11"/>
       <c r="M197" s="11"/>
-      <c r="N197" s="13"/>
-      <c r="O197" s="14"/>
-      <c r="P197" s="14"/>
-      <c r="Q197" s="14"/>
-      <c r="R197" s="13"/>
-      <c r="S197" s="10"/>
+      <c r="N197" s="11"/>
+      <c r="O197" s="10"/>
+      <c r="P197" s="10"/>
+      <c r="Q197" s="10"/>
+      <c r="R197" s="11"/>
+      <c r="S197" s="13"/>
+      <c r="T197" s="10"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="10"/>
@@ -5042,12 +5241,13 @@
       <c r="K198" s="11"/>
       <c r="L198" s="11"/>
       <c r="M198" s="11"/>
-      <c r="N198" s="13"/>
-      <c r="O198" s="14"/>
-      <c r="P198" s="14"/>
-      <c r="Q198" s="14"/>
-      <c r="R198" s="13"/>
-      <c r="S198" s="10"/>
+      <c r="N198" s="11"/>
+      <c r="O198" s="10"/>
+      <c r="P198" s="10"/>
+      <c r="Q198" s="10"/>
+      <c r="R198" s="11"/>
+      <c r="S198" s="13"/>
+      <c r="T198" s="10"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="10"/>
@@ -5063,12 +5263,13 @@
       <c r="K199" s="11"/>
       <c r="L199" s="11"/>
       <c r="M199" s="11"/>
-      <c r="N199" s="13"/>
-      <c r="O199" s="14"/>
-      <c r="P199" s="14"/>
-      <c r="Q199" s="14"/>
-      <c r="R199" s="13"/>
-      <c r="S199" s="10"/>
+      <c r="N199" s="11"/>
+      <c r="O199" s="10"/>
+      <c r="P199" s="10"/>
+      <c r="Q199" s="10"/>
+      <c r="R199" s="11"/>
+      <c r="S199" s="13"/>
+      <c r="T199" s="10"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="10"/>
@@ -5084,12 +5285,13 @@
       <c r="K200" s="11"/>
       <c r="L200" s="11"/>
       <c r="M200" s="11"/>
-      <c r="N200" s="13"/>
-      <c r="O200" s="14"/>
-      <c r="P200" s="14"/>
-      <c r="Q200" s="14"/>
-      <c r="R200" s="13"/>
-      <c r="S200" s="10"/>
+      <c r="N200" s="11"/>
+      <c r="O200" s="10"/>
+      <c r="P200" s="10"/>
+      <c r="Q200" s="10"/>
+      <c r="R200" s="11"/>
+      <c r="S200" s="13"/>
+      <c r="T200" s="10"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="10"/>
@@ -5105,12 +5307,13 @@
       <c r="K201" s="11"/>
       <c r="L201" s="11"/>
       <c r="M201" s="11"/>
-      <c r="N201" s="13"/>
-      <c r="O201" s="14"/>
-      <c r="P201" s="14"/>
-      <c r="Q201" s="14"/>
-      <c r="R201" s="13"/>
-      <c r="S201" s="10"/>
+      <c r="N201" s="11"/>
+      <c r="O201" s="10"/>
+      <c r="P201" s="10"/>
+      <c r="Q201" s="10"/>
+      <c r="R201" s="11"/>
+      <c r="S201" s="13"/>
+      <c r="T201" s="10"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="10"/>
@@ -5126,12 +5329,13 @@
       <c r="K202" s="11"/>
       <c r="L202" s="11"/>
       <c r="M202" s="11"/>
-      <c r="N202" s="13"/>
-      <c r="O202" s="14"/>
-      <c r="P202" s="14"/>
-      <c r="Q202" s="14"/>
-      <c r="R202" s="13"/>
-      <c r="S202" s="10"/>
+      <c r="N202" s="11"/>
+      <c r="O202" s="10"/>
+      <c r="P202" s="10"/>
+      <c r="Q202" s="10"/>
+      <c r="R202" s="11"/>
+      <c r="S202" s="13"/>
+      <c r="T202" s="10"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="10"/>
@@ -5147,12 +5351,13 @@
       <c r="K203" s="11"/>
       <c r="L203" s="11"/>
       <c r="M203" s="11"/>
-      <c r="N203" s="13"/>
-      <c r="O203" s="14"/>
-      <c r="P203" s="14"/>
-      <c r="Q203" s="14"/>
-      <c r="R203" s="13"/>
-      <c r="S203" s="10"/>
+      <c r="N203" s="11"/>
+      <c r="O203" s="10"/>
+      <c r="P203" s="10"/>
+      <c r="Q203" s="10"/>
+      <c r="R203" s="11"/>
+      <c r="S203" s="13"/>
+      <c r="T203" s="10"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="10"/>
@@ -5168,12 +5373,13 @@
       <c r="K204" s="11"/>
       <c r="L204" s="11"/>
       <c r="M204" s="11"/>
-      <c r="N204" s="13"/>
-      <c r="O204" s="14"/>
-      <c r="P204" s="14"/>
-      <c r="Q204" s="14"/>
-      <c r="R204" s="13"/>
-      <c r="S204" s="10"/>
+      <c r="N204" s="11"/>
+      <c r="O204" s="10"/>
+      <c r="P204" s="10"/>
+      <c r="Q204" s="10"/>
+      <c r="R204" s="11"/>
+      <c r="S204" s="13"/>
+      <c r="T204" s="10"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="10"/>
@@ -5189,12 +5395,13 @@
       <c r="K205" s="11"/>
       <c r="L205" s="11"/>
       <c r="M205" s="11"/>
-      <c r="N205" s="13"/>
-      <c r="O205" s="14"/>
-      <c r="P205" s="14"/>
-      <c r="Q205" s="14"/>
-      <c r="R205" s="13"/>
-      <c r="S205" s="10"/>
+      <c r="N205" s="11"/>
+      <c r="O205" s="10"/>
+      <c r="P205" s="10"/>
+      <c r="Q205" s="10"/>
+      <c r="R205" s="11"/>
+      <c r="S205" s="13"/>
+      <c r="T205" s="10"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="10"/>
@@ -5210,12 +5417,13 @@
       <c r="K206" s="11"/>
       <c r="L206" s="11"/>
       <c r="M206" s="11"/>
-      <c r="N206" s="13"/>
-      <c r="O206" s="14"/>
-      <c r="P206" s="14"/>
-      <c r="Q206" s="14"/>
-      <c r="R206" s="13"/>
-      <c r="S206" s="10"/>
+      <c r="N206" s="11"/>
+      <c r="O206" s="10"/>
+      <c r="P206" s="10"/>
+      <c r="Q206" s="10"/>
+      <c r="R206" s="11"/>
+      <c r="S206" s="13"/>
+      <c r="T206" s="10"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="10"/>
@@ -5231,12 +5439,13 @@
       <c r="K207" s="11"/>
       <c r="L207" s="11"/>
       <c r="M207" s="11"/>
-      <c r="N207" s="13"/>
-      <c r="O207" s="14"/>
-      <c r="P207" s="14"/>
-      <c r="Q207" s="14"/>
-      <c r="R207" s="13"/>
-      <c r="S207" s="10"/>
+      <c r="N207" s="11"/>
+      <c r="O207" s="10"/>
+      <c r="P207" s="10"/>
+      <c r="Q207" s="10"/>
+      <c r="R207" s="11"/>
+      <c r="S207" s="13"/>
+      <c r="T207" s="10"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="10"/>
@@ -5252,12 +5461,13 @@
       <c r="K208" s="11"/>
       <c r="L208" s="11"/>
       <c r="M208" s="11"/>
-      <c r="N208" s="13"/>
-      <c r="O208" s="14"/>
-      <c r="P208" s="14"/>
-      <c r="Q208" s="14"/>
-      <c r="R208" s="13"/>
-      <c r="S208" s="10"/>
+      <c r="N208" s="11"/>
+      <c r="O208" s="10"/>
+      <c r="P208" s="10"/>
+      <c r="Q208" s="10"/>
+      <c r="R208" s="11"/>
+      <c r="S208" s="13"/>
+      <c r="T208" s="10"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="10"/>
@@ -5273,12 +5483,13 @@
       <c r="K209" s="11"/>
       <c r="L209" s="11"/>
       <c r="M209" s="11"/>
-      <c r="N209" s="13"/>
-      <c r="O209" s="14"/>
-      <c r="P209" s="14"/>
-      <c r="Q209" s="14"/>
-      <c r="R209" s="13"/>
-      <c r="S209" s="10"/>
+      <c r="N209" s="11"/>
+      <c r="O209" s="10"/>
+      <c r="P209" s="10"/>
+      <c r="Q209" s="10"/>
+      <c r="R209" s="11"/>
+      <c r="S209" s="13"/>
+      <c r="T209" s="10"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="10"/>
@@ -5294,12 +5505,13 @@
       <c r="K210" s="11"/>
       <c r="L210" s="11"/>
       <c r="M210" s="11"/>
-      <c r="N210" s="13"/>
-      <c r="O210" s="14"/>
-      <c r="P210" s="14"/>
-      <c r="Q210" s="14"/>
-      <c r="R210" s="13"/>
-      <c r="S210" s="10"/>
+      <c r="N210" s="11"/>
+      <c r="O210" s="10"/>
+      <c r="P210" s="10"/>
+      <c r="Q210" s="10"/>
+      <c r="R210" s="11"/>
+      <c r="S210" s="13"/>
+      <c r="T210" s="10"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="10"/>
@@ -5315,12 +5527,13 @@
       <c r="K211" s="11"/>
       <c r="L211" s="11"/>
       <c r="M211" s="11"/>
-      <c r="N211" s="13"/>
-      <c r="O211" s="14"/>
-      <c r="P211" s="14"/>
-      <c r="Q211" s="14"/>
-      <c r="R211" s="13"/>
-      <c r="S211" s="10"/>
+      <c r="N211" s="11"/>
+      <c r="O211" s="10"/>
+      <c r="P211" s="10"/>
+      <c r="Q211" s="10"/>
+      <c r="R211" s="11"/>
+      <c r="S211" s="13"/>
+      <c r="T211" s="10"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="10"/>
@@ -5336,12 +5549,13 @@
       <c r="K212" s="11"/>
       <c r="L212" s="11"/>
       <c r="M212" s="11"/>
-      <c r="N212" s="13"/>
-      <c r="O212" s="14"/>
-      <c r="P212" s="14"/>
-      <c r="Q212" s="14"/>
-      <c r="R212" s="13"/>
-      <c r="S212" s="10"/>
+      <c r="N212" s="11"/>
+      <c r="O212" s="10"/>
+      <c r="P212" s="10"/>
+      <c r="Q212" s="10"/>
+      <c r="R212" s="11"/>
+      <c r="S212" s="13"/>
+      <c r="T212" s="10"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="10"/>
@@ -5357,12 +5571,13 @@
       <c r="K213" s="11"/>
       <c r="L213" s="11"/>
       <c r="M213" s="11"/>
-      <c r="N213" s="13"/>
-      <c r="O213" s="14"/>
-      <c r="P213" s="14"/>
-      <c r="Q213" s="14"/>
-      <c r="R213" s="13"/>
-      <c r="S213" s="10"/>
+      <c r="N213" s="11"/>
+      <c r="O213" s="10"/>
+      <c r="P213" s="10"/>
+      <c r="Q213" s="10"/>
+      <c r="R213" s="11"/>
+      <c r="S213" s="13"/>
+      <c r="T213" s="10"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="10"/>
@@ -5378,12 +5593,13 @@
       <c r="K214" s="11"/>
       <c r="L214" s="11"/>
       <c r="M214" s="11"/>
-      <c r="N214" s="13"/>
-      <c r="O214" s="14"/>
-      <c r="P214" s="14"/>
-      <c r="Q214" s="14"/>
-      <c r="R214" s="13"/>
-      <c r="S214" s="10"/>
+      <c r="N214" s="11"/>
+      <c r="O214" s="10"/>
+      <c r="P214" s="10"/>
+      <c r="Q214" s="10"/>
+      <c r="R214" s="11"/>
+      <c r="S214" s="13"/>
+      <c r="T214" s="10"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="10"/>
@@ -5399,12 +5615,13 @@
       <c r="K215" s="11"/>
       <c r="L215" s="11"/>
       <c r="M215" s="11"/>
-      <c r="N215" s="13"/>
-      <c r="O215" s="14"/>
-      <c r="P215" s="14"/>
-      <c r="Q215" s="14"/>
-      <c r="R215" s="13"/>
-      <c r="S215" s="10"/>
+      <c r="N215" s="11"/>
+      <c r="O215" s="10"/>
+      <c r="P215" s="10"/>
+      <c r="Q215" s="10"/>
+      <c r="R215" s="11"/>
+      <c r="S215" s="13"/>
+      <c r="T215" s="10"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="10"/>
@@ -5420,12 +5637,13 @@
       <c r="K216" s="11"/>
       <c r="L216" s="11"/>
       <c r="M216" s="11"/>
-      <c r="N216" s="13"/>
-      <c r="O216" s="14"/>
-      <c r="P216" s="14"/>
-      <c r="Q216" s="14"/>
-      <c r="R216" s="13"/>
-      <c r="S216" s="10"/>
+      <c r="N216" s="11"/>
+      <c r="O216" s="10"/>
+      <c r="P216" s="10"/>
+      <c r="Q216" s="10"/>
+      <c r="R216" s="11"/>
+      <c r="S216" s="13"/>
+      <c r="T216" s="10"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="10"/>
@@ -5441,12 +5659,13 @@
       <c r="K217" s="11"/>
       <c r="L217" s="11"/>
       <c r="M217" s="11"/>
-      <c r="N217" s="13"/>
-      <c r="O217" s="14"/>
-      <c r="P217" s="14"/>
-      <c r="Q217" s="14"/>
-      <c r="R217" s="13"/>
-      <c r="S217" s="10"/>
+      <c r="N217" s="11"/>
+      <c r="O217" s="10"/>
+      <c r="P217" s="10"/>
+      <c r="Q217" s="10"/>
+      <c r="R217" s="11"/>
+      <c r="S217" s="13"/>
+      <c r="T217" s="10"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="10"/>
@@ -5462,12 +5681,13 @@
       <c r="K218" s="11"/>
       <c r="L218" s="11"/>
       <c r="M218" s="11"/>
-      <c r="N218" s="13"/>
-      <c r="O218" s="14"/>
-      <c r="P218" s="14"/>
-      <c r="Q218" s="14"/>
-      <c r="R218" s="13"/>
-      <c r="S218" s="10"/>
+      <c r="N218" s="11"/>
+      <c r="O218" s="10"/>
+      <c r="P218" s="10"/>
+      <c r="Q218" s="10"/>
+      <c r="R218" s="11"/>
+      <c r="S218" s="13"/>
+      <c r="T218" s="10"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="10"/>
@@ -5483,12 +5703,13 @@
       <c r="K219" s="11"/>
       <c r="L219" s="11"/>
       <c r="M219" s="11"/>
-      <c r="N219" s="13"/>
-      <c r="O219" s="14"/>
-      <c r="P219" s="14"/>
-      <c r="Q219" s="14"/>
-      <c r="R219" s="13"/>
-      <c r="S219" s="10"/>
+      <c r="N219" s="11"/>
+      <c r="O219" s="10"/>
+      <c r="P219" s="10"/>
+      <c r="Q219" s="10"/>
+      <c r="R219" s="11"/>
+      <c r="S219" s="13"/>
+      <c r="T219" s="10"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="10"/>
@@ -5504,12 +5725,13 @@
       <c r="K220" s="11"/>
       <c r="L220" s="11"/>
       <c r="M220" s="11"/>
-      <c r="N220" s="13"/>
-      <c r="O220" s="14"/>
-      <c r="P220" s="14"/>
-      <c r="Q220" s="14"/>
-      <c r="R220" s="13"/>
-      <c r="S220" s="10"/>
+      <c r="N220" s="11"/>
+      <c r="O220" s="10"/>
+      <c r="P220" s="10"/>
+      <c r="Q220" s="10"/>
+      <c r="R220" s="11"/>
+      <c r="S220" s="13"/>
+      <c r="T220" s="10"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="10"/>
@@ -5525,12 +5747,13 @@
       <c r="K221" s="11"/>
       <c r="L221" s="11"/>
       <c r="M221" s="11"/>
-      <c r="N221" s="13"/>
-      <c r="O221" s="14"/>
-      <c r="P221" s="14"/>
-      <c r="Q221" s="14"/>
-      <c r="R221" s="13"/>
-      <c r="S221" s="10"/>
+      <c r="N221" s="11"/>
+      <c r="O221" s="10"/>
+      <c r="P221" s="10"/>
+      <c r="Q221" s="10"/>
+      <c r="R221" s="11"/>
+      <c r="S221" s="13"/>
+      <c r="T221" s="10"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="10"/>
@@ -5546,12 +5769,13 @@
       <c r="K222" s="11"/>
       <c r="L222" s="11"/>
       <c r="M222" s="11"/>
-      <c r="N222" s="13"/>
-      <c r="O222" s="14"/>
-      <c r="P222" s="14"/>
-      <c r="Q222" s="14"/>
-      <c r="R222" s="13"/>
-      <c r="S222" s="10"/>
+      <c r="N222" s="11"/>
+      <c r="O222" s="10"/>
+      <c r="P222" s="10"/>
+      <c r="Q222" s="10"/>
+      <c r="R222" s="11"/>
+      <c r="S222" s="13"/>
+      <c r="T222" s="10"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="10"/>
@@ -5567,12 +5791,13 @@
       <c r="K223" s="11"/>
       <c r="L223" s="11"/>
       <c r="M223" s="11"/>
-      <c r="N223" s="13"/>
-      <c r="O223" s="14"/>
-      <c r="P223" s="14"/>
-      <c r="Q223" s="14"/>
-      <c r="R223" s="13"/>
-      <c r="S223" s="10"/>
+      <c r="N223" s="11"/>
+      <c r="O223" s="10"/>
+      <c r="P223" s="10"/>
+      <c r="Q223" s="10"/>
+      <c r="R223" s="11"/>
+      <c r="S223" s="13"/>
+      <c r="T223" s="10"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="10"/>
@@ -5588,12 +5813,13 @@
       <c r="K224" s="11"/>
       <c r="L224" s="11"/>
       <c r="M224" s="11"/>
-      <c r="N224" s="13"/>
-      <c r="O224" s="14"/>
-      <c r="P224" s="14"/>
-      <c r="Q224" s="14"/>
-      <c r="R224" s="13"/>
-      <c r="S224" s="10"/>
+      <c r="N224" s="11"/>
+      <c r="O224" s="10"/>
+      <c r="P224" s="10"/>
+      <c r="Q224" s="10"/>
+      <c r="R224" s="11"/>
+      <c r="S224" s="13"/>
+      <c r="T224" s="10"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="10"/>
@@ -5609,12 +5835,13 @@
       <c r="K225" s="11"/>
       <c r="L225" s="11"/>
       <c r="M225" s="11"/>
-      <c r="N225" s="13"/>
-      <c r="O225" s="14"/>
-      <c r="P225" s="14"/>
-      <c r="Q225" s="14"/>
-      <c r="R225" s="13"/>
-      <c r="S225" s="10"/>
+      <c r="N225" s="11"/>
+      <c r="O225" s="10"/>
+      <c r="P225" s="10"/>
+      <c r="Q225" s="10"/>
+      <c r="R225" s="11"/>
+      <c r="S225" s="13"/>
+      <c r="T225" s="10"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="10"/>
@@ -5630,12 +5857,13 @@
       <c r="K226" s="11"/>
       <c r="L226" s="11"/>
       <c r="M226" s="11"/>
-      <c r="N226" s="13"/>
-      <c r="O226" s="14"/>
-      <c r="P226" s="14"/>
-      <c r="Q226" s="14"/>
-      <c r="R226" s="13"/>
-      <c r="S226" s="10"/>
+      <c r="N226" s="11"/>
+      <c r="O226" s="10"/>
+      <c r="P226" s="10"/>
+      <c r="Q226" s="10"/>
+      <c r="R226" s="11"/>
+      <c r="S226" s="13"/>
+      <c r="T226" s="10"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="10"/>
@@ -5651,12 +5879,13 @@
       <c r="K227" s="11"/>
       <c r="L227" s="11"/>
       <c r="M227" s="11"/>
-      <c r="N227" s="13"/>
-      <c r="O227" s="14"/>
-      <c r="P227" s="14"/>
-      <c r="Q227" s="14"/>
-      <c r="R227" s="13"/>
-      <c r="S227" s="10"/>
+      <c r="N227" s="11"/>
+      <c r="O227" s="10"/>
+      <c r="P227" s="10"/>
+      <c r="Q227" s="10"/>
+      <c r="R227" s="11"/>
+      <c r="S227" s="13"/>
+      <c r="T227" s="10"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="10"/>
@@ -5672,12 +5901,13 @@
       <c r="K228" s="11"/>
       <c r="L228" s="11"/>
       <c r="M228" s="11"/>
-      <c r="N228" s="13"/>
-      <c r="O228" s="14"/>
-      <c r="P228" s="14"/>
-      <c r="Q228" s="14"/>
-      <c r="R228" s="13"/>
-      <c r="S228" s="10"/>
+      <c r="N228" s="11"/>
+      <c r="O228" s="10"/>
+      <c r="P228" s="10"/>
+      <c r="Q228" s="10"/>
+      <c r="R228" s="11"/>
+      <c r="S228" s="13"/>
+      <c r="T228" s="10"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="10"/>
@@ -5693,12 +5923,13 @@
       <c r="K229" s="11"/>
       <c r="L229" s="11"/>
       <c r="M229" s="11"/>
-      <c r="N229" s="13"/>
-      <c r="O229" s="14"/>
-      <c r="P229" s="14"/>
-      <c r="Q229" s="14"/>
-      <c r="R229" s="13"/>
-      <c r="S229" s="10"/>
+      <c r="N229" s="11"/>
+      <c r="O229" s="10"/>
+      <c r="P229" s="10"/>
+      <c r="Q229" s="10"/>
+      <c r="R229" s="11"/>
+      <c r="S229" s="13"/>
+      <c r="T229" s="10"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="10"/>
@@ -5714,12 +5945,13 @@
       <c r="K230" s="11"/>
       <c r="L230" s="11"/>
       <c r="M230" s="11"/>
-      <c r="N230" s="13"/>
-      <c r="O230" s="14"/>
-      <c r="P230" s="14"/>
-      <c r="Q230" s="14"/>
-      <c r="R230" s="13"/>
-      <c r="S230" s="10"/>
+      <c r="N230" s="11"/>
+      <c r="O230" s="10"/>
+      <c r="P230" s="10"/>
+      <c r="Q230" s="10"/>
+      <c r="R230" s="11"/>
+      <c r="S230" s="13"/>
+      <c r="T230" s="10"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="10"/>
@@ -5735,12 +5967,13 @@
       <c r="K231" s="11"/>
       <c r="L231" s="11"/>
       <c r="M231" s="11"/>
-      <c r="N231" s="13"/>
-      <c r="O231" s="14"/>
-      <c r="P231" s="14"/>
-      <c r="Q231" s="14"/>
-      <c r="R231" s="13"/>
-      <c r="S231" s="10"/>
+      <c r="N231" s="11"/>
+      <c r="O231" s="10"/>
+      <c r="P231" s="10"/>
+      <c r="Q231" s="10"/>
+      <c r="R231" s="11"/>
+      <c r="S231" s="13"/>
+      <c r="T231" s="10"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="10"/>
@@ -5756,12 +5989,13 @@
       <c r="K232" s="11"/>
       <c r="L232" s="11"/>
       <c r="M232" s="11"/>
-      <c r="N232" s="13"/>
-      <c r="O232" s="14"/>
-      <c r="P232" s="14"/>
-      <c r="Q232" s="14"/>
-      <c r="R232" s="13"/>
-      <c r="S232" s="10"/>
+      <c r="N232" s="11"/>
+      <c r="O232" s="10"/>
+      <c r="P232" s="10"/>
+      <c r="Q232" s="10"/>
+      <c r="R232" s="11"/>
+      <c r="S232" s="13"/>
+      <c r="T232" s="10"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="10"/>
@@ -5777,12 +6011,13 @@
       <c r="K233" s="11"/>
       <c r="L233" s="11"/>
       <c r="M233" s="11"/>
-      <c r="N233" s="13"/>
-      <c r="O233" s="14"/>
-      <c r="P233" s="14"/>
-      <c r="Q233" s="14"/>
-      <c r="R233" s="13"/>
-      <c r="S233" s="10"/>
+      <c r="N233" s="11"/>
+      <c r="O233" s="10"/>
+      <c r="P233" s="10"/>
+      <c r="Q233" s="10"/>
+      <c r="R233" s="11"/>
+      <c r="S233" s="13"/>
+      <c r="T233" s="10"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="10"/>
@@ -5798,12 +6033,13 @@
       <c r="K234" s="11"/>
       <c r="L234" s="11"/>
       <c r="M234" s="11"/>
-      <c r="N234" s="13"/>
-      <c r="O234" s="14"/>
-      <c r="P234" s="14"/>
-      <c r="Q234" s="14"/>
-      <c r="R234" s="13"/>
-      <c r="S234" s="10"/>
+      <c r="N234" s="11"/>
+      <c r="O234" s="10"/>
+      <c r="P234" s="10"/>
+      <c r="Q234" s="10"/>
+      <c r="R234" s="11"/>
+      <c r="S234" s="13"/>
+      <c r="T234" s="10"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="10"/>
@@ -5819,12 +6055,13 @@
       <c r="K235" s="11"/>
       <c r="L235" s="11"/>
       <c r="M235" s="11"/>
-      <c r="N235" s="13"/>
-      <c r="O235" s="14"/>
-      <c r="P235" s="14"/>
-      <c r="Q235" s="14"/>
-      <c r="R235" s="13"/>
-      <c r="S235" s="10"/>
+      <c r="N235" s="11"/>
+      <c r="O235" s="10"/>
+      <c r="P235" s="10"/>
+      <c r="Q235" s="10"/>
+      <c r="R235" s="11"/>
+      <c r="S235" s="13"/>
+      <c r="T235" s="10"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="10"/>
@@ -5840,12 +6077,13 @@
       <c r="K236" s="11"/>
       <c r="L236" s="11"/>
       <c r="M236" s="11"/>
-      <c r="N236" s="13"/>
-      <c r="O236" s="14"/>
-      <c r="P236" s="14"/>
-      <c r="Q236" s="14"/>
-      <c r="R236" s="13"/>
-      <c r="S236" s="10"/>
+      <c r="N236" s="11"/>
+      <c r="O236" s="10"/>
+      <c r="P236" s="10"/>
+      <c r="Q236" s="10"/>
+      <c r="R236" s="11"/>
+      <c r="S236" s="13"/>
+      <c r="T236" s="10"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="10"/>
@@ -5861,12 +6099,13 @@
       <c r="K237" s="11"/>
       <c r="L237" s="11"/>
       <c r="M237" s="11"/>
-      <c r="N237" s="13"/>
-      <c r="O237" s="14"/>
-      <c r="P237" s="14"/>
-      <c r="Q237" s="14"/>
-      <c r="R237" s="13"/>
-      <c r="S237" s="10"/>
+      <c r="N237" s="11"/>
+      <c r="O237" s="10"/>
+      <c r="P237" s="10"/>
+      <c r="Q237" s="10"/>
+      <c r="R237" s="11"/>
+      <c r="S237" s="13"/>
+      <c r="T237" s="10"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="10"/>
@@ -5882,12 +6121,13 @@
       <c r="K238" s="11"/>
       <c r="L238" s="11"/>
       <c r="M238" s="11"/>
-      <c r="N238" s="13"/>
-      <c r="O238" s="14"/>
-      <c r="P238" s="14"/>
-      <c r="Q238" s="14"/>
-      <c r="R238" s="13"/>
-      <c r="S238" s="10"/>
+      <c r="N238" s="11"/>
+      <c r="O238" s="10"/>
+      <c r="P238" s="10"/>
+      <c r="Q238" s="10"/>
+      <c r="R238" s="11"/>
+      <c r="S238" s="13"/>
+      <c r="T238" s="10"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="10"/>
@@ -5903,12 +6143,13 @@
       <c r="K239" s="11"/>
       <c r="L239" s="11"/>
       <c r="M239" s="11"/>
-      <c r="N239" s="13"/>
-      <c r="O239" s="14"/>
-      <c r="P239" s="14"/>
-      <c r="Q239" s="14"/>
-      <c r="R239" s="13"/>
-      <c r="S239" s="10"/>
+      <c r="N239" s="11"/>
+      <c r="O239" s="10"/>
+      <c r="P239" s="10"/>
+      <c r="Q239" s="10"/>
+      <c r="R239" s="11"/>
+      <c r="S239" s="13"/>
+      <c r="T239" s="10"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="10"/>
@@ -5924,12 +6165,13 @@
       <c r="K240" s="11"/>
       <c r="L240" s="11"/>
       <c r="M240" s="11"/>
-      <c r="N240" s="13"/>
-      <c r="O240" s="14"/>
-      <c r="P240" s="14"/>
-      <c r="Q240" s="14"/>
-      <c r="R240" s="13"/>
-      <c r="S240" s="10"/>
+      <c r="N240" s="11"/>
+      <c r="O240" s="10"/>
+      <c r="P240" s="10"/>
+      <c r="Q240" s="10"/>
+      <c r="R240" s="11"/>
+      <c r="S240" s="13"/>
+      <c r="T240" s="10"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="10"/>
@@ -5945,12 +6187,13 @@
       <c r="K241" s="11"/>
       <c r="L241" s="11"/>
       <c r="M241" s="11"/>
-      <c r="N241" s="13"/>
-      <c r="O241" s="14"/>
-      <c r="P241" s="14"/>
-      <c r="Q241" s="14"/>
-      <c r="R241" s="13"/>
-      <c r="S241" s="10"/>
+      <c r="N241" s="11"/>
+      <c r="O241" s="10"/>
+      <c r="P241" s="10"/>
+      <c r="Q241" s="10"/>
+      <c r="R241" s="11"/>
+      <c r="S241" s="13"/>
+      <c r="T241" s="10"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="10"/>
@@ -5966,12 +6209,13 @@
       <c r="K242" s="11"/>
       <c r="L242" s="11"/>
       <c r="M242" s="11"/>
-      <c r="N242" s="13"/>
-      <c r="O242" s="14"/>
-      <c r="P242" s="14"/>
-      <c r="Q242" s="14"/>
-      <c r="R242" s="13"/>
-      <c r="S242" s="10"/>
+      <c r="N242" s="11"/>
+      <c r="O242" s="10"/>
+      <c r="P242" s="10"/>
+      <c r="Q242" s="10"/>
+      <c r="R242" s="11"/>
+      <c r="S242" s="13"/>
+      <c r="T242" s="10"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="10"/>
@@ -5987,12 +6231,13 @@
       <c r="K243" s="11"/>
       <c r="L243" s="11"/>
       <c r="M243" s="11"/>
-      <c r="N243" s="13"/>
-      <c r="O243" s="14"/>
-      <c r="P243" s="14"/>
-      <c r="Q243" s="14"/>
-      <c r="R243" s="13"/>
-      <c r="S243" s="10"/>
+      <c r="N243" s="11"/>
+      <c r="O243" s="10"/>
+      <c r="P243" s="10"/>
+      <c r="Q243" s="10"/>
+      <c r="R243" s="11"/>
+      <c r="S243" s="13"/>
+      <c r="T243" s="10"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="10"/>
@@ -6008,12 +6253,13 @@
       <c r="K244" s="11"/>
       <c r="L244" s="11"/>
       <c r="M244" s="11"/>
-      <c r="N244" s="13"/>
-      <c r="O244" s="14"/>
-      <c r="P244" s="14"/>
-      <c r="Q244" s="14"/>
-      <c r="R244" s="13"/>
-      <c r="S244" s="10"/>
+      <c r="N244" s="11"/>
+      <c r="O244" s="10"/>
+      <c r="P244" s="10"/>
+      <c r="Q244" s="10"/>
+      <c r="R244" s="11"/>
+      <c r="S244" s="13"/>
+      <c r="T244" s="10"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="10"/>
@@ -6029,12 +6275,13 @@
       <c r="K245" s="11"/>
       <c r="L245" s="11"/>
       <c r="M245" s="11"/>
-      <c r="N245" s="13"/>
-      <c r="O245" s="14"/>
-      <c r="P245" s="14"/>
-      <c r="Q245" s="14"/>
-      <c r="R245" s="13"/>
-      <c r="S245" s="10"/>
+      <c r="N245" s="11"/>
+      <c r="O245" s="10"/>
+      <c r="P245" s="10"/>
+      <c r="Q245" s="10"/>
+      <c r="R245" s="11"/>
+      <c r="S245" s="13"/>
+      <c r="T245" s="10"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="10"/>
@@ -6050,12 +6297,13 @@
       <c r="K246" s="11"/>
       <c r="L246" s="11"/>
       <c r="M246" s="11"/>
-      <c r="N246" s="13"/>
-      <c r="O246" s="14"/>
-      <c r="P246" s="14"/>
-      <c r="Q246" s="14"/>
-      <c r="R246" s="13"/>
-      <c r="S246" s="10"/>
+      <c r="N246" s="11"/>
+      <c r="O246" s="10"/>
+      <c r="P246" s="10"/>
+      <c r="Q246" s="10"/>
+      <c r="R246" s="11"/>
+      <c r="S246" s="13"/>
+      <c r="T246" s="10"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="10"/>
@@ -6071,12 +6319,13 @@
       <c r="K247" s="11"/>
       <c r="L247" s="11"/>
       <c r="M247" s="11"/>
-      <c r="N247" s="13"/>
-      <c r="O247" s="14"/>
-      <c r="P247" s="14"/>
-      <c r="Q247" s="14"/>
-      <c r="R247" s="13"/>
-      <c r="S247" s="10"/>
+      <c r="N247" s="11"/>
+      <c r="O247" s="10"/>
+      <c r="P247" s="10"/>
+      <c r="Q247" s="10"/>
+      <c r="R247" s="11"/>
+      <c r="S247" s="13"/>
+      <c r="T247" s="10"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="10"/>
@@ -6092,12 +6341,13 @@
       <c r="K248" s="11"/>
       <c r="L248" s="11"/>
       <c r="M248" s="11"/>
-      <c r="N248" s="13"/>
-      <c r="O248" s="14"/>
-      <c r="P248" s="14"/>
-      <c r="Q248" s="14"/>
-      <c r="R248" s="13"/>
-      <c r="S248" s="10"/>
+      <c r="N248" s="11"/>
+      <c r="O248" s="10"/>
+      <c r="P248" s="10"/>
+      <c r="Q248" s="10"/>
+      <c r="R248" s="11"/>
+      <c r="S248" s="13"/>
+      <c r="T248" s="10"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="10"/>
@@ -6113,12 +6363,13 @@
       <c r="K249" s="11"/>
       <c r="L249" s="11"/>
       <c r="M249" s="11"/>
-      <c r="N249" s="13"/>
-      <c r="O249" s="14"/>
-      <c r="P249" s="14"/>
-      <c r="Q249" s="14"/>
-      <c r="R249" s="13"/>
-      <c r="S249" s="10"/>
+      <c r="N249" s="11"/>
+      <c r="O249" s="10"/>
+      <c r="P249" s="10"/>
+      <c r="Q249" s="10"/>
+      <c r="R249" s="11"/>
+      <c r="S249" s="13"/>
+      <c r="T249" s="10"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="10"/>
@@ -6134,12 +6385,13 @@
       <c r="K250" s="11"/>
       <c r="L250" s="11"/>
       <c r="M250" s="11"/>
-      <c r="N250" s="13"/>
-      <c r="O250" s="14"/>
-      <c r="P250" s="14"/>
-      <c r="Q250" s="14"/>
-      <c r="R250" s="13"/>
-      <c r="S250" s="10"/>
+      <c r="N250" s="11"/>
+      <c r="O250" s="10"/>
+      <c r="P250" s="10"/>
+      <c r="Q250" s="10"/>
+      <c r="R250" s="11"/>
+      <c r="S250" s="13"/>
+      <c r="T250" s="10"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="10"/>
@@ -6155,12 +6407,13 @@
       <c r="K251" s="11"/>
       <c r="L251" s="11"/>
       <c r="M251" s="11"/>
-      <c r="N251" s="13"/>
-      <c r="O251" s="14"/>
-      <c r="P251" s="14"/>
-      <c r="Q251" s="14"/>
-      <c r="R251" s="13"/>
-      <c r="S251" s="10"/>
+      <c r="N251" s="11"/>
+      <c r="O251" s="10"/>
+      <c r="P251" s="10"/>
+      <c r="Q251" s="10"/>
+      <c r="R251" s="11"/>
+      <c r="S251" s="13"/>
+      <c r="T251" s="10"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="10"/>
@@ -6176,12 +6429,13 @@
       <c r="K252" s="11"/>
       <c r="L252" s="11"/>
       <c r="M252" s="11"/>
-      <c r="N252" s="13"/>
-      <c r="O252" s="14"/>
-      <c r="P252" s="14"/>
-      <c r="Q252" s="14"/>
-      <c r="R252" s="13"/>
-      <c r="S252" s="10"/>
+      <c r="N252" s="11"/>
+      <c r="O252" s="10"/>
+      <c r="P252" s="10"/>
+      <c r="Q252" s="10"/>
+      <c r="R252" s="11"/>
+      <c r="S252" s="13"/>
+      <c r="T252" s="10"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="10"/>
@@ -6197,12 +6451,13 @@
       <c r="K253" s="11"/>
       <c r="L253" s="11"/>
       <c r="M253" s="11"/>
-      <c r="N253" s="13"/>
-      <c r="O253" s="14"/>
-      <c r="P253" s="14"/>
-      <c r="Q253" s="14"/>
-      <c r="R253" s="13"/>
-      <c r="S253" s="10"/>
+      <c r="N253" s="11"/>
+      <c r="O253" s="10"/>
+      <c r="P253" s="10"/>
+      <c r="Q253" s="10"/>
+      <c r="R253" s="11"/>
+      <c r="S253" s="13"/>
+      <c r="T253" s="10"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="10"/>
@@ -6218,12 +6473,13 @@
       <c r="K254" s="11"/>
       <c r="L254" s="11"/>
       <c r="M254" s="11"/>
-      <c r="N254" s="13"/>
-      <c r="O254" s="14"/>
-      <c r="P254" s="14"/>
-      <c r="Q254" s="14"/>
-      <c r="R254" s="13"/>
-      <c r="S254" s="10"/>
+      <c r="N254" s="11"/>
+      <c r="O254" s="10"/>
+      <c r="P254" s="10"/>
+      <c r="Q254" s="10"/>
+      <c r="R254" s="11"/>
+      <c r="S254" s="13"/>
+      <c r="T254" s="10"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="10"/>
@@ -6239,12 +6495,13 @@
       <c r="K255" s="11"/>
       <c r="L255" s="11"/>
       <c r="M255" s="11"/>
-      <c r="N255" s="13"/>
-      <c r="O255" s="14"/>
-      <c r="P255" s="14"/>
-      <c r="Q255" s="14"/>
-      <c r="R255" s="13"/>
-      <c r="S255" s="10"/>
+      <c r="N255" s="11"/>
+      <c r="O255" s="10"/>
+      <c r="P255" s="10"/>
+      <c r="Q255" s="10"/>
+      <c r="R255" s="11"/>
+      <c r="S255" s="13"/>
+      <c r="T255" s="10"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="10"/>
@@ -6260,12 +6517,13 @@
       <c r="K256" s="11"/>
       <c r="L256" s="11"/>
       <c r="M256" s="11"/>
-      <c r="N256" s="13"/>
-      <c r="O256" s="14"/>
-      <c r="P256" s="14"/>
-      <c r="Q256" s="14"/>
-      <c r="R256" s="13"/>
-      <c r="S256" s="10"/>
+      <c r="N256" s="11"/>
+      <c r="O256" s="10"/>
+      <c r="P256" s="10"/>
+      <c r="Q256" s="10"/>
+      <c r="R256" s="11"/>
+      <c r="S256" s="13"/>
+      <c r="T256" s="10"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="10"/>
@@ -6281,12 +6539,13 @@
       <c r="K257" s="11"/>
       <c r="L257" s="11"/>
       <c r="M257" s="11"/>
-      <c r="N257" s="13"/>
-      <c r="O257" s="14"/>
-      <c r="P257" s="14"/>
-      <c r="Q257" s="14"/>
-      <c r="R257" s="13"/>
-      <c r="S257" s="10"/>
+      <c r="N257" s="11"/>
+      <c r="O257" s="10"/>
+      <c r="P257" s="10"/>
+      <c r="Q257" s="10"/>
+      <c r="R257" s="11"/>
+      <c r="S257" s="13"/>
+      <c r="T257" s="10"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="10"/>
@@ -6302,12 +6561,13 @@
       <c r="K258" s="11"/>
       <c r="L258" s="11"/>
       <c r="M258" s="11"/>
-      <c r="N258" s="13"/>
-      <c r="O258" s="14"/>
-      <c r="P258" s="14"/>
-      <c r="Q258" s="14"/>
-      <c r="R258" s="13"/>
-      <c r="S258" s="10"/>
+      <c r="N258" s="11"/>
+      <c r="O258" s="10"/>
+      <c r="P258" s="10"/>
+      <c r="Q258" s="10"/>
+      <c r="R258" s="11"/>
+      <c r="S258" s="13"/>
+      <c r="T258" s="10"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="10"/>
@@ -6323,12 +6583,13 @@
       <c r="K259" s="11"/>
       <c r="L259" s="11"/>
       <c r="M259" s="11"/>
-      <c r="N259" s="13"/>
-      <c r="O259" s="14"/>
-      <c r="P259" s="14"/>
-      <c r="Q259" s="14"/>
-      <c r="R259" s="13"/>
-      <c r="S259" s="10"/>
+      <c r="N259" s="11"/>
+      <c r="O259" s="10"/>
+      <c r="P259" s="10"/>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="11"/>
+      <c r="S259" s="13"/>
+      <c r="T259" s="10"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="10"/>
@@ -6344,12 +6605,13 @@
       <c r="K260" s="11"/>
       <c r="L260" s="11"/>
       <c r="M260" s="11"/>
-      <c r="N260" s="13"/>
-      <c r="O260" s="14"/>
-      <c r="P260" s="14"/>
-      <c r="Q260" s="14"/>
-      <c r="R260" s="13"/>
-      <c r="S260" s="10"/>
+      <c r="N260" s="11"/>
+      <c r="O260" s="10"/>
+      <c r="P260" s="10"/>
+      <c r="Q260" s="10"/>
+      <c r="R260" s="11"/>
+      <c r="S260" s="13"/>
+      <c r="T260" s="10"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="10"/>
@@ -6365,12 +6627,13 @@
       <c r="K261" s="11"/>
       <c r="L261" s="11"/>
       <c r="M261" s="11"/>
-      <c r="N261" s="13"/>
-      <c r="O261" s="14"/>
-      <c r="P261" s="14"/>
-      <c r="Q261" s="14"/>
-      <c r="R261" s="13"/>
-      <c r="S261" s="10"/>
+      <c r="N261" s="11"/>
+      <c r="O261" s="10"/>
+      <c r="P261" s="10"/>
+      <c r="Q261" s="10"/>
+      <c r="R261" s="11"/>
+      <c r="S261" s="13"/>
+      <c r="T261" s="10"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="10"/>
@@ -6386,12 +6649,13 @@
       <c r="K262" s="11"/>
       <c r="L262" s="11"/>
       <c r="M262" s="11"/>
-      <c r="N262" s="13"/>
-      <c r="O262" s="14"/>
-      <c r="P262" s="14"/>
-      <c r="Q262" s="14"/>
-      <c r="R262" s="13"/>
-      <c r="S262" s="10"/>
+      <c r="N262" s="11"/>
+      <c r="O262" s="10"/>
+      <c r="P262" s="10"/>
+      <c r="Q262" s="10"/>
+      <c r="R262" s="11"/>
+      <c r="S262" s="13"/>
+      <c r="T262" s="10"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="10"/>
@@ -6407,12 +6671,13 @@
       <c r="K263" s="11"/>
       <c r="L263" s="11"/>
       <c r="M263" s="11"/>
-      <c r="N263" s="13"/>
-      <c r="O263" s="14"/>
-      <c r="P263" s="14"/>
-      <c r="Q263" s="14"/>
-      <c r="R263" s="13"/>
-      <c r="S263" s="10"/>
+      <c r="N263" s="11"/>
+      <c r="O263" s="10"/>
+      <c r="P263" s="10"/>
+      <c r="Q263" s="10"/>
+      <c r="R263" s="11"/>
+      <c r="S263" s="13"/>
+      <c r="T263" s="10"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="10"/>
@@ -6428,12 +6693,13 @@
       <c r="K264" s="11"/>
       <c r="L264" s="11"/>
       <c r="M264" s="11"/>
-      <c r="N264" s="13"/>
-      <c r="O264" s="14"/>
-      <c r="P264" s="14"/>
-      <c r="Q264" s="14"/>
-      <c r="R264" s="13"/>
-      <c r="S264" s="10"/>
+      <c r="N264" s="11"/>
+      <c r="O264" s="10"/>
+      <c r="P264" s="10"/>
+      <c r="Q264" s="10"/>
+      <c r="R264" s="11"/>
+      <c r="S264" s="13"/>
+      <c r="T264" s="10"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="10"/>
@@ -6449,12 +6715,13 @@
       <c r="K265" s="11"/>
       <c r="L265" s="11"/>
       <c r="M265" s="11"/>
-      <c r="N265" s="13"/>
-      <c r="O265" s="14"/>
-      <c r="P265" s="14"/>
-      <c r="Q265" s="14"/>
-      <c r="R265" s="13"/>
-      <c r="S265" s="10"/>
+      <c r="N265" s="11"/>
+      <c r="O265" s="10"/>
+      <c r="P265" s="10"/>
+      <c r="Q265" s="10"/>
+      <c r="R265" s="11"/>
+      <c r="S265" s="13"/>
+      <c r="T265" s="10"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="10"/>
@@ -6470,12 +6737,13 @@
       <c r="K266" s="11"/>
       <c r="L266" s="11"/>
       <c r="M266" s="11"/>
-      <c r="N266" s="13"/>
-      <c r="O266" s="14"/>
-      <c r="P266" s="14"/>
-      <c r="Q266" s="14"/>
-      <c r="R266" s="13"/>
-      <c r="S266" s="10"/>
+      <c r="N266" s="11"/>
+      <c r="O266" s="10"/>
+      <c r="P266" s="10"/>
+      <c r="Q266" s="10"/>
+      <c r="R266" s="11"/>
+      <c r="S266" s="13"/>
+      <c r="T266" s="10"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="10"/>
@@ -6491,12 +6759,13 @@
       <c r="K267" s="11"/>
       <c r="L267" s="11"/>
       <c r="M267" s="11"/>
-      <c r="N267" s="13"/>
-      <c r="O267" s="14"/>
-      <c r="P267" s="14"/>
-      <c r="Q267" s="14"/>
-      <c r="R267" s="13"/>
-      <c r="S267" s="10"/>
+      <c r="N267" s="11"/>
+      <c r="O267" s="10"/>
+      <c r="P267" s="10"/>
+      <c r="Q267" s="10"/>
+      <c r="R267" s="11"/>
+      <c r="S267" s="13"/>
+      <c r="T267" s="10"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="10"/>
@@ -6512,12 +6781,13 @@
       <c r="K268" s="11"/>
       <c r="L268" s="11"/>
       <c r="M268" s="11"/>
-      <c r="N268" s="13"/>
-      <c r="O268" s="14"/>
-      <c r="P268" s="14"/>
-      <c r="Q268" s="14"/>
-      <c r="R268" s="13"/>
-      <c r="S268" s="10"/>
+      <c r="N268" s="11"/>
+      <c r="O268" s="10"/>
+      <c r="P268" s="10"/>
+      <c r="Q268" s="10"/>
+      <c r="R268" s="11"/>
+      <c r="S268" s="13"/>
+      <c r="T268" s="10"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="10"/>
@@ -6533,12 +6803,13 @@
       <c r="K269" s="11"/>
       <c r="L269" s="11"/>
       <c r="M269" s="11"/>
-      <c r="N269" s="13"/>
-      <c r="O269" s="14"/>
-      <c r="P269" s="14"/>
-      <c r="Q269" s="14"/>
-      <c r="R269" s="13"/>
-      <c r="S269" s="10"/>
+      <c r="N269" s="11"/>
+      <c r="O269" s="10"/>
+      <c r="P269" s="10"/>
+      <c r="Q269" s="10"/>
+      <c r="R269" s="11"/>
+      <c r="S269" s="13"/>
+      <c r="T269" s="10"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="10"/>
@@ -6554,12 +6825,13 @@
       <c r="K270" s="11"/>
       <c r="L270" s="11"/>
       <c r="M270" s="11"/>
-      <c r="N270" s="13"/>
-      <c r="O270" s="14"/>
-      <c r="P270" s="14"/>
-      <c r="Q270" s="14"/>
-      <c r="R270" s="13"/>
-      <c r="S270" s="10"/>
+      <c r="N270" s="11"/>
+      <c r="O270" s="10"/>
+      <c r="P270" s="10"/>
+      <c r="Q270" s="10"/>
+      <c r="R270" s="11"/>
+      <c r="S270" s="13"/>
+      <c r="T270" s="10"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="10"/>
@@ -6575,12 +6847,13 @@
       <c r="K271" s="11"/>
       <c r="L271" s="11"/>
       <c r="M271" s="11"/>
-      <c r="N271" s="13"/>
-      <c r="O271" s="14"/>
-      <c r="P271" s="14"/>
-      <c r="Q271" s="14"/>
-      <c r="R271" s="13"/>
-      <c r="S271" s="10"/>
+      <c r="N271" s="11"/>
+      <c r="O271" s="10"/>
+      <c r="P271" s="10"/>
+      <c r="Q271" s="10"/>
+      <c r="R271" s="11"/>
+      <c r="S271" s="13"/>
+      <c r="T271" s="10"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="10"/>
@@ -6596,12 +6869,13 @@
       <c r="K272" s="11"/>
       <c r="L272" s="11"/>
       <c r="M272" s="11"/>
-      <c r="N272" s="13"/>
-      <c r="O272" s="14"/>
-      <c r="P272" s="14"/>
-      <c r="Q272" s="14"/>
-      <c r="R272" s="13"/>
-      <c r="S272" s="10"/>
+      <c r="N272" s="11"/>
+      <c r="O272" s="10"/>
+      <c r="P272" s="10"/>
+      <c r="Q272" s="10"/>
+      <c r="R272" s="11"/>
+      <c r="S272" s="13"/>
+      <c r="T272" s="10"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="10"/>
@@ -6617,12 +6891,13 @@
       <c r="K273" s="11"/>
       <c r="L273" s="11"/>
       <c r="M273" s="11"/>
-      <c r="N273" s="13"/>
-      <c r="O273" s="14"/>
-      <c r="P273" s="14"/>
-      <c r="Q273" s="14"/>
-      <c r="R273" s="13"/>
-      <c r="S273" s="10"/>
+      <c r="N273" s="11"/>
+      <c r="O273" s="10"/>
+      <c r="P273" s="10"/>
+      <c r="Q273" s="10"/>
+      <c r="R273" s="11"/>
+      <c r="S273" s="13"/>
+      <c r="T273" s="10"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="10"/>
@@ -6638,12 +6913,13 @@
       <c r="K274" s="11"/>
       <c r="L274" s="11"/>
       <c r="M274" s="11"/>
-      <c r="N274" s="13"/>
-      <c r="O274" s="14"/>
-      <c r="P274" s="14"/>
-      <c r="Q274" s="14"/>
-      <c r="R274" s="13"/>
-      <c r="S274" s="10"/>
+      <c r="N274" s="11"/>
+      <c r="O274" s="10"/>
+      <c r="P274" s="10"/>
+      <c r="Q274" s="10"/>
+      <c r="R274" s="11"/>
+      <c r="S274" s="13"/>
+      <c r="T274" s="10"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="10"/>
@@ -6659,12 +6935,13 @@
       <c r="K275" s="11"/>
       <c r="L275" s="11"/>
       <c r="M275" s="11"/>
-      <c r="N275" s="13"/>
-      <c r="O275" s="14"/>
-      <c r="P275" s="14"/>
-      <c r="Q275" s="14"/>
-      <c r="R275" s="13"/>
-      <c r="S275" s="10"/>
+      <c r="N275" s="11"/>
+      <c r="O275" s="10"/>
+      <c r="P275" s="10"/>
+      <c r="Q275" s="10"/>
+      <c r="R275" s="11"/>
+      <c r="S275" s="13"/>
+      <c r="T275" s="10"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="10"/>
@@ -6680,12 +6957,13 @@
       <c r="K276" s="11"/>
       <c r="L276" s="11"/>
       <c r="M276" s="11"/>
-      <c r="N276" s="13"/>
-      <c r="O276" s="14"/>
-      <c r="P276" s="14"/>
-      <c r="Q276" s="14"/>
-      <c r="R276" s="13"/>
-      <c r="S276" s="10"/>
+      <c r="N276" s="11"/>
+      <c r="O276" s="10"/>
+      <c r="P276" s="10"/>
+      <c r="Q276" s="10"/>
+      <c r="R276" s="11"/>
+      <c r="S276" s="13"/>
+      <c r="T276" s="10"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="10"/>
@@ -6701,12 +6979,13 @@
       <c r="K277" s="11"/>
       <c r="L277" s="11"/>
       <c r="M277" s="11"/>
-      <c r="N277" s="13"/>
-      <c r="O277" s="14"/>
-      <c r="P277" s="14"/>
-      <c r="Q277" s="14"/>
-      <c r="R277" s="13"/>
-      <c r="S277" s="10"/>
+      <c r="N277" s="11"/>
+      <c r="O277" s="10"/>
+      <c r="P277" s="10"/>
+      <c r="Q277" s="10"/>
+      <c r="R277" s="11"/>
+      <c r="S277" s="13"/>
+      <c r="T277" s="10"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="10"/>
@@ -6722,12 +7001,13 @@
       <c r="K278" s="11"/>
       <c r="L278" s="11"/>
       <c r="M278" s="11"/>
-      <c r="N278" s="13"/>
-      <c r="O278" s="14"/>
-      <c r="P278" s="14"/>
-      <c r="Q278" s="14"/>
-      <c r="R278" s="13"/>
-      <c r="S278" s="10"/>
+      <c r="N278" s="11"/>
+      <c r="O278" s="10"/>
+      <c r="P278" s="10"/>
+      <c r="Q278" s="10"/>
+      <c r="R278" s="11"/>
+      <c r="S278" s="13"/>
+      <c r="T278" s="10"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="10"/>
@@ -6743,12 +7023,13 @@
       <c r="K279" s="11"/>
       <c r="L279" s="11"/>
       <c r="M279" s="11"/>
-      <c r="N279" s="13"/>
-      <c r="O279" s="14"/>
-      <c r="P279" s="14"/>
-      <c r="Q279" s="14"/>
-      <c r="R279" s="13"/>
-      <c r="S279" s="10"/>
+      <c r="N279" s="11"/>
+      <c r="O279" s="10"/>
+      <c r="P279" s="10"/>
+      <c r="Q279" s="10"/>
+      <c r="R279" s="11"/>
+      <c r="S279" s="13"/>
+      <c r="T279" s="10"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="10"/>
@@ -6764,12 +7045,13 @@
       <c r="K280" s="11"/>
       <c r="L280" s="11"/>
       <c r="M280" s="11"/>
-      <c r="N280" s="13"/>
-      <c r="O280" s="14"/>
-      <c r="P280" s="14"/>
-      <c r="Q280" s="14"/>
-      <c r="R280" s="13"/>
-      <c r="S280" s="10"/>
+      <c r="N280" s="11"/>
+      <c r="O280" s="10"/>
+      <c r="P280" s="10"/>
+      <c r="Q280" s="10"/>
+      <c r="R280" s="11"/>
+      <c r="S280" s="13"/>
+      <c r="T280" s="10"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="10"/>
@@ -6785,12 +7067,13 @@
       <c r="K281" s="11"/>
       <c r="L281" s="11"/>
       <c r="M281" s="11"/>
-      <c r="N281" s="13"/>
-      <c r="O281" s="14"/>
-      <c r="P281" s="14"/>
-      <c r="Q281" s="14"/>
-      <c r="R281" s="13"/>
-      <c r="S281" s="10"/>
+      <c r="N281" s="11"/>
+      <c r="O281" s="10"/>
+      <c r="P281" s="10"/>
+      <c r="Q281" s="10"/>
+      <c r="R281" s="11"/>
+      <c r="S281" s="13"/>
+      <c r="T281" s="10"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="10"/>
@@ -6806,12 +7089,13 @@
       <c r="K282" s="11"/>
       <c r="L282" s="11"/>
       <c r="M282" s="11"/>
-      <c r="N282" s="13"/>
-      <c r="O282" s="14"/>
-      <c r="P282" s="14"/>
-      <c r="Q282" s="14"/>
-      <c r="R282" s="13"/>
-      <c r="S282" s="10"/>
+      <c r="N282" s="11"/>
+      <c r="O282" s="10"/>
+      <c r="P282" s="10"/>
+      <c r="Q282" s="10"/>
+      <c r="R282" s="11"/>
+      <c r="S282" s="13"/>
+      <c r="T282" s="10"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="10"/>
@@ -6827,12 +7111,13 @@
       <c r="K283" s="11"/>
       <c r="L283" s="11"/>
       <c r="M283" s="11"/>
-      <c r="N283" s="13"/>
-      <c r="O283" s="14"/>
-      <c r="P283" s="14"/>
-      <c r="Q283" s="14"/>
-      <c r="R283" s="13"/>
-      <c r="S283" s="10"/>
+      <c r="N283" s="11"/>
+      <c r="O283" s="10"/>
+      <c r="P283" s="10"/>
+      <c r="Q283" s="10"/>
+      <c r="R283" s="11"/>
+      <c r="S283" s="13"/>
+      <c r="T283" s="10"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="10"/>
@@ -6848,12 +7133,13 @@
       <c r="K284" s="11"/>
       <c r="L284" s="11"/>
       <c r="M284" s="11"/>
-      <c r="N284" s="13"/>
-      <c r="O284" s="14"/>
-      <c r="P284" s="14"/>
-      <c r="Q284" s="14"/>
-      <c r="R284" s="13"/>
-      <c r="S284" s="10"/>
+      <c r="N284" s="11"/>
+      <c r="O284" s="10"/>
+      <c r="P284" s="10"/>
+      <c r="Q284" s="10"/>
+      <c r="R284" s="11"/>
+      <c r="S284" s="13"/>
+      <c r="T284" s="10"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="10"/>
@@ -6869,12 +7155,13 @@
       <c r="K285" s="11"/>
       <c r="L285" s="11"/>
       <c r="M285" s="11"/>
-      <c r="N285" s="13"/>
-      <c r="O285" s="14"/>
-      <c r="P285" s="14"/>
-      <c r="Q285" s="14"/>
-      <c r="R285" s="13"/>
-      <c r="S285" s="10"/>
+      <c r="N285" s="11"/>
+      <c r="O285" s="10"/>
+      <c r="P285" s="10"/>
+      <c r="Q285" s="10"/>
+      <c r="R285" s="11"/>
+      <c r="S285" s="13"/>
+      <c r="T285" s="10"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="10"/>
@@ -6890,12 +7177,13 @@
       <c r="K286" s="11"/>
       <c r="L286" s="11"/>
       <c r="M286" s="11"/>
-      <c r="N286" s="13"/>
-      <c r="O286" s="14"/>
-      <c r="P286" s="14"/>
-      <c r="Q286" s="14"/>
-      <c r="R286" s="13"/>
-      <c r="S286" s="10"/>
+      <c r="N286" s="11"/>
+      <c r="O286" s="10"/>
+      <c r="P286" s="10"/>
+      <c r="Q286" s="10"/>
+      <c r="R286" s="11"/>
+      <c r="S286" s="13"/>
+      <c r="T286" s="10"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="10"/>
@@ -6911,12 +7199,13 @@
       <c r="K287" s="11"/>
       <c r="L287" s="11"/>
       <c r="M287" s="11"/>
-      <c r="N287" s="13"/>
-      <c r="O287" s="14"/>
-      <c r="P287" s="14"/>
-      <c r="Q287" s="14"/>
-      <c r="R287" s="13"/>
-      <c r="S287" s="10"/>
+      <c r="N287" s="11"/>
+      <c r="O287" s="10"/>
+      <c r="P287" s="10"/>
+      <c r="Q287" s="10"/>
+      <c r="R287" s="11"/>
+      <c r="S287" s="13"/>
+      <c r="T287" s="10"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="10"/>
@@ -6932,12 +7221,13 @@
       <c r="K288" s="11"/>
       <c r="L288" s="11"/>
       <c r="M288" s="11"/>
-      <c r="N288" s="13"/>
-      <c r="O288" s="14"/>
-      <c r="P288" s="14"/>
-      <c r="Q288" s="14"/>
-      <c r="R288" s="13"/>
-      <c r="S288" s="10"/>
+      <c r="N288" s="11"/>
+      <c r="O288" s="10"/>
+      <c r="P288" s="10"/>
+      <c r="Q288" s="10"/>
+      <c r="R288" s="11"/>
+      <c r="S288" s="13"/>
+      <c r="T288" s="10"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="10"/>
@@ -6953,12 +7243,13 @@
       <c r="K289" s="11"/>
       <c r="L289" s="11"/>
       <c r="M289" s="11"/>
-      <c r="N289" s="13"/>
-      <c r="O289" s="14"/>
-      <c r="P289" s="14"/>
-      <c r="Q289" s="14"/>
-      <c r="R289" s="13"/>
-      <c r="S289" s="10"/>
+      <c r="N289" s="11"/>
+      <c r="O289" s="10"/>
+      <c r="P289" s="10"/>
+      <c r="Q289" s="10"/>
+      <c r="R289" s="11"/>
+      <c r="S289" s="13"/>
+      <c r="T289" s="10"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="10"/>
@@ -6974,12 +7265,13 @@
       <c r="K290" s="11"/>
       <c r="L290" s="11"/>
       <c r="M290" s="11"/>
-      <c r="N290" s="13"/>
-      <c r="O290" s="14"/>
-      <c r="P290" s="14"/>
-      <c r="Q290" s="14"/>
-      <c r="R290" s="13"/>
-      <c r="S290" s="10"/>
+      <c r="N290" s="11"/>
+      <c r="O290" s="10"/>
+      <c r="P290" s="10"/>
+      <c r="Q290" s="10"/>
+      <c r="R290" s="11"/>
+      <c r="S290" s="13"/>
+      <c r="T290" s="10"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="10"/>
@@ -6995,12 +7287,13 @@
       <c r="K291" s="11"/>
       <c r="L291" s="11"/>
       <c r="M291" s="11"/>
-      <c r="N291" s="13"/>
-      <c r="O291" s="14"/>
-      <c r="P291" s="14"/>
-      <c r="Q291" s="14"/>
-      <c r="R291" s="13"/>
-      <c r="S291" s="10"/>
+      <c r="N291" s="11"/>
+      <c r="O291" s="10"/>
+      <c r="P291" s="10"/>
+      <c r="Q291" s="10"/>
+      <c r="R291" s="11"/>
+      <c r="S291" s="13"/>
+      <c r="T291" s="10"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="10"/>
@@ -7016,12 +7309,13 @@
       <c r="K292" s="11"/>
       <c r="L292" s="11"/>
       <c r="M292" s="11"/>
-      <c r="N292" s="13"/>
-      <c r="O292" s="14"/>
-      <c r="P292" s="14"/>
-      <c r="Q292" s="14"/>
-      <c r="R292" s="13"/>
-      <c r="S292" s="10"/>
+      <c r="N292" s="11"/>
+      <c r="O292" s="10"/>
+      <c r="P292" s="10"/>
+      <c r="Q292" s="10"/>
+      <c r="R292" s="11"/>
+      <c r="S292" s="13"/>
+      <c r="T292" s="10"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="10"/>
@@ -7037,12 +7331,13 @@
       <c r="K293" s="11"/>
       <c r="L293" s="11"/>
       <c r="M293" s="11"/>
-      <c r="N293" s="13"/>
-      <c r="O293" s="14"/>
-      <c r="P293" s="14"/>
-      <c r="Q293" s="14"/>
-      <c r="R293" s="13"/>
-      <c r="S293" s="10"/>
+      <c r="N293" s="11"/>
+      <c r="O293" s="10"/>
+      <c r="P293" s="10"/>
+      <c r="Q293" s="10"/>
+      <c r="R293" s="11"/>
+      <c r="S293" s="13"/>
+      <c r="T293" s="10"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="10"/>
@@ -7058,12 +7353,13 @@
       <c r="K294" s="11"/>
       <c r="L294" s="11"/>
       <c r="M294" s="11"/>
-      <c r="N294" s="13"/>
-      <c r="O294" s="14"/>
-      <c r="P294" s="14"/>
-      <c r="Q294" s="14"/>
-      <c r="R294" s="13"/>
-      <c r="S294" s="10"/>
+      <c r="N294" s="11"/>
+      <c r="O294" s="10"/>
+      <c r="P294" s="10"/>
+      <c r="Q294" s="10"/>
+      <c r="R294" s="11"/>
+      <c r="S294" s="13"/>
+      <c r="T294" s="10"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="10"/>
@@ -7079,12 +7375,13 @@
       <c r="K295" s="11"/>
       <c r="L295" s="11"/>
       <c r="M295" s="11"/>
-      <c r="N295" s="13"/>
-      <c r="O295" s="14"/>
-      <c r="P295" s="14"/>
-      <c r="Q295" s="14"/>
-      <c r="R295" s="13"/>
-      <c r="S295" s="10"/>
+      <c r="N295" s="11"/>
+      <c r="O295" s="10"/>
+      <c r="P295" s="10"/>
+      <c r="Q295" s="10"/>
+      <c r="R295" s="11"/>
+      <c r="S295" s="13"/>
+      <c r="T295" s="10"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="10"/>
@@ -7100,12 +7397,13 @@
       <c r="K296" s="11"/>
       <c r="L296" s="11"/>
       <c r="M296" s="11"/>
-      <c r="N296" s="13"/>
-      <c r="O296" s="14"/>
-      <c r="P296" s="14"/>
-      <c r="Q296" s="14"/>
-      <c r="R296" s="13"/>
-      <c r="S296" s="10"/>
+      <c r="N296" s="11"/>
+      <c r="O296" s="10"/>
+      <c r="P296" s="10"/>
+      <c r="Q296" s="10"/>
+      <c r="R296" s="11"/>
+      <c r="S296" s="13"/>
+      <c r="T296" s="10"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="10"/>
@@ -7121,12 +7419,13 @@
       <c r="K297" s="11"/>
       <c r="L297" s="11"/>
       <c r="M297" s="11"/>
-      <c r="N297" s="13"/>
-      <c r="O297" s="14"/>
-      <c r="P297" s="14"/>
-      <c r="Q297" s="14"/>
-      <c r="R297" s="13"/>
-      <c r="S297" s="10"/>
+      <c r="N297" s="11"/>
+      <c r="O297" s="10"/>
+      <c r="P297" s="10"/>
+      <c r="Q297" s="10"/>
+      <c r="R297" s="11"/>
+      <c r="S297" s="13"/>
+      <c r="T297" s="10"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="10"/>
@@ -7142,12 +7441,13 @@
       <c r="K298" s="11"/>
       <c r="L298" s="11"/>
       <c r="M298" s="11"/>
-      <c r="N298" s="13"/>
-      <c r="O298" s="14"/>
-      <c r="P298" s="14"/>
-      <c r="Q298" s="14"/>
-      <c r="R298" s="13"/>
-      <c r="S298" s="10"/>
+      <c r="N298" s="11"/>
+      <c r="O298" s="10"/>
+      <c r="P298" s="10"/>
+      <c r="Q298" s="10"/>
+      <c r="R298" s="11"/>
+      <c r="S298" s="13"/>
+      <c r="T298" s="10"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="10"/>
@@ -7163,12 +7463,13 @@
       <c r="K299" s="11"/>
       <c r="L299" s="11"/>
       <c r="M299" s="11"/>
-      <c r="N299" s="13"/>
-      <c r="O299" s="14"/>
-      <c r="P299" s="14"/>
-      <c r="Q299" s="14"/>
-      <c r="R299" s="13"/>
-      <c r="S299" s="10"/>
+      <c r="N299" s="11"/>
+      <c r="O299" s="10"/>
+      <c r="P299" s="10"/>
+      <c r="Q299" s="10"/>
+      <c r="R299" s="11"/>
+      <c r="S299" s="13"/>
+      <c r="T299" s="10"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="10"/>
@@ -7184,15 +7485,16 @@
       <c r="K300" s="11"/>
       <c r="L300" s="11"/>
       <c r="M300" s="11"/>
-      <c r="N300" s="13"/>
-      <c r="O300" s="14"/>
-      <c r="P300" s="14"/>
-      <c r="Q300" s="14"/>
-      <c r="R300" s="13"/>
-      <c r="S300" s="10"/>
+      <c r="N300" s="11"/>
+      <c r="O300" s="10"/>
+      <c r="P300" s="10"/>
+      <c r="Q300" s="10"/>
+      <c r="R300" s="11"/>
+      <c r="S300" s="13"/>
+      <c r="T300" s="10"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation allowBlank="true" error="اختر قيمة من القائمة المنسدلة" errorStyle="stop" errorTitle="دورة سداد غير معروفة" operator="between" prompt="اختر من القائمة — لا تكتب يدويًا" promptTitle="دورة السداد" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D300" type="list">
       <formula1>"شهري,سنوي,نصف سنوي,كل 3 اشهر,اسبوعي,يومي"</formula1>
       <formula2>0</formula2>
@@ -7229,6 +7531,10 @@
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S2:S300" type="list">
+      <formula1>"تلقائي,تُطبَّق,معفاة"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7254,83 +7560,83 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="17" t="s">
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17" t="s">
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="s">
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="15" t="s">
         <v>52</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="18" t="s">
-        <v>53</v>
+      <c r="B16" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/public/watheq-template.xlsx
+++ b/public/watheq-template.xlsx
@@ -106,12 +106,64 @@
         </r>
       </text>
     </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">يُكتشف من التاريخ تلقائيًّا. املأه فقط إن كانت تواريخك ميلادية وعقودك هجرية (أو العكس): هجري / ميلادي</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">بديل مريح عن «عدد الدفعات»: اكتب </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">24 لعقد سنتين ويُحسب العدد بحسب دورة السداد. إن ملأت العمودين فـ«عدد الدفعات» هو المعتمد.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="FreeSans"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">متأخرات من عقد سابق أو مستأجر سابق على هذه الوحدة — تظهر في الكشوف ولا تدخل في دفعات العقد الجاري</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t xml:space="preserve">اسم المستأجر</t>
   </si>
@@ -170,6 +222,15 @@
     <t xml:space="preserve">الضريبة (اختياري)</t>
   </si>
   <si>
+    <t xml:space="preserve">التقويم (اختياري)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مدة العقد بالأشهر (اختياري)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين مرحَّل (اختياري)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ملاحظة (لا تُستورد)</t>
   </si>
   <si>
@@ -192,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">شقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هجري</t>
   </si>
   <si>
     <t xml:space="preserve">مثال — احذف هذا الصف</t>
@@ -230,52 +294,73 @@
     <t xml:space="preserve">0533334444</t>
   </si>
   <si>
-    <t xml:space="preserve">قالب وثيق — رفع الوحدات والمستأجرين دفعة واحدة</t>
+    <t xml:space="preserve">قالب وثيق لرفع الوحدات والمستأجرين</t>
   </si>
   <si>
-    <t xml:space="preserve">ثلاث خطوات لا غير:</t>
+    <t xml:space="preserve">عبّئ ورقة «الوحدات»: صفٌّ لكل وحدة. الأعمدة التسعة الأولى مطلوبة، والباقي اختياري.</t>
   </si>
   <si>
-    <t xml:space="preserve">١  املأ ورقة «الوحدات»: صف لكل وحدة. الصفوف الرمادية أمثلة توضّح الصيغة — احذفها قبل الرفع.</t>
+    <t xml:space="preserve">المطلوب</t>
   </si>
   <si>
-    <t xml:space="preserve">٢  احفظ بصيغة CSV:  ملف ← حفظ باسم ← CSV UTF-8 (Comma delimited).  في Numbers: ملف ← تصدير إلى ← CSV.</t>
+    <t xml:space="preserve">• اسم المستأجر · رقم الوحدة · قيمة الدفعة · دورة السداد · بداية العقد · عدد الدفعات · الجوال · رقم الهوية · الدفعات المسدّدة</t>
   </si>
   <si>
-    <t xml:space="preserve">٣  ارفع الملف في وثيق: الأملاك ← رفع Excel ← اختر العقار ← اسحب الملف. ستظهر البيانات للمراجعة قبل أي حفظ.</t>
+    <t xml:space="preserve">• «قيمة الدفعة» هي مبلغ الدفعة الواحدة لا الإيجار السنوي. عقد 60,000 سنويًّا يُدفع نصف سنوي → اكتب 30,000 ودورة «كل 6 أشهر».</t>
   </si>
   <si>
-    <t xml:space="preserve">ما تحتاج معرفته عن الخانات:</t>
+    <t xml:space="preserve">• «الدفعات المسدّدة» كم دفعة سُدّدت منذ بداية العقد حتى اليوم — بدونها يُعدّ العقد غير مسدَّد بالكامل وتظهر متأخرات وهمية.</t>
   </si>
   <si>
-    <t xml:space="preserve">• دورة السداد: قائمة منسدلة — اختر منها ولا تكتب يدويًا.</t>
+    <t xml:space="preserve">التواريخ</t>
   </si>
   <si>
-    <t xml:space="preserve">• قيمة الدفعة: قيمة الدفعة الواحدة لا إجمالي العقد. عقد 30,000 سنويًا يُدفع نصف سنوي → 15000 وعدد الدفعات 2 لكل سنة.</t>
+    <t xml:space="preserve">• تُقبل ميلادية 2026-01-15 وهجرية 1447-03-15 (السنة بين 1300 و1600 تعني هجريًّا) — والنظام يحوّل ويعرض التاريخين معًا.</t>
   </si>
   <si>
-    <t xml:space="preserve">• بداية العقد: بصيغة 2026-01-01 ميلادي، أو 1447-03-15 هجري ويُحوَّل تلقائيًا. وثيق يحسب كل المواعيد منها ويعرض التاريخين معًا.</t>
+    <t xml:space="preserve">• أول دفعة تستحق في يوم بداية العقد. إن اتفقتم على تاريخ مختلف املأ «أول استحقاق».</t>
   </si>
   <si>
-    <t xml:space="preserve">• الدفعات المسدّدة: للعقود القائمة فقط — كم دفعة سُدّدت منذ بداية العقد حتى اليوم. عقد شهري من يناير مدفوع حتى أغسطس → 8. بدونها يظهر العقد كأنه لم يُسدَّد منه شيء.</t>
+    <t xml:space="preserve">• التقويم يُكتشف من التاريخ تلقائيًّا. املأ عمود «التقويم» فقط إن كانت تواريخك ميلادية وعقودك هجرية أو العكس.</t>
   </si>
   <si>
-    <t xml:space="preserve">• العقار (اختياري): اسم العقار كما هو في وثيق بالضبط — فيذهب الصف إليه، وترفع كل عقاراتك من ملف واحد. الفارغ يذهب للعقار المختار عند الرفع.</t>
+    <t xml:space="preserve">مدة العقد</t>
   </si>
   <si>
-    <t xml:space="preserve">• الجوال ورقم الهوية: خانات نصية عمدًا حتى لا يحذف إكسل الصفر الأول. الأرقام العربية (٠٥…) مقبولة.</t>
+    <t xml:space="preserve">• ليست كل العقود سنة: اكتب «عدد الدفعات» مباشرة (سنتان نصف سنوي = 4)، أو اترك العمود واكتب «مدة العقد بالأشهر» = 24 ويُحسب العدد.</t>
   </si>
   <si>
-    <t xml:space="preserve">• عمود «ملاحظة» لك وحدك — وثيق يتجاهله عند الرفع.</t>
+    <t xml:space="preserve">عدة عقارات في ملف واحد</t>
   </si>
   <si>
-    <t xml:space="preserve">أخطاء شائعة يمنعها هذا القالب:</t>
+    <t xml:space="preserve">• اكتب اسم العقار في عمود «العقار» لكل صف — يجب أن يطابق اسمه في وثيق حرفيًّا. أنشئ العقارات أولًا ثم ارفع الملف مرة واحدة.</t>
   </si>
   <si>
-    <t xml:space="preserve">• صفر الجوال المحذوف · تاريخ مقلوب الصيغة · «ربع سنوي» مكتوبة بعشر طرق · قيمة سنوية في خانة الدفعة.</t>
+    <t xml:space="preserve">• الصف الذي يُترك عموده فارغًا يذهب للعقار المختار في شاشة الرفع.</t>
   </si>
   <si>
-    <t xml:space="preserve">احتجت مساعدة؟ watheqdocs@gmail.com · داخل وثيق: المستشار الذكي</t>
+    <t xml:space="preserve">الاختياري المفيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• نوع الوحدة (شقة/محل/استديو…) يحدد أيضًا الضريبة في العمارة المختلطة: السكني معفى والتجاري خاضع.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• «الضريبة»: اتركه «تلقائي» غالبًا. «معفاة» أو «تُطبَّق» للحالات الخاصة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• «دين مرحَّل»: متأخرات من عقد أو مستأجر سابق على الوحدة — تظهر في الكشوف ولا تدخل في دفعات العقد الجاري.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• حسابا الكهرباء والماء يظهران في مخالصة الإخلاء، ورقم العقد يظهر في كل مستند وتبحث به.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأملاك ← رفع Excel ← اختر أي عقار ← اسحب الملف. ستظهر معاينة بكل صف وحالته قبل الحفظ — راجعها ثم احفظ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الصفوف الأربعة الأولى في ورقة «الوحدات» أمثلة توضيحية — احذفها قبل الرفع.</t>
   </si>
 </sst>
 </file>
@@ -287,7 +372,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +442,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FFB8782A"/>
@@ -365,7 +457,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF8A8477"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -441,7 +533,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -452,6 +544,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -478,10 +574,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -494,10 +586,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -506,11 +594,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -766,7 +854,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T300"/>
+  <dimension ref="A1:W300"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -783,8 +871,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -845,140 +935,164 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>22</v>
+      <c r="D2" s="7" t="s">
+        <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>23</v>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>25</v>
+      <c r="V2" s="9"/>
+      <c r="W2" s="4" t="s">
+        <v>31</v>
       </c>
-      <c r="I2" s="6" t="n">
-        <v>8</v>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>32</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
-        <v>26</v>
+      <c r="B3" s="5" t="s">
+        <v>33</v>
       </c>
-      <c r="O2" s="8" t="n">
+      <c r="C3" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="9"/>
+      <c r="W3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="P2" s="8" t="n">
-        <v>2</v>
+      <c r="G4" s="5" t="s">
+        <v>42</v>
       </c>
-      <c r="Q2" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" s="7"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6" t="n">
+      <c r="H4" s="5"/>
+      <c r="I4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="3" t="s">
-        <v>27</v>
+      <c r="J4" s="7"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1000,8 +1114,11 @@
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="11"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="10"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -1022,8 +1139,11 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="11"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="10"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10"/>
@@ -1044,8 +1164,11 @@
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="11"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="10"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -1066,8 +1189,11 @@
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="11"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="10"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
@@ -1088,8 +1214,11 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="11"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="10"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -1110,8 +1239,11 @@
       <c r="P10" s="10"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="11"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="10"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
@@ -1132,8 +1264,11 @@
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="11"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="10"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -1154,8 +1289,11 @@
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="11"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="10"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
@@ -1176,8 +1314,11 @@
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="11"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="10"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -1198,8 +1339,11 @@
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="11"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="10"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
@@ -1220,8 +1364,11 @@
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="11"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="10"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -1242,8 +1389,11 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="11"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="10"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
@@ -1264,8 +1414,11 @@
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="11"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="10"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -1286,8 +1439,11 @@
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="11"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="10"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10"/>
@@ -1308,8 +1464,11 @@
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="11"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="10"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10"/>
@@ -1330,8 +1489,11 @@
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="11"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="10"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10"/>
@@ -1352,8 +1514,11 @@
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="11"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="10"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
@@ -1374,8 +1539,11 @@
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="11"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="10"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10"/>
@@ -1396,8 +1564,11 @@
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="11"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="10"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10"/>
@@ -1418,8 +1589,11 @@
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="11"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="10"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -1440,8 +1614,11 @@
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="11"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="10"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
@@ -1462,8 +1639,11 @@
       <c r="P26" s="10"/>
       <c r="Q26" s="10"/>
       <c r="R26" s="11"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="10"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -1484,8 +1664,11 @@
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="11"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="10"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
@@ -1506,8 +1689,11 @@
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="11"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="10"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -1528,8 +1714,11 @@
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="11"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="10"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
@@ -1550,8 +1739,11 @@
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
       <c r="R30" s="11"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="10"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -1572,8 +1764,11 @@
       <c r="P31" s="10"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="11"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="10"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10"/>
@@ -1594,8 +1789,11 @@
       <c r="P32" s="10"/>
       <c r="Q32" s="10"/>
       <c r="R32" s="11"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="10"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -1616,8 +1814,11 @@
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="11"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="10"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10"/>
@@ -1638,8 +1839,11 @@
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="11"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="10"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -1660,8 +1864,11 @@
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="11"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="10"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10"/>
@@ -1682,8 +1889,11 @@
       <c r="P36" s="10"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="11"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="10"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -1704,8 +1914,11 @@
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="11"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="10"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10"/>
@@ -1726,8 +1939,11 @@
       <c r="P38" s="10"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="11"/>
-      <c r="S38" s="13"/>
-      <c r="T38" s="10"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="10"/>
@@ -1748,8 +1964,11 @@
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="11"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="10"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
@@ -1770,8 +1989,11 @@
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="11"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="10"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
@@ -1792,8 +2014,11 @@
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="11"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="10"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10"/>
@@ -1814,8 +2039,11 @@
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="11"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="10"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="10"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
@@ -1836,8 +2064,11 @@
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="11"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="10"/>
+      <c r="S43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -1858,8 +2089,11 @@
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="11"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="10"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
@@ -1880,8 +2114,11 @@
       <c r="P45" s="10"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="11"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="10"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -1902,8 +2139,11 @@
       <c r="P46" s="10"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="11"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="10"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
@@ -1924,8 +2164,11 @@
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="11"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="10"/>
+      <c r="S47" s="11"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -1946,8 +2189,11 @@
       <c r="P48" s="10"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="11"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="10"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
@@ -1968,8 +2214,11 @@
       <c r="P49" s="10"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="10"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -1990,8 +2239,11 @@
       <c r="P50" s="10"/>
       <c r="Q50" s="10"/>
       <c r="R50" s="11"/>
-      <c r="S50" s="13"/>
-      <c r="T50" s="10"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="10"/>
@@ -2012,8 +2264,11 @@
       <c r="P51" s="10"/>
       <c r="Q51" s="10"/>
       <c r="R51" s="11"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="10"/>
+      <c r="S51" s="11"/>
+      <c r="T51" s="11"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -2034,8 +2289,11 @@
       <c r="P52" s="10"/>
       <c r="Q52" s="10"/>
       <c r="R52" s="11"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="10"/>
+      <c r="S52" s="11"/>
+      <c r="T52" s="11"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10"/>
@@ -2056,8 +2314,11 @@
       <c r="P53" s="10"/>
       <c r="Q53" s="10"/>
       <c r="R53" s="11"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="10"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -2078,8 +2339,11 @@
       <c r="P54" s="10"/>
       <c r="Q54" s="10"/>
       <c r="R54" s="11"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="10"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10"/>
@@ -2100,8 +2364,11 @@
       <c r="P55" s="10"/>
       <c r="Q55" s="10"/>
       <c r="R55" s="11"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="10"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="10"/>
+      <c r="V55" s="10"/>
+      <c r="W55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -2122,8 +2389,11 @@
       <c r="P56" s="10"/>
       <c r="Q56" s="10"/>
       <c r="R56" s="11"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="10"/>
+      <c r="S56" s="11"/>
+      <c r="T56" s="11"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10"/>
@@ -2144,8 +2414,11 @@
       <c r="P57" s="10"/>
       <c r="Q57" s="10"/>
       <c r="R57" s="11"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="10"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="10"/>
+      <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10"/>
@@ -2166,8 +2439,11 @@
       <c r="P58" s="10"/>
       <c r="Q58" s="10"/>
       <c r="R58" s="11"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="10"/>
+      <c r="S58" s="11"/>
+      <c r="T58" s="11"/>
+      <c r="U58" s="10"/>
+      <c r="V58" s="10"/>
+      <c r="W58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10"/>
@@ -2188,8 +2464,11 @@
       <c r="P59" s="10"/>
       <c r="Q59" s="10"/>
       <c r="R59" s="11"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="10"/>
+      <c r="S59" s="11"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10"/>
@@ -2210,8 +2489,11 @@
       <c r="P60" s="10"/>
       <c r="Q60" s="10"/>
       <c r="R60" s="11"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="10"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10"/>
@@ -2232,8 +2514,11 @@
       <c r="P61" s="10"/>
       <c r="Q61" s="10"/>
       <c r="R61" s="11"/>
-      <c r="S61" s="13"/>
-      <c r="T61" s="10"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="10"/>
+      <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10"/>
@@ -2254,8 +2539,11 @@
       <c r="P62" s="10"/>
       <c r="Q62" s="10"/>
       <c r="R62" s="11"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="10"/>
+      <c r="S62" s="11"/>
+      <c r="T62" s="11"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -2276,8 +2564,11 @@
       <c r="P63" s="10"/>
       <c r="Q63" s="10"/>
       <c r="R63" s="11"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="10"/>
+      <c r="S63" s="11"/>
+      <c r="T63" s="11"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10"/>
@@ -2298,8 +2589,11 @@
       <c r="P64" s="10"/>
       <c r="Q64" s="10"/>
       <c r="R64" s="11"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="10"/>
+      <c r="S64" s="11"/>
+      <c r="T64" s="11"/>
+      <c r="U64" s="10"/>
+      <c r="V64" s="10"/>
+      <c r="W64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -2320,8 +2614,11 @@
       <c r="P65" s="10"/>
       <c r="Q65" s="10"/>
       <c r="R65" s="11"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="10"/>
+      <c r="S65" s="11"/>
+      <c r="T65" s="11"/>
+      <c r="U65" s="10"/>
+      <c r="V65" s="10"/>
+      <c r="W65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10"/>
@@ -2342,8 +2639,11 @@
       <c r="P66" s="10"/>
       <c r="Q66" s="10"/>
       <c r="R66" s="11"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="10"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -2364,8 +2664,11 @@
       <c r="P67" s="10"/>
       <c r="Q67" s="10"/>
       <c r="R67" s="11"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="10"/>
+      <c r="S67" s="11"/>
+      <c r="T67" s="11"/>
+      <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
+      <c r="W67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="10"/>
@@ -2386,8 +2689,11 @@
       <c r="P68" s="10"/>
       <c r="Q68" s="10"/>
       <c r="R68" s="11"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="10"/>
+      <c r="S68" s="11"/>
+      <c r="T68" s="11"/>
+      <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
+      <c r="W68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -2408,8 +2714,11 @@
       <c r="P69" s="10"/>
       <c r="Q69" s="10"/>
       <c r="R69" s="11"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="10"/>
+      <c r="S69" s="11"/>
+      <c r="T69" s="11"/>
+      <c r="U69" s="10"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="10"/>
@@ -2430,8 +2739,11 @@
       <c r="P70" s="10"/>
       <c r="Q70" s="10"/>
       <c r="R70" s="11"/>
-      <c r="S70" s="13"/>
-      <c r="T70" s="10"/>
+      <c r="S70" s="11"/>
+      <c r="T70" s="11"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -2452,8 +2764,11 @@
       <c r="P71" s="10"/>
       <c r="Q71" s="10"/>
       <c r="R71" s="11"/>
-      <c r="S71" s="13"/>
-      <c r="T71" s="10"/>
+      <c r="S71" s="11"/>
+      <c r="T71" s="11"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10"/>
@@ -2474,8 +2789,11 @@
       <c r="P72" s="10"/>
       <c r="Q72" s="10"/>
       <c r="R72" s="11"/>
-      <c r="S72" s="13"/>
-      <c r="T72" s="10"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="11"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -2496,8 +2814,11 @@
       <c r="P73" s="10"/>
       <c r="Q73" s="10"/>
       <c r="R73" s="11"/>
-      <c r="S73" s="13"/>
-      <c r="T73" s="10"/>
+      <c r="S73" s="11"/>
+      <c r="T73" s="11"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="10"/>
@@ -2518,8 +2839,11 @@
       <c r="P74" s="10"/>
       <c r="Q74" s="10"/>
       <c r="R74" s="11"/>
-      <c r="S74" s="13"/>
-      <c r="T74" s="10"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="11"/>
+      <c r="U74" s="10"/>
+      <c r="V74" s="10"/>
+      <c r="W74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -2540,8 +2864,11 @@
       <c r="P75" s="10"/>
       <c r="Q75" s="10"/>
       <c r="R75" s="11"/>
-      <c r="S75" s="13"/>
-      <c r="T75" s="10"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="10"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10"/>
@@ -2562,8 +2889,11 @@
       <c r="P76" s="10"/>
       <c r="Q76" s="10"/>
       <c r="R76" s="11"/>
-      <c r="S76" s="13"/>
-      <c r="T76" s="10"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="10"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10"/>
@@ -2584,8 +2914,11 @@
       <c r="P77" s="10"/>
       <c r="Q77" s="10"/>
       <c r="R77" s="11"/>
-      <c r="S77" s="13"/>
-      <c r="T77" s="10"/>
+      <c r="S77" s="11"/>
+      <c r="T77" s="11"/>
+      <c r="U77" s="10"/>
+      <c r="V77" s="10"/>
+      <c r="W77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10"/>
@@ -2606,8 +2939,11 @@
       <c r="P78" s="10"/>
       <c r="Q78" s="10"/>
       <c r="R78" s="11"/>
-      <c r="S78" s="13"/>
-      <c r="T78" s="10"/>
+      <c r="S78" s="11"/>
+      <c r="T78" s="11"/>
+      <c r="U78" s="10"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10"/>
@@ -2628,8 +2964,11 @@
       <c r="P79" s="10"/>
       <c r="Q79" s="10"/>
       <c r="R79" s="11"/>
-      <c r="S79" s="13"/>
-      <c r="T79" s="10"/>
+      <c r="S79" s="11"/>
+      <c r="T79" s="11"/>
+      <c r="U79" s="10"/>
+      <c r="V79" s="10"/>
+      <c r="W79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="10"/>
@@ -2650,8 +2989,11 @@
       <c r="P80" s="10"/>
       <c r="Q80" s="10"/>
       <c r="R80" s="11"/>
-      <c r="S80" s="13"/>
-      <c r="T80" s="10"/>
+      <c r="S80" s="11"/>
+      <c r="T80" s="11"/>
+      <c r="U80" s="10"/>
+      <c r="V80" s="10"/>
+      <c r="W80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="10"/>
@@ -2672,8 +3014,11 @@
       <c r="P81" s="10"/>
       <c r="Q81" s="10"/>
       <c r="R81" s="11"/>
-      <c r="S81" s="13"/>
-      <c r="T81" s="10"/>
+      <c r="S81" s="11"/>
+      <c r="T81" s="11"/>
+      <c r="U81" s="10"/>
+      <c r="V81" s="10"/>
+      <c r="W81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="10"/>
@@ -2694,8 +3039,11 @@
       <c r="P82" s="10"/>
       <c r="Q82" s="10"/>
       <c r="R82" s="11"/>
-      <c r="S82" s="13"/>
-      <c r="T82" s="10"/>
+      <c r="S82" s="11"/>
+      <c r="T82" s="11"/>
+      <c r="U82" s="10"/>
+      <c r="V82" s="10"/>
+      <c r="W82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="10"/>
@@ -2716,8 +3064,11 @@
       <c r="P83" s="10"/>
       <c r="Q83" s="10"/>
       <c r="R83" s="11"/>
-      <c r="S83" s="13"/>
-      <c r="T83" s="10"/>
+      <c r="S83" s="11"/>
+      <c r="T83" s="11"/>
+      <c r="U83" s="10"/>
+      <c r="V83" s="10"/>
+      <c r="W83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10"/>
@@ -2738,8 +3089,11 @@
       <c r="P84" s="10"/>
       <c r="Q84" s="10"/>
       <c r="R84" s="11"/>
-      <c r="S84" s="13"/>
-      <c r="T84" s="10"/>
+      <c r="S84" s="11"/>
+      <c r="T84" s="11"/>
+      <c r="U84" s="10"/>
+      <c r="V84" s="10"/>
+      <c r="W84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10"/>
@@ -2760,8 +3114,11 @@
       <c r="P85" s="10"/>
       <c r="Q85" s="10"/>
       <c r="R85" s="11"/>
-      <c r="S85" s="13"/>
-      <c r="T85" s="10"/>
+      <c r="S85" s="11"/>
+      <c r="T85" s="11"/>
+      <c r="U85" s="10"/>
+      <c r="V85" s="10"/>
+      <c r="W85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10"/>
@@ -2782,8 +3139,11 @@
       <c r="P86" s="10"/>
       <c r="Q86" s="10"/>
       <c r="R86" s="11"/>
-      <c r="S86" s="13"/>
-      <c r="T86" s="10"/>
+      <c r="S86" s="11"/>
+      <c r="T86" s="11"/>
+      <c r="U86" s="10"/>
+      <c r="V86" s="10"/>
+      <c r="W86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10"/>
@@ -2804,8 +3164,11 @@
       <c r="P87" s="10"/>
       <c r="Q87" s="10"/>
       <c r="R87" s="11"/>
-      <c r="S87" s="13"/>
-      <c r="T87" s="10"/>
+      <c r="S87" s="11"/>
+      <c r="T87" s="11"/>
+      <c r="U87" s="10"/>
+      <c r="V87" s="10"/>
+      <c r="W87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10"/>
@@ -2826,8 +3189,11 @@
       <c r="P88" s="10"/>
       <c r="Q88" s="10"/>
       <c r="R88" s="11"/>
-      <c r="S88" s="13"/>
-      <c r="T88" s="10"/>
+      <c r="S88" s="11"/>
+      <c r="T88" s="11"/>
+      <c r="U88" s="10"/>
+      <c r="V88" s="10"/>
+      <c r="W88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10"/>
@@ -2848,8 +3214,11 @@
       <c r="P89" s="10"/>
       <c r="Q89" s="10"/>
       <c r="R89" s="11"/>
-      <c r="S89" s="13"/>
-      <c r="T89" s="10"/>
+      <c r="S89" s="11"/>
+      <c r="T89" s="11"/>
+      <c r="U89" s="10"/>
+      <c r="V89" s="10"/>
+      <c r="W89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="10"/>
@@ -2870,8 +3239,11 @@
       <c r="P90" s="10"/>
       <c r="Q90" s="10"/>
       <c r="R90" s="11"/>
-      <c r="S90" s="13"/>
-      <c r="T90" s="10"/>
+      <c r="S90" s="11"/>
+      <c r="T90" s="11"/>
+      <c r="U90" s="10"/>
+      <c r="V90" s="10"/>
+      <c r="W90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10"/>
@@ -2892,8 +3264,11 @@
       <c r="P91" s="10"/>
       <c r="Q91" s="10"/>
       <c r="R91" s="11"/>
-      <c r="S91" s="13"/>
-      <c r="T91" s="10"/>
+      <c r="S91" s="11"/>
+      <c r="T91" s="11"/>
+      <c r="U91" s="10"/>
+      <c r="V91" s="10"/>
+      <c r="W91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10"/>
@@ -2914,8 +3289,11 @@
       <c r="P92" s="10"/>
       <c r="Q92" s="10"/>
       <c r="R92" s="11"/>
-      <c r="S92" s="13"/>
-      <c r="T92" s="10"/>
+      <c r="S92" s="11"/>
+      <c r="T92" s="11"/>
+      <c r="U92" s="10"/>
+      <c r="V92" s="10"/>
+      <c r="W92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10"/>
@@ -2936,8 +3314,11 @@
       <c r="P93" s="10"/>
       <c r="Q93" s="10"/>
       <c r="R93" s="11"/>
-      <c r="S93" s="13"/>
-      <c r="T93" s="10"/>
+      <c r="S93" s="11"/>
+      <c r="T93" s="11"/>
+      <c r="U93" s="10"/>
+      <c r="V93" s="10"/>
+      <c r="W93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10"/>
@@ -2958,8 +3339,11 @@
       <c r="P94" s="10"/>
       <c r="Q94" s="10"/>
       <c r="R94" s="11"/>
-      <c r="S94" s="13"/>
-      <c r="T94" s="10"/>
+      <c r="S94" s="11"/>
+      <c r="T94" s="11"/>
+      <c r="U94" s="10"/>
+      <c r="V94" s="10"/>
+      <c r="W94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10"/>
@@ -2980,8 +3364,11 @@
       <c r="P95" s="10"/>
       <c r="Q95" s="10"/>
       <c r="R95" s="11"/>
-      <c r="S95" s="13"/>
-      <c r="T95" s="10"/>
+      <c r="S95" s="11"/>
+      <c r="T95" s="11"/>
+      <c r="U95" s="10"/>
+      <c r="V95" s="10"/>
+      <c r="W95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="10"/>
@@ -3002,8 +3389,11 @@
       <c r="P96" s="10"/>
       <c r="Q96" s="10"/>
       <c r="R96" s="11"/>
-      <c r="S96" s="13"/>
-      <c r="T96" s="10"/>
+      <c r="S96" s="11"/>
+      <c r="T96" s="11"/>
+      <c r="U96" s="10"/>
+      <c r="V96" s="10"/>
+      <c r="W96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10"/>
@@ -3024,8 +3414,11 @@
       <c r="P97" s="10"/>
       <c r="Q97" s="10"/>
       <c r="R97" s="11"/>
-      <c r="S97" s="13"/>
-      <c r="T97" s="10"/>
+      <c r="S97" s="11"/>
+      <c r="T97" s="11"/>
+      <c r="U97" s="10"/>
+      <c r="V97" s="10"/>
+      <c r="W97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10"/>
@@ -3046,8 +3439,11 @@
       <c r="P98" s="10"/>
       <c r="Q98" s="10"/>
       <c r="R98" s="11"/>
-      <c r="S98" s="13"/>
-      <c r="T98" s="10"/>
+      <c r="S98" s="11"/>
+      <c r="T98" s="11"/>
+      <c r="U98" s="10"/>
+      <c r="V98" s="10"/>
+      <c r="W98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10"/>
@@ -3068,8 +3464,11 @@
       <c r="P99" s="10"/>
       <c r="Q99" s="10"/>
       <c r="R99" s="11"/>
-      <c r="S99" s="13"/>
-      <c r="T99" s="10"/>
+      <c r="S99" s="11"/>
+      <c r="T99" s="11"/>
+      <c r="U99" s="10"/>
+      <c r="V99" s="10"/>
+      <c r="W99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10"/>
@@ -3090,8 +3489,11 @@
       <c r="P100" s="10"/>
       <c r="Q100" s="10"/>
       <c r="R100" s="11"/>
-      <c r="S100" s="13"/>
-      <c r="T100" s="10"/>
+      <c r="S100" s="11"/>
+      <c r="T100" s="11"/>
+      <c r="U100" s="10"/>
+      <c r="V100" s="10"/>
+      <c r="W100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10"/>
@@ -3112,8 +3514,11 @@
       <c r="P101" s="10"/>
       <c r="Q101" s="10"/>
       <c r="R101" s="11"/>
-      <c r="S101" s="13"/>
-      <c r="T101" s="10"/>
+      <c r="S101" s="11"/>
+      <c r="T101" s="11"/>
+      <c r="U101" s="10"/>
+      <c r="V101" s="10"/>
+      <c r="W101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="10"/>
@@ -3134,8 +3539,11 @@
       <c r="P102" s="10"/>
       <c r="Q102" s="10"/>
       <c r="R102" s="11"/>
-      <c r="S102" s="13"/>
-      <c r="T102" s="10"/>
+      <c r="S102" s="11"/>
+      <c r="T102" s="11"/>
+      <c r="U102" s="10"/>
+      <c r="V102" s="10"/>
+      <c r="W102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="10"/>
@@ -3156,8 +3564,11 @@
       <c r="P103" s="10"/>
       <c r="Q103" s="10"/>
       <c r="R103" s="11"/>
-      <c r="S103" s="13"/>
-      <c r="T103" s="10"/>
+      <c r="S103" s="11"/>
+      <c r="T103" s="11"/>
+      <c r="U103" s="10"/>
+      <c r="V103" s="10"/>
+      <c r="W103" s="10"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10"/>
@@ -3178,8 +3589,11 @@
       <c r="P104" s="10"/>
       <c r="Q104" s="10"/>
       <c r="R104" s="11"/>
-      <c r="S104" s="13"/>
-      <c r="T104" s="10"/>
+      <c r="S104" s="11"/>
+      <c r="T104" s="11"/>
+      <c r="U104" s="10"/>
+      <c r="V104" s="10"/>
+      <c r="W104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10"/>
@@ -3200,8 +3614,11 @@
       <c r="P105" s="10"/>
       <c r="Q105" s="10"/>
       <c r="R105" s="11"/>
-      <c r="S105" s="13"/>
-      <c r="T105" s="10"/>
+      <c r="S105" s="11"/>
+      <c r="T105" s="11"/>
+      <c r="U105" s="10"/>
+      <c r="V105" s="10"/>
+      <c r="W105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10"/>
@@ -3222,8 +3639,11 @@
       <c r="P106" s="10"/>
       <c r="Q106" s="10"/>
       <c r="R106" s="11"/>
-      <c r="S106" s="13"/>
-      <c r="T106" s="10"/>
+      <c r="S106" s="11"/>
+      <c r="T106" s="11"/>
+      <c r="U106" s="10"/>
+      <c r="V106" s="10"/>
+      <c r="W106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10"/>
@@ -3244,8 +3664,11 @@
       <c r="P107" s="10"/>
       <c r="Q107" s="10"/>
       <c r="R107" s="11"/>
-      <c r="S107" s="13"/>
-      <c r="T107" s="10"/>
+      <c r="S107" s="11"/>
+      <c r="T107" s="11"/>
+      <c r="U107" s="10"/>
+      <c r="V107" s="10"/>
+      <c r="W107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10"/>
@@ -3266,8 +3689,11 @@
       <c r="P108" s="10"/>
       <c r="Q108" s="10"/>
       <c r="R108" s="11"/>
-      <c r="S108" s="13"/>
-      <c r="T108" s="10"/>
+      <c r="S108" s="11"/>
+      <c r="T108" s="11"/>
+      <c r="U108" s="10"/>
+      <c r="V108" s="10"/>
+      <c r="W108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10"/>
@@ -3288,8 +3714,11 @@
       <c r="P109" s="10"/>
       <c r="Q109" s="10"/>
       <c r="R109" s="11"/>
-      <c r="S109" s="13"/>
-      <c r="T109" s="10"/>
+      <c r="S109" s="11"/>
+      <c r="T109" s="11"/>
+      <c r="U109" s="10"/>
+      <c r="V109" s="10"/>
+      <c r="W109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10"/>
@@ -3310,8 +3739,11 @@
       <c r="P110" s="10"/>
       <c r="Q110" s="10"/>
       <c r="R110" s="11"/>
-      <c r="S110" s="13"/>
-      <c r="T110" s="10"/>
+      <c r="S110" s="11"/>
+      <c r="T110" s="11"/>
+      <c r="U110" s="10"/>
+      <c r="V110" s="10"/>
+      <c r="W110" s="10"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="10"/>
@@ -3332,8 +3764,11 @@
       <c r="P111" s="10"/>
       <c r="Q111" s="10"/>
       <c r="R111" s="11"/>
-      <c r="S111" s="13"/>
-      <c r="T111" s="10"/>
+      <c r="S111" s="11"/>
+      <c r="T111" s="11"/>
+      <c r="U111" s="10"/>
+      <c r="V111" s="10"/>
+      <c r="W111" s="10"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="10"/>
@@ -3354,8 +3789,11 @@
       <c r="P112" s="10"/>
       <c r="Q112" s="10"/>
       <c r="R112" s="11"/>
-      <c r="S112" s="13"/>
-      <c r="T112" s="10"/>
+      <c r="S112" s="11"/>
+      <c r="T112" s="11"/>
+      <c r="U112" s="10"/>
+      <c r="V112" s="10"/>
+      <c r="W112" s="10"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="10"/>
@@ -3376,8 +3814,11 @@
       <c r="P113" s="10"/>
       <c r="Q113" s="10"/>
       <c r="R113" s="11"/>
-      <c r="S113" s="13"/>
-      <c r="T113" s="10"/>
+      <c r="S113" s="11"/>
+      <c r="T113" s="11"/>
+      <c r="U113" s="10"/>
+      <c r="V113" s="10"/>
+      <c r="W113" s="10"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="10"/>
@@ -3398,8 +3839,11 @@
       <c r="P114" s="10"/>
       <c r="Q114" s="10"/>
       <c r="R114" s="11"/>
-      <c r="S114" s="13"/>
-      <c r="T114" s="10"/>
+      <c r="S114" s="11"/>
+      <c r="T114" s="11"/>
+      <c r="U114" s="10"/>
+      <c r="V114" s="10"/>
+      <c r="W114" s="10"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="10"/>
@@ -3420,8 +3864,11 @@
       <c r="P115" s="10"/>
       <c r="Q115" s="10"/>
       <c r="R115" s="11"/>
-      <c r="S115" s="13"/>
-      <c r="T115" s="10"/>
+      <c r="S115" s="11"/>
+      <c r="T115" s="11"/>
+      <c r="U115" s="10"/>
+      <c r="V115" s="10"/>
+      <c r="W115" s="10"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="10"/>
@@ -3442,8 +3889,11 @@
       <c r="P116" s="10"/>
       <c r="Q116" s="10"/>
       <c r="R116" s="11"/>
-      <c r="S116" s="13"/>
-      <c r="T116" s="10"/>
+      <c r="S116" s="11"/>
+      <c r="T116" s="11"/>
+      <c r="U116" s="10"/>
+      <c r="V116" s="10"/>
+      <c r="W116" s="10"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="10"/>
@@ -3464,8 +3914,11 @@
       <c r="P117" s="10"/>
       <c r="Q117" s="10"/>
       <c r="R117" s="11"/>
-      <c r="S117" s="13"/>
-      <c r="T117" s="10"/>
+      <c r="S117" s="11"/>
+      <c r="T117" s="11"/>
+      <c r="U117" s="10"/>
+      <c r="V117" s="10"/>
+      <c r="W117" s="10"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="10"/>
@@ -3486,8 +3939,11 @@
       <c r="P118" s="10"/>
       <c r="Q118" s="10"/>
       <c r="R118" s="11"/>
-      <c r="S118" s="13"/>
-      <c r="T118" s="10"/>
+      <c r="S118" s="11"/>
+      <c r="T118" s="11"/>
+      <c r="U118" s="10"/>
+      <c r="V118" s="10"/>
+      <c r="W118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="10"/>
@@ -3508,8 +3964,11 @@
       <c r="P119" s="10"/>
       <c r="Q119" s="10"/>
       <c r="R119" s="11"/>
-      <c r="S119" s="13"/>
-      <c r="T119" s="10"/>
+      <c r="S119" s="11"/>
+      <c r="T119" s="11"/>
+      <c r="U119" s="10"/>
+      <c r="V119" s="10"/>
+      <c r="W119" s="10"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="10"/>
@@ -3530,8 +3989,11 @@
       <c r="P120" s="10"/>
       <c r="Q120" s="10"/>
       <c r="R120" s="11"/>
-      <c r="S120" s="13"/>
-      <c r="T120" s="10"/>
+      <c r="S120" s="11"/>
+      <c r="T120" s="11"/>
+      <c r="U120" s="10"/>
+      <c r="V120" s="10"/>
+      <c r="W120" s="10"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="10"/>
@@ -3552,8 +4014,11 @@
       <c r="P121" s="10"/>
       <c r="Q121" s="10"/>
       <c r="R121" s="11"/>
-      <c r="S121" s="13"/>
-      <c r="T121" s="10"/>
+      <c r="S121" s="11"/>
+      <c r="T121" s="11"/>
+      <c r="U121" s="10"/>
+      <c r="V121" s="10"/>
+      <c r="W121" s="10"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="10"/>
@@ -3574,8 +4039,11 @@
       <c r="P122" s="10"/>
       <c r="Q122" s="10"/>
       <c r="R122" s="11"/>
-      <c r="S122" s="13"/>
-      <c r="T122" s="10"/>
+      <c r="S122" s="11"/>
+      <c r="T122" s="11"/>
+      <c r="U122" s="10"/>
+      <c r="V122" s="10"/>
+      <c r="W122" s="10"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="10"/>
@@ -3596,8 +4064,11 @@
       <c r="P123" s="10"/>
       <c r="Q123" s="10"/>
       <c r="R123" s="11"/>
-      <c r="S123" s="13"/>
-      <c r="T123" s="10"/>
+      <c r="S123" s="11"/>
+      <c r="T123" s="11"/>
+      <c r="U123" s="10"/>
+      <c r="V123" s="10"/>
+      <c r="W123" s="10"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="10"/>
@@ -3618,8 +4089,11 @@
       <c r="P124" s="10"/>
       <c r="Q124" s="10"/>
       <c r="R124" s="11"/>
-      <c r="S124" s="13"/>
-      <c r="T124" s="10"/>
+      <c r="S124" s="11"/>
+      <c r="T124" s="11"/>
+      <c r="U124" s="10"/>
+      <c r="V124" s="10"/>
+      <c r="W124" s="10"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="10"/>
@@ -3640,8 +4114,11 @@
       <c r="P125" s="10"/>
       <c r="Q125" s="10"/>
       <c r="R125" s="11"/>
-      <c r="S125" s="13"/>
-      <c r="T125" s="10"/>
+      <c r="S125" s="11"/>
+      <c r="T125" s="11"/>
+      <c r="U125" s="10"/>
+      <c r="V125" s="10"/>
+      <c r="W125" s="10"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="10"/>
@@ -3662,8 +4139,11 @@
       <c r="P126" s="10"/>
       <c r="Q126" s="10"/>
       <c r="R126" s="11"/>
-      <c r="S126" s="13"/>
-      <c r="T126" s="10"/>
+      <c r="S126" s="11"/>
+      <c r="T126" s="11"/>
+      <c r="U126" s="10"/>
+      <c r="V126" s="10"/>
+      <c r="W126" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="10"/>
@@ -3684,8 +4164,11 @@
       <c r="P127" s="10"/>
       <c r="Q127" s="10"/>
       <c r="R127" s="11"/>
-      <c r="S127" s="13"/>
-      <c r="T127" s="10"/>
+      <c r="S127" s="11"/>
+      <c r="T127" s="11"/>
+      <c r="U127" s="10"/>
+      <c r="V127" s="10"/>
+      <c r="W127" s="10"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="10"/>
@@ -3706,8 +4189,11 @@
       <c r="P128" s="10"/>
       <c r="Q128" s="10"/>
       <c r="R128" s="11"/>
-      <c r="S128" s="13"/>
-      <c r="T128" s="10"/>
+      <c r="S128" s="11"/>
+      <c r="T128" s="11"/>
+      <c r="U128" s="10"/>
+      <c r="V128" s="10"/>
+      <c r="W128" s="10"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="10"/>
@@ -3728,8 +4214,11 @@
       <c r="P129" s="10"/>
       <c r="Q129" s="10"/>
       <c r="R129" s="11"/>
-      <c r="S129" s="13"/>
-      <c r="T129" s="10"/>
+      <c r="S129" s="11"/>
+      <c r="T129" s="11"/>
+      <c r="U129" s="10"/>
+      <c r="V129" s="10"/>
+      <c r="W129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="10"/>
@@ -3750,8 +4239,11 @@
       <c r="P130" s="10"/>
       <c r="Q130" s="10"/>
       <c r="R130" s="11"/>
-      <c r="S130" s="13"/>
-      <c r="T130" s="10"/>
+      <c r="S130" s="11"/>
+      <c r="T130" s="11"/>
+      <c r="U130" s="10"/>
+      <c r="V130" s="10"/>
+      <c r="W130" s="10"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="10"/>
@@ -3772,8 +4264,11 @@
       <c r="P131" s="10"/>
       <c r="Q131" s="10"/>
       <c r="R131" s="11"/>
-      <c r="S131" s="13"/>
-      <c r="T131" s="10"/>
+      <c r="S131" s="11"/>
+      <c r="T131" s="11"/>
+      <c r="U131" s="10"/>
+      <c r="V131" s="10"/>
+      <c r="W131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="10"/>
@@ -3794,8 +4289,11 @@
       <c r="P132" s="10"/>
       <c r="Q132" s="10"/>
       <c r="R132" s="11"/>
-      <c r="S132" s="13"/>
-      <c r="T132" s="10"/>
+      <c r="S132" s="11"/>
+      <c r="T132" s="11"/>
+      <c r="U132" s="10"/>
+      <c r="V132" s="10"/>
+      <c r="W132" s="10"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="10"/>
@@ -3816,8 +4314,11 @@
       <c r="P133" s="10"/>
       <c r="Q133" s="10"/>
       <c r="R133" s="11"/>
-      <c r="S133" s="13"/>
-      <c r="T133" s="10"/>
+      <c r="S133" s="11"/>
+      <c r="T133" s="11"/>
+      <c r="U133" s="10"/>
+      <c r="V133" s="10"/>
+      <c r="W133" s="10"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="10"/>
@@ -3838,8 +4339,11 @@
       <c r="P134" s="10"/>
       <c r="Q134" s="10"/>
       <c r="R134" s="11"/>
-      <c r="S134" s="13"/>
-      <c r="T134" s="10"/>
+      <c r="S134" s="11"/>
+      <c r="T134" s="11"/>
+      <c r="U134" s="10"/>
+      <c r="V134" s="10"/>
+      <c r="W134" s="10"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="10"/>
@@ -3860,8 +4364,11 @@
       <c r="P135" s="10"/>
       <c r="Q135" s="10"/>
       <c r="R135" s="11"/>
-      <c r="S135" s="13"/>
-      <c r="T135" s="10"/>
+      <c r="S135" s="11"/>
+      <c r="T135" s="11"/>
+      <c r="U135" s="10"/>
+      <c r="V135" s="10"/>
+      <c r="W135" s="10"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="10"/>
@@ -3882,8 +4389,11 @@
       <c r="P136" s="10"/>
       <c r="Q136" s="10"/>
       <c r="R136" s="11"/>
-      <c r="S136" s="13"/>
-      <c r="T136" s="10"/>
+      <c r="S136" s="11"/>
+      <c r="T136" s="11"/>
+      <c r="U136" s="10"/>
+      <c r="V136" s="10"/>
+      <c r="W136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="10"/>
@@ -3904,8 +4414,11 @@
       <c r="P137" s="10"/>
       <c r="Q137" s="10"/>
       <c r="R137" s="11"/>
-      <c r="S137" s="13"/>
-      <c r="T137" s="10"/>
+      <c r="S137" s="11"/>
+      <c r="T137" s="11"/>
+      <c r="U137" s="10"/>
+      <c r="V137" s="10"/>
+      <c r="W137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="10"/>
@@ -3926,8 +4439,11 @@
       <c r="P138" s="10"/>
       <c r="Q138" s="10"/>
       <c r="R138" s="11"/>
-      <c r="S138" s="13"/>
-      <c r="T138" s="10"/>
+      <c r="S138" s="11"/>
+      <c r="T138" s="11"/>
+      <c r="U138" s="10"/>
+      <c r="V138" s="10"/>
+      <c r="W138" s="10"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="10"/>
@@ -3948,8 +4464,11 @@
       <c r="P139" s="10"/>
       <c r="Q139" s="10"/>
       <c r="R139" s="11"/>
-      <c r="S139" s="13"/>
-      <c r="T139" s="10"/>
+      <c r="S139" s="11"/>
+      <c r="T139" s="11"/>
+      <c r="U139" s="10"/>
+      <c r="V139" s="10"/>
+      <c r="W139" s="10"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="10"/>
@@ -3970,8 +4489,11 @@
       <c r="P140" s="10"/>
       <c r="Q140" s="10"/>
       <c r="R140" s="11"/>
-      <c r="S140" s="13"/>
-      <c r="T140" s="10"/>
+      <c r="S140" s="11"/>
+      <c r="T140" s="11"/>
+      <c r="U140" s="10"/>
+      <c r="V140" s="10"/>
+      <c r="W140" s="10"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="10"/>
@@ -3992,8 +4514,11 @@
       <c r="P141" s="10"/>
       <c r="Q141" s="10"/>
       <c r="R141" s="11"/>
-      <c r="S141" s="13"/>
-      <c r="T141" s="10"/>
+      <c r="S141" s="11"/>
+      <c r="T141" s="11"/>
+      <c r="U141" s="10"/>
+      <c r="V141" s="10"/>
+      <c r="W141" s="10"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="10"/>
@@ -4014,8 +4539,11 @@
       <c r="P142" s="10"/>
       <c r="Q142" s="10"/>
       <c r="R142" s="11"/>
-      <c r="S142" s="13"/>
-      <c r="T142" s="10"/>
+      <c r="S142" s="11"/>
+      <c r="T142" s="11"/>
+      <c r="U142" s="10"/>
+      <c r="V142" s="10"/>
+      <c r="W142" s="10"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="10"/>
@@ -4036,8 +4564,11 @@
       <c r="P143" s="10"/>
       <c r="Q143" s="10"/>
       <c r="R143" s="11"/>
-      <c r="S143" s="13"/>
-      <c r="T143" s="10"/>
+      <c r="S143" s="11"/>
+      <c r="T143" s="11"/>
+      <c r="U143" s="10"/>
+      <c r="V143" s="10"/>
+      <c r="W143" s="10"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="10"/>
@@ -4058,8 +4589,11 @@
       <c r="P144" s="10"/>
       <c r="Q144" s="10"/>
       <c r="R144" s="11"/>
-      <c r="S144" s="13"/>
-      <c r="T144" s="10"/>
+      <c r="S144" s="11"/>
+      <c r="T144" s="11"/>
+      <c r="U144" s="10"/>
+      <c r="V144" s="10"/>
+      <c r="W144" s="10"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="10"/>
@@ -4080,8 +4614,11 @@
       <c r="P145" s="10"/>
       <c r="Q145" s="10"/>
       <c r="R145" s="11"/>
-      <c r="S145" s="13"/>
-      <c r="T145" s="10"/>
+      <c r="S145" s="11"/>
+      <c r="T145" s="11"/>
+      <c r="U145" s="10"/>
+      <c r="V145" s="10"/>
+      <c r="W145" s="10"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="10"/>
@@ -4102,8 +4639,11 @@
       <c r="P146" s="10"/>
       <c r="Q146" s="10"/>
       <c r="R146" s="11"/>
-      <c r="S146" s="13"/>
-      <c r="T146" s="10"/>
+      <c r="S146" s="11"/>
+      <c r="T146" s="11"/>
+      <c r="U146" s="10"/>
+      <c r="V146" s="10"/>
+      <c r="W146" s="10"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="10"/>
@@ -4124,8 +4664,11 @@
       <c r="P147" s="10"/>
       <c r="Q147" s="10"/>
       <c r="R147" s="11"/>
-      <c r="S147" s="13"/>
-      <c r="T147" s="10"/>
+      <c r="S147" s="11"/>
+      <c r="T147" s="11"/>
+      <c r="U147" s="10"/>
+      <c r="V147" s="10"/>
+      <c r="W147" s="10"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="10"/>
@@ -4146,8 +4689,11 @@
       <c r="P148" s="10"/>
       <c r="Q148" s="10"/>
       <c r="R148" s="11"/>
-      <c r="S148" s="13"/>
-      <c r="T148" s="10"/>
+      <c r="S148" s="11"/>
+      <c r="T148" s="11"/>
+      <c r="U148" s="10"/>
+      <c r="V148" s="10"/>
+      <c r="W148" s="10"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="10"/>
@@ -4168,8 +4714,11 @@
       <c r="P149" s="10"/>
       <c r="Q149" s="10"/>
       <c r="R149" s="11"/>
-      <c r="S149" s="13"/>
-      <c r="T149" s="10"/>
+      <c r="S149" s="11"/>
+      <c r="T149" s="11"/>
+      <c r="U149" s="10"/>
+      <c r="V149" s="10"/>
+      <c r="W149" s="10"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="10"/>
@@ -4190,8 +4739,11 @@
       <c r="P150" s="10"/>
       <c r="Q150" s="10"/>
       <c r="R150" s="11"/>
-      <c r="S150" s="13"/>
-      <c r="T150" s="10"/>
+      <c r="S150" s="11"/>
+      <c r="T150" s="11"/>
+      <c r="U150" s="10"/>
+      <c r="V150" s="10"/>
+      <c r="W150" s="10"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="10"/>
@@ -4212,8 +4764,11 @@
       <c r="P151" s="10"/>
       <c r="Q151" s="10"/>
       <c r="R151" s="11"/>
-      <c r="S151" s="13"/>
-      <c r="T151" s="10"/>
+      <c r="S151" s="11"/>
+      <c r="T151" s="11"/>
+      <c r="U151" s="10"/>
+      <c r="V151" s="10"/>
+      <c r="W151" s="10"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="10"/>
@@ -4234,8 +4789,11 @@
       <c r="P152" s="10"/>
       <c r="Q152" s="10"/>
       <c r="R152" s="11"/>
-      <c r="S152" s="13"/>
-      <c r="T152" s="10"/>
+      <c r="S152" s="11"/>
+      <c r="T152" s="11"/>
+      <c r="U152" s="10"/>
+      <c r="V152" s="10"/>
+      <c r="W152" s="10"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="10"/>
@@ -4256,8 +4814,11 @@
       <c r="P153" s="10"/>
       <c r="Q153" s="10"/>
       <c r="R153" s="11"/>
-      <c r="S153" s="13"/>
-      <c r="T153" s="10"/>
+      <c r="S153" s="11"/>
+      <c r="T153" s="11"/>
+      <c r="U153" s="10"/>
+      <c r="V153" s="10"/>
+      <c r="W153" s="10"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="10"/>
@@ -4278,8 +4839,11 @@
       <c r="P154" s="10"/>
       <c r="Q154" s="10"/>
       <c r="R154" s="11"/>
-      <c r="S154" s="13"/>
-      <c r="T154" s="10"/>
+      <c r="S154" s="11"/>
+      <c r="T154" s="11"/>
+      <c r="U154" s="10"/>
+      <c r="V154" s="10"/>
+      <c r="W154" s="10"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="10"/>
@@ -4300,8 +4864,11 @@
       <c r="P155" s="10"/>
       <c r="Q155" s="10"/>
       <c r="R155" s="11"/>
-      <c r="S155" s="13"/>
-      <c r="T155" s="10"/>
+      <c r="S155" s="11"/>
+      <c r="T155" s="11"/>
+      <c r="U155" s="10"/>
+      <c r="V155" s="10"/>
+      <c r="W155" s="10"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="10"/>
@@ -4322,8 +4889,11 @@
       <c r="P156" s="10"/>
       <c r="Q156" s="10"/>
       <c r="R156" s="11"/>
-      <c r="S156" s="13"/>
-      <c r="T156" s="10"/>
+      <c r="S156" s="11"/>
+      <c r="T156" s="11"/>
+      <c r="U156" s="10"/>
+      <c r="V156" s="10"/>
+      <c r="W156" s="10"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="10"/>
@@ -4344,8 +4914,11 @@
       <c r="P157" s="10"/>
       <c r="Q157" s="10"/>
       <c r="R157" s="11"/>
-      <c r="S157" s="13"/>
-      <c r="T157" s="10"/>
+      <c r="S157" s="11"/>
+      <c r="T157" s="11"/>
+      <c r="U157" s="10"/>
+      <c r="V157" s="10"/>
+      <c r="W157" s="10"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="10"/>
@@ -4366,8 +4939,11 @@
       <c r="P158" s="10"/>
       <c r="Q158" s="10"/>
       <c r="R158" s="11"/>
-      <c r="S158" s="13"/>
-      <c r="T158" s="10"/>
+      <c r="S158" s="11"/>
+      <c r="T158" s="11"/>
+      <c r="U158" s="10"/>
+      <c r="V158" s="10"/>
+      <c r="W158" s="10"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="10"/>
@@ -4388,8 +4964,11 @@
       <c r="P159" s="10"/>
       <c r="Q159" s="10"/>
       <c r="R159" s="11"/>
-      <c r="S159" s="13"/>
-      <c r="T159" s="10"/>
+      <c r="S159" s="11"/>
+      <c r="T159" s="11"/>
+      <c r="U159" s="10"/>
+      <c r="V159" s="10"/>
+      <c r="W159" s="10"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="10"/>
@@ -4410,8 +4989,11 @@
       <c r="P160" s="10"/>
       <c r="Q160" s="10"/>
       <c r="R160" s="11"/>
-      <c r="S160" s="13"/>
-      <c r="T160" s="10"/>
+      <c r="S160" s="11"/>
+      <c r="T160" s="11"/>
+      <c r="U160" s="10"/>
+      <c r="V160" s="10"/>
+      <c r="W160" s="10"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="10"/>
@@ -4432,8 +5014,11 @@
       <c r="P161" s="10"/>
       <c r="Q161" s="10"/>
       <c r="R161" s="11"/>
-      <c r="S161" s="13"/>
-      <c r="T161" s="10"/>
+      <c r="S161" s="11"/>
+      <c r="T161" s="11"/>
+      <c r="U161" s="10"/>
+      <c r="V161" s="10"/>
+      <c r="W161" s="10"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="10"/>
@@ -4454,8 +5039,11 @@
       <c r="P162" s="10"/>
       <c r="Q162" s="10"/>
       <c r="R162" s="11"/>
-      <c r="S162" s="13"/>
-      <c r="T162" s="10"/>
+      <c r="S162" s="11"/>
+      <c r="T162" s="11"/>
+      <c r="U162" s="10"/>
+      <c r="V162" s="10"/>
+      <c r="W162" s="10"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="10"/>
@@ -4476,8 +5064,11 @@
       <c r="P163" s="10"/>
       <c r="Q163" s="10"/>
       <c r="R163" s="11"/>
-      <c r="S163" s="13"/>
-      <c r="T163" s="10"/>
+      <c r="S163" s="11"/>
+      <c r="T163" s="11"/>
+      <c r="U163" s="10"/>
+      <c r="V163" s="10"/>
+      <c r="W163" s="10"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="10"/>
@@ -4498,8 +5089,11 @@
       <c r="P164" s="10"/>
       <c r="Q164" s="10"/>
       <c r="R164" s="11"/>
-      <c r="S164" s="13"/>
-      <c r="T164" s="10"/>
+      <c r="S164" s="11"/>
+      <c r="T164" s="11"/>
+      <c r="U164" s="10"/>
+      <c r="V164" s="10"/>
+      <c r="W164" s="10"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="10"/>
@@ -4520,8 +5114,11 @@
       <c r="P165" s="10"/>
       <c r="Q165" s="10"/>
       <c r="R165" s="11"/>
-      <c r="S165" s="13"/>
-      <c r="T165" s="10"/>
+      <c r="S165" s="11"/>
+      <c r="T165" s="11"/>
+      <c r="U165" s="10"/>
+      <c r="V165" s="10"/>
+      <c r="W165" s="10"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="10"/>
@@ -4542,8 +5139,11 @@
       <c r="P166" s="10"/>
       <c r="Q166" s="10"/>
       <c r="R166" s="11"/>
-      <c r="S166" s="13"/>
-      <c r="T166" s="10"/>
+      <c r="S166" s="11"/>
+      <c r="T166" s="11"/>
+      <c r="U166" s="10"/>
+      <c r="V166" s="10"/>
+      <c r="W166" s="10"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="10"/>
@@ -4564,8 +5164,11 @@
       <c r="P167" s="10"/>
       <c r="Q167" s="10"/>
       <c r="R167" s="11"/>
-      <c r="S167" s="13"/>
-      <c r="T167" s="10"/>
+      <c r="S167" s="11"/>
+      <c r="T167" s="11"/>
+      <c r="U167" s="10"/>
+      <c r="V167" s="10"/>
+      <c r="W167" s="10"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="10"/>
@@ -4586,8 +5189,11 @@
       <c r="P168" s="10"/>
       <c r="Q168" s="10"/>
       <c r="R168" s="11"/>
-      <c r="S168" s="13"/>
-      <c r="T168" s="10"/>
+      <c r="S168" s="11"/>
+      <c r="T168" s="11"/>
+      <c r="U168" s="10"/>
+      <c r="V168" s="10"/>
+      <c r="W168" s="10"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="10"/>
@@ -4608,8 +5214,11 @@
       <c r="P169" s="10"/>
       <c r="Q169" s="10"/>
       <c r="R169" s="11"/>
-      <c r="S169" s="13"/>
-      <c r="T169" s="10"/>
+      <c r="S169" s="11"/>
+      <c r="T169" s="11"/>
+      <c r="U169" s="10"/>
+      <c r="V169" s="10"/>
+      <c r="W169" s="10"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="10"/>
@@ -4630,8 +5239,11 @@
       <c r="P170" s="10"/>
       <c r="Q170" s="10"/>
       <c r="R170" s="11"/>
-      <c r="S170" s="13"/>
-      <c r="T170" s="10"/>
+      <c r="S170" s="11"/>
+      <c r="T170" s="11"/>
+      <c r="U170" s="10"/>
+      <c r="V170" s="10"/>
+      <c r="W170" s="10"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="10"/>
@@ -4652,8 +5264,11 @@
       <c r="P171" s="10"/>
       <c r="Q171" s="10"/>
       <c r="R171" s="11"/>
-      <c r="S171" s="13"/>
-      <c r="T171" s="10"/>
+      <c r="S171" s="11"/>
+      <c r="T171" s="11"/>
+      <c r="U171" s="10"/>
+      <c r="V171" s="10"/>
+      <c r="W171" s="10"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="10"/>
@@ -4674,8 +5289,11 @@
       <c r="P172" s="10"/>
       <c r="Q172" s="10"/>
       <c r="R172" s="11"/>
-      <c r="S172" s="13"/>
-      <c r="T172" s="10"/>
+      <c r="S172" s="11"/>
+      <c r="T172" s="11"/>
+      <c r="U172" s="10"/>
+      <c r="V172" s="10"/>
+      <c r="W172" s="10"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="10"/>
@@ -4696,8 +5314,11 @@
       <c r="P173" s="10"/>
       <c r="Q173" s="10"/>
       <c r="R173" s="11"/>
-      <c r="S173" s="13"/>
-      <c r="T173" s="10"/>
+      <c r="S173" s="11"/>
+      <c r="T173" s="11"/>
+      <c r="U173" s="10"/>
+      <c r="V173" s="10"/>
+      <c r="W173" s="10"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="10"/>
@@ -4718,8 +5339,11 @@
       <c r="P174" s="10"/>
       <c r="Q174" s="10"/>
       <c r="R174" s="11"/>
-      <c r="S174" s="13"/>
-      <c r="T174" s="10"/>
+      <c r="S174" s="11"/>
+      <c r="T174" s="11"/>
+      <c r="U174" s="10"/>
+      <c r="V174" s="10"/>
+      <c r="W174" s="10"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="10"/>
@@ -4740,8 +5364,11 @@
       <c r="P175" s="10"/>
       <c r="Q175" s="10"/>
       <c r="R175" s="11"/>
-      <c r="S175" s="13"/>
-      <c r="T175" s="10"/>
+      <c r="S175" s="11"/>
+      <c r="T175" s="11"/>
+      <c r="U175" s="10"/>
+      <c r="V175" s="10"/>
+      <c r="W175" s="10"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="10"/>
@@ -4762,8 +5389,11 @@
       <c r="P176" s="10"/>
       <c r="Q176" s="10"/>
       <c r="R176" s="11"/>
-      <c r="S176" s="13"/>
-      <c r="T176" s="10"/>
+      <c r="S176" s="11"/>
+      <c r="T176" s="11"/>
+      <c r="U176" s="10"/>
+      <c r="V176" s="10"/>
+      <c r="W176" s="10"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="10"/>
@@ -4784,8 +5414,11 @@
       <c r="P177" s="10"/>
       <c r="Q177" s="10"/>
       <c r="R177" s="11"/>
-      <c r="S177" s="13"/>
-      <c r="T177" s="10"/>
+      <c r="S177" s="11"/>
+      <c r="T177" s="11"/>
+      <c r="U177" s="10"/>
+      <c r="V177" s="10"/>
+      <c r="W177" s="10"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="10"/>
@@ -4806,8 +5439,11 @@
       <c r="P178" s="10"/>
       <c r="Q178" s="10"/>
       <c r="R178" s="11"/>
-      <c r="S178" s="13"/>
-      <c r="T178" s="10"/>
+      <c r="S178" s="11"/>
+      <c r="T178" s="11"/>
+      <c r="U178" s="10"/>
+      <c r="V178" s="10"/>
+      <c r="W178" s="10"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="10"/>
@@ -4828,8 +5464,11 @@
       <c r="P179" s="10"/>
       <c r="Q179" s="10"/>
       <c r="R179" s="11"/>
-      <c r="S179" s="13"/>
-      <c r="T179" s="10"/>
+      <c r="S179" s="11"/>
+      <c r="T179" s="11"/>
+      <c r="U179" s="10"/>
+      <c r="V179" s="10"/>
+      <c r="W179" s="10"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="10"/>
@@ -4850,8 +5489,11 @@
       <c r="P180" s="10"/>
       <c r="Q180" s="10"/>
       <c r="R180" s="11"/>
-      <c r="S180" s="13"/>
-      <c r="T180" s="10"/>
+      <c r="S180" s="11"/>
+      <c r="T180" s="11"/>
+      <c r="U180" s="10"/>
+      <c r="V180" s="10"/>
+      <c r="W180" s="10"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="10"/>
@@ -4872,8 +5514,11 @@
       <c r="P181" s="10"/>
       <c r="Q181" s="10"/>
       <c r="R181" s="11"/>
-      <c r="S181" s="13"/>
-      <c r="T181" s="10"/>
+      <c r="S181" s="11"/>
+      <c r="T181" s="11"/>
+      <c r="U181" s="10"/>
+      <c r="V181" s="10"/>
+      <c r="W181" s="10"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="10"/>
@@ -4894,8 +5539,11 @@
       <c r="P182" s="10"/>
       <c r="Q182" s="10"/>
       <c r="R182" s="11"/>
-      <c r="S182" s="13"/>
-      <c r="T182" s="10"/>
+      <c r="S182" s="11"/>
+      <c r="T182" s="11"/>
+      <c r="U182" s="10"/>
+      <c r="V182" s="10"/>
+      <c r="W182" s="10"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="10"/>
@@ -4916,8 +5564,11 @@
       <c r="P183" s="10"/>
       <c r="Q183" s="10"/>
       <c r="R183" s="11"/>
-      <c r="S183" s="13"/>
-      <c r="T183" s="10"/>
+      <c r="S183" s="11"/>
+      <c r="T183" s="11"/>
+      <c r="U183" s="10"/>
+      <c r="V183" s="10"/>
+      <c r="W183" s="10"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="10"/>
@@ -4938,8 +5589,11 @@
       <c r="P184" s="10"/>
       <c r="Q184" s="10"/>
       <c r="R184" s="11"/>
-      <c r="S184" s="13"/>
-      <c r="T184" s="10"/>
+      <c r="S184" s="11"/>
+      <c r="T184" s="11"/>
+      <c r="U184" s="10"/>
+      <c r="V184" s="10"/>
+      <c r="W184" s="10"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="10"/>
@@ -4960,8 +5614,11 @@
       <c r="P185" s="10"/>
       <c r="Q185" s="10"/>
       <c r="R185" s="11"/>
-      <c r="S185" s="13"/>
-      <c r="T185" s="10"/>
+      <c r="S185" s="11"/>
+      <c r="T185" s="11"/>
+      <c r="U185" s="10"/>
+      <c r="V185" s="10"/>
+      <c r="W185" s="10"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="10"/>
@@ -4982,8 +5639,11 @@
       <c r="P186" s="10"/>
       <c r="Q186" s="10"/>
       <c r="R186" s="11"/>
-      <c r="S186" s="13"/>
-      <c r="T186" s="10"/>
+      <c r="S186" s="11"/>
+      <c r="T186" s="11"/>
+      <c r="U186" s="10"/>
+      <c r="V186" s="10"/>
+      <c r="W186" s="10"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="10"/>
@@ -5004,8 +5664,11 @@
       <c r="P187" s="10"/>
       <c r="Q187" s="10"/>
       <c r="R187" s="11"/>
-      <c r="S187" s="13"/>
-      <c r="T187" s="10"/>
+      <c r="S187" s="11"/>
+      <c r="T187" s="11"/>
+      <c r="U187" s="10"/>
+      <c r="V187" s="10"/>
+      <c r="W187" s="10"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="10"/>
@@ -5026,8 +5689,11 @@
       <c r="P188" s="10"/>
       <c r="Q188" s="10"/>
       <c r="R188" s="11"/>
-      <c r="S188" s="13"/>
-      <c r="T188" s="10"/>
+      <c r="S188" s="11"/>
+      <c r="T188" s="11"/>
+      <c r="U188" s="10"/>
+      <c r="V188" s="10"/>
+      <c r="W188" s="10"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="10"/>
@@ -5048,8 +5714,11 @@
       <c r="P189" s="10"/>
       <c r="Q189" s="10"/>
       <c r="R189" s="11"/>
-      <c r="S189" s="13"/>
-      <c r="T189" s="10"/>
+      <c r="S189" s="11"/>
+      <c r="T189" s="11"/>
+      <c r="U189" s="10"/>
+      <c r="V189" s="10"/>
+      <c r="W189" s="10"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="10"/>
@@ -5070,8 +5739,11 @@
       <c r="P190" s="10"/>
       <c r="Q190" s="10"/>
       <c r="R190" s="11"/>
-      <c r="S190" s="13"/>
-      <c r="T190" s="10"/>
+      <c r="S190" s="11"/>
+      <c r="T190" s="11"/>
+      <c r="U190" s="10"/>
+      <c r="V190" s="10"/>
+      <c r="W190" s="10"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="10"/>
@@ -5092,8 +5764,11 @@
       <c r="P191" s="10"/>
       <c r="Q191" s="10"/>
       <c r="R191" s="11"/>
-      <c r="S191" s="13"/>
-      <c r="T191" s="10"/>
+      <c r="S191" s="11"/>
+      <c r="T191" s="11"/>
+      <c r="U191" s="10"/>
+      <c r="V191" s="10"/>
+      <c r="W191" s="10"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="10"/>
@@ -5114,8 +5789,11 @@
       <c r="P192" s="10"/>
       <c r="Q192" s="10"/>
       <c r="R192" s="11"/>
-      <c r="S192" s="13"/>
-      <c r="T192" s="10"/>
+      <c r="S192" s="11"/>
+      <c r="T192" s="11"/>
+      <c r="U192" s="10"/>
+      <c r="V192" s="10"/>
+      <c r="W192" s="10"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="10"/>
@@ -5136,8 +5814,11 @@
       <c r="P193" s="10"/>
       <c r="Q193" s="10"/>
       <c r="R193" s="11"/>
-      <c r="S193" s="13"/>
-      <c r="T193" s="10"/>
+      <c r="S193" s="11"/>
+      <c r="T193" s="11"/>
+      <c r="U193" s="10"/>
+      <c r="V193" s="10"/>
+      <c r="W193" s="10"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="10"/>
@@ -5158,8 +5839,11 @@
       <c r="P194" s="10"/>
       <c r="Q194" s="10"/>
       <c r="R194" s="11"/>
-      <c r="S194" s="13"/>
-      <c r="T194" s="10"/>
+      <c r="S194" s="11"/>
+      <c r="T194" s="11"/>
+      <c r="U194" s="10"/>
+      <c r="V194" s="10"/>
+      <c r="W194" s="10"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="10"/>
@@ -5180,8 +5864,11 @@
       <c r="P195" s="10"/>
       <c r="Q195" s="10"/>
       <c r="R195" s="11"/>
-      <c r="S195" s="13"/>
-      <c r="T195" s="10"/>
+      <c r="S195" s="11"/>
+      <c r="T195" s="11"/>
+      <c r="U195" s="10"/>
+      <c r="V195" s="10"/>
+      <c r="W195" s="10"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="10"/>
@@ -5202,8 +5889,11 @@
       <c r="P196" s="10"/>
       <c r="Q196" s="10"/>
       <c r="R196" s="11"/>
-      <c r="S196" s="13"/>
-      <c r="T196" s="10"/>
+      <c r="S196" s="11"/>
+      <c r="T196" s="11"/>
+      <c r="U196" s="10"/>
+      <c r="V196" s="10"/>
+      <c r="W196" s="10"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="10"/>
@@ -5224,8 +5914,11 @@
       <c r="P197" s="10"/>
       <c r="Q197" s="10"/>
       <c r="R197" s="11"/>
-      <c r="S197" s="13"/>
-      <c r="T197" s="10"/>
+      <c r="S197" s="11"/>
+      <c r="T197" s="11"/>
+      <c r="U197" s="10"/>
+      <c r="V197" s="10"/>
+      <c r="W197" s="10"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="10"/>
@@ -5246,8 +5939,11 @@
       <c r="P198" s="10"/>
       <c r="Q198" s="10"/>
       <c r="R198" s="11"/>
-      <c r="S198" s="13"/>
-      <c r="T198" s="10"/>
+      <c r="S198" s="11"/>
+      <c r="T198" s="11"/>
+      <c r="U198" s="10"/>
+      <c r="V198" s="10"/>
+      <c r="W198" s="10"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="10"/>
@@ -5268,8 +5964,11 @@
       <c r="P199" s="10"/>
       <c r="Q199" s="10"/>
       <c r="R199" s="11"/>
-      <c r="S199" s="13"/>
-      <c r="T199" s="10"/>
+      <c r="S199" s="11"/>
+      <c r="T199" s="11"/>
+      <c r="U199" s="10"/>
+      <c r="V199" s="10"/>
+      <c r="W199" s="10"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="10"/>
@@ -5290,8 +5989,11 @@
       <c r="P200" s="10"/>
       <c r="Q200" s="10"/>
       <c r="R200" s="11"/>
-      <c r="S200" s="13"/>
-      <c r="T200" s="10"/>
+      <c r="S200" s="11"/>
+      <c r="T200" s="11"/>
+      <c r="U200" s="10"/>
+      <c r="V200" s="10"/>
+      <c r="W200" s="10"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="10"/>
@@ -5312,8 +6014,11 @@
       <c r="P201" s="10"/>
       <c r="Q201" s="10"/>
       <c r="R201" s="11"/>
-      <c r="S201" s="13"/>
-      <c r="T201" s="10"/>
+      <c r="S201" s="11"/>
+      <c r="T201" s="11"/>
+      <c r="U201" s="10"/>
+      <c r="V201" s="10"/>
+      <c r="W201" s="10"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="10"/>
@@ -5334,8 +6039,11 @@
       <c r="P202" s="10"/>
       <c r="Q202" s="10"/>
       <c r="R202" s="11"/>
-      <c r="S202" s="13"/>
-      <c r="T202" s="10"/>
+      <c r="S202" s="11"/>
+      <c r="T202" s="11"/>
+      <c r="U202" s="10"/>
+      <c r="V202" s="10"/>
+      <c r="W202" s="10"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="10"/>
@@ -5356,8 +6064,11 @@
       <c r="P203" s="10"/>
       <c r="Q203" s="10"/>
       <c r="R203" s="11"/>
-      <c r="S203" s="13"/>
-      <c r="T203" s="10"/>
+      <c r="S203" s="11"/>
+      <c r="T203" s="11"/>
+      <c r="U203" s="10"/>
+      <c r="V203" s="10"/>
+      <c r="W203" s="10"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="10"/>
@@ -5378,8 +6089,11 @@
       <c r="P204" s="10"/>
       <c r="Q204" s="10"/>
       <c r="R204" s="11"/>
-      <c r="S204" s="13"/>
-      <c r="T204" s="10"/>
+      <c r="S204" s="11"/>
+      <c r="T204" s="11"/>
+      <c r="U204" s="10"/>
+      <c r="V204" s="10"/>
+      <c r="W204" s="10"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="10"/>
@@ -5400,8 +6114,11 @@
       <c r="P205" s="10"/>
       <c r="Q205" s="10"/>
       <c r="R205" s="11"/>
-      <c r="S205" s="13"/>
-      <c r="T205" s="10"/>
+      <c r="S205" s="11"/>
+      <c r="T205" s="11"/>
+      <c r="U205" s="10"/>
+      <c r="V205" s="10"/>
+      <c r="W205" s="10"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="10"/>
@@ -5422,8 +6139,11 @@
       <c r="P206" s="10"/>
       <c r="Q206" s="10"/>
       <c r="R206" s="11"/>
-      <c r="S206" s="13"/>
-      <c r="T206" s="10"/>
+      <c r="S206" s="11"/>
+      <c r="T206" s="11"/>
+      <c r="U206" s="10"/>
+      <c r="V206" s="10"/>
+      <c r="W206" s="10"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="10"/>
@@ -5444,8 +6164,11 @@
       <c r="P207" s="10"/>
       <c r="Q207" s="10"/>
       <c r="R207" s="11"/>
-      <c r="S207" s="13"/>
-      <c r="T207" s="10"/>
+      <c r="S207" s="11"/>
+      <c r="T207" s="11"/>
+      <c r="U207" s="10"/>
+      <c r="V207" s="10"/>
+      <c r="W207" s="10"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="10"/>
@@ -5466,8 +6189,11 @@
       <c r="P208" s="10"/>
       <c r="Q208" s="10"/>
       <c r="R208" s="11"/>
-      <c r="S208" s="13"/>
-      <c r="T208" s="10"/>
+      <c r="S208" s="11"/>
+      <c r="T208" s="11"/>
+      <c r="U208" s="10"/>
+      <c r="V208" s="10"/>
+      <c r="W208" s="10"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="10"/>
@@ -5488,8 +6214,11 @@
       <c r="P209" s="10"/>
       <c r="Q209" s="10"/>
       <c r="R209" s="11"/>
-      <c r="S209" s="13"/>
-      <c r="T209" s="10"/>
+      <c r="S209" s="11"/>
+      <c r="T209" s="11"/>
+      <c r="U209" s="10"/>
+      <c r="V209" s="10"/>
+      <c r="W209" s="10"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="10"/>
@@ -5510,8 +6239,11 @@
       <c r="P210" s="10"/>
       <c r="Q210" s="10"/>
       <c r="R210" s="11"/>
-      <c r="S210" s="13"/>
-      <c r="T210" s="10"/>
+      <c r="S210" s="11"/>
+      <c r="T210" s="11"/>
+      <c r="U210" s="10"/>
+      <c r="V210" s="10"/>
+      <c r="W210" s="10"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="10"/>
@@ -5532,8 +6264,11 @@
       <c r="P211" s="10"/>
       <c r="Q211" s="10"/>
       <c r="R211" s="11"/>
-      <c r="S211" s="13"/>
-      <c r="T211" s="10"/>
+      <c r="S211" s="11"/>
+      <c r="T211" s="11"/>
+      <c r="U211" s="10"/>
+      <c r="V211" s="10"/>
+      <c r="W211" s="10"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="10"/>
@@ -5554,8 +6289,11 @@
       <c r="P212" s="10"/>
       <c r="Q212" s="10"/>
       <c r="R212" s="11"/>
-      <c r="S212" s="13"/>
-      <c r="T212" s="10"/>
+      <c r="S212" s="11"/>
+      <c r="T212" s="11"/>
+      <c r="U212" s="10"/>
+      <c r="V212" s="10"/>
+      <c r="W212" s="10"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="10"/>
@@ -5576,8 +6314,11 @@
       <c r="P213" s="10"/>
       <c r="Q213" s="10"/>
       <c r="R213" s="11"/>
-      <c r="S213" s="13"/>
-      <c r="T213" s="10"/>
+      <c r="S213" s="11"/>
+      <c r="T213" s="11"/>
+      <c r="U213" s="10"/>
+      <c r="V213" s="10"/>
+      <c r="W213" s="10"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="10"/>
@@ -5598,8 +6339,11 @@
       <c r="P214" s="10"/>
       <c r="Q214" s="10"/>
       <c r="R214" s="11"/>
-      <c r="S214" s="13"/>
-      <c r="T214" s="10"/>
+      <c r="S214" s="11"/>
+      <c r="T214" s="11"/>
+      <c r="U214" s="10"/>
+      <c r="V214" s="10"/>
+      <c r="W214" s="10"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="10"/>
@@ -5620,8 +6364,11 @@
       <c r="P215" s="10"/>
       <c r="Q215" s="10"/>
       <c r="R215" s="11"/>
-      <c r="S215" s="13"/>
-      <c r="T215" s="10"/>
+      <c r="S215" s="11"/>
+      <c r="T215" s="11"/>
+      <c r="U215" s="10"/>
+      <c r="V215" s="10"/>
+      <c r="W215" s="10"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="10"/>
@@ -5642,8 +6389,11 @@
       <c r="P216" s="10"/>
       <c r="Q216" s="10"/>
       <c r="R216" s="11"/>
-      <c r="S216" s="13"/>
-      <c r="T216" s="10"/>
+      <c r="S216" s="11"/>
+      <c r="T216" s="11"/>
+      <c r="U216" s="10"/>
+      <c r="V216" s="10"/>
+      <c r="W216" s="10"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="10"/>
@@ -5664,8 +6414,11 @@
       <c r="P217" s="10"/>
       <c r="Q217" s="10"/>
       <c r="R217" s="11"/>
-      <c r="S217" s="13"/>
-      <c r="T217" s="10"/>
+      <c r="S217" s="11"/>
+      <c r="T217" s="11"/>
+      <c r="U217" s="10"/>
+      <c r="V217" s="10"/>
+      <c r="W217" s="10"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="10"/>
@@ -5686,8 +6439,11 @@
       <c r="P218" s="10"/>
       <c r="Q218" s="10"/>
       <c r="R218" s="11"/>
-      <c r="S218" s="13"/>
-      <c r="T218" s="10"/>
+      <c r="S218" s="11"/>
+      <c r="T218" s="11"/>
+      <c r="U218" s="10"/>
+      <c r="V218" s="10"/>
+      <c r="W218" s="10"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="10"/>
@@ -5708,8 +6464,11 @@
       <c r="P219" s="10"/>
       <c r="Q219" s="10"/>
       <c r="R219" s="11"/>
-      <c r="S219" s="13"/>
-      <c r="T219" s="10"/>
+      <c r="S219" s="11"/>
+      <c r="T219" s="11"/>
+      <c r="U219" s="10"/>
+      <c r="V219" s="10"/>
+      <c r="W219" s="10"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="10"/>
@@ -5730,8 +6489,11 @@
       <c r="P220" s="10"/>
       <c r="Q220" s="10"/>
       <c r="R220" s="11"/>
-      <c r="S220" s="13"/>
-      <c r="T220" s="10"/>
+      <c r="S220" s="11"/>
+      <c r="T220" s="11"/>
+      <c r="U220" s="10"/>
+      <c r="V220" s="10"/>
+      <c r="W220" s="10"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="10"/>
@@ -5752,8 +6514,11 @@
       <c r="P221" s="10"/>
       <c r="Q221" s="10"/>
       <c r="R221" s="11"/>
-      <c r="S221" s="13"/>
-      <c r="T221" s="10"/>
+      <c r="S221" s="11"/>
+      <c r="T221" s="11"/>
+      <c r="U221" s="10"/>
+      <c r="V221" s="10"/>
+      <c r="W221" s="10"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="10"/>
@@ -5774,8 +6539,11 @@
       <c r="P222" s="10"/>
       <c r="Q222" s="10"/>
       <c r="R222" s="11"/>
-      <c r="S222" s="13"/>
-      <c r="T222" s="10"/>
+      <c r="S222" s="11"/>
+      <c r="T222" s="11"/>
+      <c r="U222" s="10"/>
+      <c r="V222" s="10"/>
+      <c r="W222" s="10"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="10"/>
@@ -5796,8 +6564,11 @@
       <c r="P223" s="10"/>
       <c r="Q223" s="10"/>
       <c r="R223" s="11"/>
-      <c r="S223" s="13"/>
-      <c r="T223" s="10"/>
+      <c r="S223" s="11"/>
+      <c r="T223" s="11"/>
+      <c r="U223" s="10"/>
+      <c r="V223" s="10"/>
+      <c r="W223" s="10"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="10"/>
@@ -5818,8 +6589,11 @@
       <c r="P224" s="10"/>
       <c r="Q224" s="10"/>
       <c r="R224" s="11"/>
-      <c r="S224" s="13"/>
-      <c r="T224" s="10"/>
+      <c r="S224" s="11"/>
+      <c r="T224" s="11"/>
+      <c r="U224" s="10"/>
+      <c r="V224" s="10"/>
+      <c r="W224" s="10"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="10"/>
@@ -5840,8 +6614,11 @@
       <c r="P225" s="10"/>
       <c r="Q225" s="10"/>
       <c r="R225" s="11"/>
-      <c r="S225" s="13"/>
-      <c r="T225" s="10"/>
+      <c r="S225" s="11"/>
+      <c r="T225" s="11"/>
+      <c r="U225" s="10"/>
+      <c r="V225" s="10"/>
+      <c r="W225" s="10"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="10"/>
@@ -5862,8 +6639,11 @@
       <c r="P226" s="10"/>
       <c r="Q226" s="10"/>
       <c r="R226" s="11"/>
-      <c r="S226" s="13"/>
-      <c r="T226" s="10"/>
+      <c r="S226" s="11"/>
+      <c r="T226" s="11"/>
+      <c r="U226" s="10"/>
+      <c r="V226" s="10"/>
+      <c r="W226" s="10"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="10"/>
@@ -5884,8 +6664,11 @@
       <c r="P227" s="10"/>
       <c r="Q227" s="10"/>
       <c r="R227" s="11"/>
-      <c r="S227" s="13"/>
-      <c r="T227" s="10"/>
+      <c r="S227" s="11"/>
+      <c r="T227" s="11"/>
+      <c r="U227" s="10"/>
+      <c r="V227" s="10"/>
+      <c r="W227" s="10"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="10"/>
@@ -5906,8 +6689,11 @@
       <c r="P228" s="10"/>
       <c r="Q228" s="10"/>
       <c r="R228" s="11"/>
-      <c r="S228" s="13"/>
-      <c r="T228" s="10"/>
+      <c r="S228" s="11"/>
+      <c r="T228" s="11"/>
+      <c r="U228" s="10"/>
+      <c r="V228" s="10"/>
+      <c r="W228" s="10"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="10"/>
@@ -5928,8 +6714,11 @@
       <c r="P229" s="10"/>
       <c r="Q229" s="10"/>
       <c r="R229" s="11"/>
-      <c r="S229" s="13"/>
-      <c r="T229" s="10"/>
+      <c r="S229" s="11"/>
+      <c r="T229" s="11"/>
+      <c r="U229" s="10"/>
+      <c r="V229" s="10"/>
+      <c r="W229" s="10"/>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="10"/>
@@ -5950,8 +6739,11 @@
       <c r="P230" s="10"/>
       <c r="Q230" s="10"/>
       <c r="R230" s="11"/>
-      <c r="S230" s="13"/>
-      <c r="T230" s="10"/>
+      <c r="S230" s="11"/>
+      <c r="T230" s="11"/>
+      <c r="U230" s="10"/>
+      <c r="V230" s="10"/>
+      <c r="W230" s="10"/>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="10"/>
@@ -5972,8 +6764,11 @@
       <c r="P231" s="10"/>
       <c r="Q231" s="10"/>
       <c r="R231" s="11"/>
-      <c r="S231" s="13"/>
-      <c r="T231" s="10"/>
+      <c r="S231" s="11"/>
+      <c r="T231" s="11"/>
+      <c r="U231" s="10"/>
+      <c r="V231" s="10"/>
+      <c r="W231" s="10"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="10"/>
@@ -5994,8 +6789,11 @@
       <c r="P232" s="10"/>
       <c r="Q232" s="10"/>
       <c r="R232" s="11"/>
-      <c r="S232" s="13"/>
-      <c r="T232" s="10"/>
+      <c r="S232" s="11"/>
+      <c r="T232" s="11"/>
+      <c r="U232" s="10"/>
+      <c r="V232" s="10"/>
+      <c r="W232" s="10"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="10"/>
@@ -6016,8 +6814,11 @@
       <c r="P233" s="10"/>
       <c r="Q233" s="10"/>
       <c r="R233" s="11"/>
-      <c r="S233" s="13"/>
-      <c r="T233" s="10"/>
+      <c r="S233" s="11"/>
+      <c r="T233" s="11"/>
+      <c r="U233" s="10"/>
+      <c r="V233" s="10"/>
+      <c r="W233" s="10"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="10"/>
@@ -6038,8 +6839,11 @@
       <c r="P234" s="10"/>
       <c r="Q234" s="10"/>
       <c r="R234" s="11"/>
-      <c r="S234" s="13"/>
-      <c r="T234" s="10"/>
+      <c r="S234" s="11"/>
+      <c r="T234" s="11"/>
+      <c r="U234" s="10"/>
+      <c r="V234" s="10"/>
+      <c r="W234" s="10"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="10"/>
@@ -6060,8 +6864,11 @@
       <c r="P235" s="10"/>
       <c r="Q235" s="10"/>
       <c r="R235" s="11"/>
-      <c r="S235" s="13"/>
-      <c r="T235" s="10"/>
+      <c r="S235" s="11"/>
+      <c r="T235" s="11"/>
+      <c r="U235" s="10"/>
+      <c r="V235" s="10"/>
+      <c r="W235" s="10"/>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="10"/>
@@ -6082,8 +6889,11 @@
       <c r="P236" s="10"/>
       <c r="Q236" s="10"/>
       <c r="R236" s="11"/>
-      <c r="S236" s="13"/>
-      <c r="T236" s="10"/>
+      <c r="S236" s="11"/>
+      <c r="T236" s="11"/>
+      <c r="U236" s="10"/>
+      <c r="V236" s="10"/>
+      <c r="W236" s="10"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="10"/>
@@ -6104,8 +6914,11 @@
       <c r="P237" s="10"/>
       <c r="Q237" s="10"/>
       <c r="R237" s="11"/>
-      <c r="S237" s="13"/>
-      <c r="T237" s="10"/>
+      <c r="S237" s="11"/>
+      <c r="T237" s="11"/>
+      <c r="U237" s="10"/>
+      <c r="V237" s="10"/>
+      <c r="W237" s="10"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="10"/>
@@ -6126,8 +6939,11 @@
       <c r="P238" s="10"/>
       <c r="Q238" s="10"/>
       <c r="R238" s="11"/>
-      <c r="S238" s="13"/>
-      <c r="T238" s="10"/>
+      <c r="S238" s="11"/>
+      <c r="T238" s="11"/>
+      <c r="U238" s="10"/>
+      <c r="V238" s="10"/>
+      <c r="W238" s="10"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="10"/>
@@ -6148,8 +6964,11 @@
       <c r="P239" s="10"/>
       <c r="Q239" s="10"/>
       <c r="R239" s="11"/>
-      <c r="S239" s="13"/>
-      <c r="T239" s="10"/>
+      <c r="S239" s="11"/>
+      <c r="T239" s="11"/>
+      <c r="U239" s="10"/>
+      <c r="V239" s="10"/>
+      <c r="W239" s="10"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="10"/>
@@ -6170,8 +6989,11 @@
       <c r="P240" s="10"/>
       <c r="Q240" s="10"/>
       <c r="R240" s="11"/>
-      <c r="S240" s="13"/>
-      <c r="T240" s="10"/>
+      <c r="S240" s="11"/>
+      <c r="T240" s="11"/>
+      <c r="U240" s="10"/>
+      <c r="V240" s="10"/>
+      <c r="W240" s="10"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="10"/>
@@ -6192,8 +7014,11 @@
       <c r="P241" s="10"/>
       <c r="Q241" s="10"/>
       <c r="R241" s="11"/>
-      <c r="S241" s="13"/>
-      <c r="T241" s="10"/>
+      <c r="S241" s="11"/>
+      <c r="T241" s="11"/>
+      <c r="U241" s="10"/>
+      <c r="V241" s="10"/>
+      <c r="W241" s="10"/>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="10"/>
@@ -6214,8 +7039,11 @@
       <c r="P242" s="10"/>
       <c r="Q242" s="10"/>
       <c r="R242" s="11"/>
-      <c r="S242" s="13"/>
-      <c r="T242" s="10"/>
+      <c r="S242" s="11"/>
+      <c r="T242" s="11"/>
+      <c r="U242" s="10"/>
+      <c r="V242" s="10"/>
+      <c r="W242" s="10"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="10"/>
@@ -6236,8 +7064,11 @@
       <c r="P243" s="10"/>
       <c r="Q243" s="10"/>
       <c r="R243" s="11"/>
-      <c r="S243" s="13"/>
-      <c r="T243" s="10"/>
+      <c r="S243" s="11"/>
+      <c r="T243" s="11"/>
+      <c r="U243" s="10"/>
+      <c r="V243" s="10"/>
+      <c r="W243" s="10"/>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="10"/>
@@ -6258,8 +7089,11 @@
       <c r="P244" s="10"/>
       <c r="Q244" s="10"/>
       <c r="R244" s="11"/>
-      <c r="S244" s="13"/>
-      <c r="T244" s="10"/>
+      <c r="S244" s="11"/>
+      <c r="T244" s="11"/>
+      <c r="U244" s="10"/>
+      <c r="V244" s="10"/>
+      <c r="W244" s="10"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="10"/>
@@ -6280,8 +7114,11 @@
       <c r="P245" s="10"/>
       <c r="Q245" s="10"/>
       <c r="R245" s="11"/>
-      <c r="S245" s="13"/>
-      <c r="T245" s="10"/>
+      <c r="S245" s="11"/>
+      <c r="T245" s="11"/>
+      <c r="U245" s="10"/>
+      <c r="V245" s="10"/>
+      <c r="W245" s="10"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="10"/>
@@ -6302,8 +7139,11 @@
       <c r="P246" s="10"/>
       <c r="Q246" s="10"/>
       <c r="R246" s="11"/>
-      <c r="S246" s="13"/>
-      <c r="T246" s="10"/>
+      <c r="S246" s="11"/>
+      <c r="T246" s="11"/>
+      <c r="U246" s="10"/>
+      <c r="V246" s="10"/>
+      <c r="W246" s="10"/>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="10"/>
@@ -6324,8 +7164,11 @@
       <c r="P247" s="10"/>
       <c r="Q247" s="10"/>
       <c r="R247" s="11"/>
-      <c r="S247" s="13"/>
-      <c r="T247" s="10"/>
+      <c r="S247" s="11"/>
+      <c r="T247" s="11"/>
+      <c r="U247" s="10"/>
+      <c r="V247" s="10"/>
+      <c r="W247" s="10"/>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="10"/>
@@ -6346,8 +7189,11 @@
       <c r="P248" s="10"/>
       <c r="Q248" s="10"/>
       <c r="R248" s="11"/>
-      <c r="S248" s="13"/>
-      <c r="T248" s="10"/>
+      <c r="S248" s="11"/>
+      <c r="T248" s="11"/>
+      <c r="U248" s="10"/>
+      <c r="V248" s="10"/>
+      <c r="W248" s="10"/>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="10"/>
@@ -6368,8 +7214,11 @@
       <c r="P249" s="10"/>
       <c r="Q249" s="10"/>
       <c r="R249" s="11"/>
-      <c r="S249" s="13"/>
-      <c r="T249" s="10"/>
+      <c r="S249" s="11"/>
+      <c r="T249" s="11"/>
+      <c r="U249" s="10"/>
+      <c r="V249" s="10"/>
+      <c r="W249" s="10"/>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="10"/>
@@ -6390,8 +7239,11 @@
       <c r="P250" s="10"/>
       <c r="Q250" s="10"/>
       <c r="R250" s="11"/>
-      <c r="S250" s="13"/>
-      <c r="T250" s="10"/>
+      <c r="S250" s="11"/>
+      <c r="T250" s="11"/>
+      <c r="U250" s="10"/>
+      <c r="V250" s="10"/>
+      <c r="W250" s="10"/>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="10"/>
@@ -6412,8 +7264,11 @@
       <c r="P251" s="10"/>
       <c r="Q251" s="10"/>
       <c r="R251" s="11"/>
-      <c r="S251" s="13"/>
-      <c r="T251" s="10"/>
+      <c r="S251" s="11"/>
+      <c r="T251" s="11"/>
+      <c r="U251" s="10"/>
+      <c r="V251" s="10"/>
+      <c r="W251" s="10"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="10"/>
@@ -6434,8 +7289,11 @@
       <c r="P252" s="10"/>
       <c r="Q252" s="10"/>
       <c r="R252" s="11"/>
-      <c r="S252" s="13"/>
-      <c r="T252" s="10"/>
+      <c r="S252" s="11"/>
+      <c r="T252" s="11"/>
+      <c r="U252" s="10"/>
+      <c r="V252" s="10"/>
+      <c r="W252" s="10"/>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="10"/>
@@ -6456,8 +7314,11 @@
       <c r="P253" s="10"/>
       <c r="Q253" s="10"/>
       <c r="R253" s="11"/>
-      <c r="S253" s="13"/>
-      <c r="T253" s="10"/>
+      <c r="S253" s="11"/>
+      <c r="T253" s="11"/>
+      <c r="U253" s="10"/>
+      <c r="V253" s="10"/>
+      <c r="W253" s="10"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="10"/>
@@ -6478,8 +7339,11 @@
       <c r="P254" s="10"/>
       <c r="Q254" s="10"/>
       <c r="R254" s="11"/>
-      <c r="S254" s="13"/>
-      <c r="T254" s="10"/>
+      <c r="S254" s="11"/>
+      <c r="T254" s="11"/>
+      <c r="U254" s="10"/>
+      <c r="V254" s="10"/>
+      <c r="W254" s="10"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="10"/>
@@ -6500,8 +7364,11 @@
       <c r="P255" s="10"/>
       <c r="Q255" s="10"/>
       <c r="R255" s="11"/>
-      <c r="S255" s="13"/>
-      <c r="T255" s="10"/>
+      <c r="S255" s="11"/>
+      <c r="T255" s="11"/>
+      <c r="U255" s="10"/>
+      <c r="V255" s="10"/>
+      <c r="W255" s="10"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="10"/>
@@ -6522,8 +7389,11 @@
       <c r="P256" s="10"/>
       <c r="Q256" s="10"/>
       <c r="R256" s="11"/>
-      <c r="S256" s="13"/>
-      <c r="T256" s="10"/>
+      <c r="S256" s="11"/>
+      <c r="T256" s="11"/>
+      <c r="U256" s="10"/>
+      <c r="V256" s="10"/>
+      <c r="W256" s="10"/>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="10"/>
@@ -6544,8 +7414,11 @@
       <c r="P257" s="10"/>
       <c r="Q257" s="10"/>
       <c r="R257" s="11"/>
-      <c r="S257" s="13"/>
-      <c r="T257" s="10"/>
+      <c r="S257" s="11"/>
+      <c r="T257" s="11"/>
+      <c r="U257" s="10"/>
+      <c r="V257" s="10"/>
+      <c r="W257" s="10"/>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="10"/>
@@ -6566,8 +7439,11 @@
       <c r="P258" s="10"/>
       <c r="Q258" s="10"/>
       <c r="R258" s="11"/>
-      <c r="S258" s="13"/>
-      <c r="T258" s="10"/>
+      <c r="S258" s="11"/>
+      <c r="T258" s="11"/>
+      <c r="U258" s="10"/>
+      <c r="V258" s="10"/>
+      <c r="W258" s="10"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="10"/>
@@ -6588,8 +7464,11 @@
       <c r="P259" s="10"/>
       <c r="Q259" s="10"/>
       <c r="R259" s="11"/>
-      <c r="S259" s="13"/>
-      <c r="T259" s="10"/>
+      <c r="S259" s="11"/>
+      <c r="T259" s="11"/>
+      <c r="U259" s="10"/>
+      <c r="V259" s="10"/>
+      <c r="W259" s="10"/>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="10"/>
@@ -6610,8 +7489,11 @@
       <c r="P260" s="10"/>
       <c r="Q260" s="10"/>
       <c r="R260" s="11"/>
-      <c r="S260" s="13"/>
-      <c r="T260" s="10"/>
+      <c r="S260" s="11"/>
+      <c r="T260" s="11"/>
+      <c r="U260" s="10"/>
+      <c r="V260" s="10"/>
+      <c r="W260" s="10"/>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="10"/>
@@ -6632,8 +7514,11 @@
       <c r="P261" s="10"/>
       <c r="Q261" s="10"/>
       <c r="R261" s="11"/>
-      <c r="S261" s="13"/>
-      <c r="T261" s="10"/>
+      <c r="S261" s="11"/>
+      <c r="T261" s="11"/>
+      <c r="U261" s="10"/>
+      <c r="V261" s="10"/>
+      <c r="W261" s="10"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="10"/>
@@ -6654,8 +7539,11 @@
       <c r="P262" s="10"/>
       <c r="Q262" s="10"/>
       <c r="R262" s="11"/>
-      <c r="S262" s="13"/>
-      <c r="T262" s="10"/>
+      <c r="S262" s="11"/>
+      <c r="T262" s="11"/>
+      <c r="U262" s="10"/>
+      <c r="V262" s="10"/>
+      <c r="W262" s="10"/>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="10"/>
@@ -6676,8 +7564,11 @@
       <c r="P263" s="10"/>
       <c r="Q263" s="10"/>
       <c r="R263" s="11"/>
-      <c r="S263" s="13"/>
-      <c r="T263" s="10"/>
+      <c r="S263" s="11"/>
+      <c r="T263" s="11"/>
+      <c r="U263" s="10"/>
+      <c r="V263" s="10"/>
+      <c r="W263" s="10"/>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="10"/>
@@ -6698,8 +7589,11 @@
       <c r="P264" s="10"/>
       <c r="Q264" s="10"/>
       <c r="R264" s="11"/>
-      <c r="S264" s="13"/>
-      <c r="T264" s="10"/>
+      <c r="S264" s="11"/>
+      <c r="T264" s="11"/>
+      <c r="U264" s="10"/>
+      <c r="V264" s="10"/>
+      <c r="W264" s="10"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="10"/>
@@ -6720,8 +7614,11 @@
       <c r="P265" s="10"/>
       <c r="Q265" s="10"/>
       <c r="R265" s="11"/>
-      <c r="S265" s="13"/>
-      <c r="T265" s="10"/>
+      <c r="S265" s="11"/>
+      <c r="T265" s="11"/>
+      <c r="U265" s="10"/>
+      <c r="V265" s="10"/>
+      <c r="W265" s="10"/>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="10"/>
@@ -6742,8 +7639,11 @@
       <c r="P266" s="10"/>
       <c r="Q266" s="10"/>
       <c r="R266" s="11"/>
-      <c r="S266" s="13"/>
-      <c r="T266" s="10"/>
+      <c r="S266" s="11"/>
+      <c r="T266" s="11"/>
+      <c r="U266" s="10"/>
+      <c r="V266" s="10"/>
+      <c r="W266" s="10"/>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="10"/>
@@ -6764,8 +7664,11 @@
       <c r="P267" s="10"/>
       <c r="Q267" s="10"/>
       <c r="R267" s="11"/>
-      <c r="S267" s="13"/>
-      <c r="T267" s="10"/>
+      <c r="S267" s="11"/>
+      <c r="T267" s="11"/>
+      <c r="U267" s="10"/>
+      <c r="V267" s="10"/>
+      <c r="W267" s="10"/>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="10"/>
@@ -6786,8 +7689,11 @@
       <c r="P268" s="10"/>
       <c r="Q268" s="10"/>
       <c r="R268" s="11"/>
-      <c r="S268" s="13"/>
-      <c r="T268" s="10"/>
+      <c r="S268" s="11"/>
+      <c r="T268" s="11"/>
+      <c r="U268" s="10"/>
+      <c r="V268" s="10"/>
+      <c r="W268" s="10"/>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="10"/>
@@ -6808,8 +7714,11 @@
       <c r="P269" s="10"/>
       <c r="Q269" s="10"/>
       <c r="R269" s="11"/>
-      <c r="S269" s="13"/>
-      <c r="T269" s="10"/>
+      <c r="S269" s="11"/>
+      <c r="T269" s="11"/>
+      <c r="U269" s="10"/>
+      <c r="V269" s="10"/>
+      <c r="W269" s="10"/>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="10"/>
@@ -6830,8 +7739,11 @@
       <c r="P270" s="10"/>
       <c r="Q270" s="10"/>
       <c r="R270" s="11"/>
-      <c r="S270" s="13"/>
-      <c r="T270" s="10"/>
+      <c r="S270" s="11"/>
+      <c r="T270" s="11"/>
+      <c r="U270" s="10"/>
+      <c r="V270" s="10"/>
+      <c r="W270" s="10"/>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="10"/>
@@ -6852,8 +7764,11 @@
       <c r="P271" s="10"/>
       <c r="Q271" s="10"/>
       <c r="R271" s="11"/>
-      <c r="S271" s="13"/>
-      <c r="T271" s="10"/>
+      <c r="S271" s="11"/>
+      <c r="T271" s="11"/>
+      <c r="U271" s="10"/>
+      <c r="V271" s="10"/>
+      <c r="W271" s="10"/>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="10"/>
@@ -6874,8 +7789,11 @@
       <c r="P272" s="10"/>
       <c r="Q272" s="10"/>
       <c r="R272" s="11"/>
-      <c r="S272" s="13"/>
-      <c r="T272" s="10"/>
+      <c r="S272" s="11"/>
+      <c r="T272" s="11"/>
+      <c r="U272" s="10"/>
+      <c r="V272" s="10"/>
+      <c r="W272" s="10"/>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="10"/>
@@ -6896,8 +7814,11 @@
       <c r="P273" s="10"/>
       <c r="Q273" s="10"/>
       <c r="R273" s="11"/>
-      <c r="S273" s="13"/>
-      <c r="T273" s="10"/>
+      <c r="S273" s="11"/>
+      <c r="T273" s="11"/>
+      <c r="U273" s="10"/>
+      <c r="V273" s="10"/>
+      <c r="W273" s="10"/>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="10"/>
@@ -6918,8 +7839,11 @@
       <c r="P274" s="10"/>
       <c r="Q274" s="10"/>
       <c r="R274" s="11"/>
-      <c r="S274" s="13"/>
-      <c r="T274" s="10"/>
+      <c r="S274" s="11"/>
+      <c r="T274" s="11"/>
+      <c r="U274" s="10"/>
+      <c r="V274" s="10"/>
+      <c r="W274" s="10"/>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="10"/>
@@ -6940,8 +7864,11 @@
       <c r="P275" s="10"/>
       <c r="Q275" s="10"/>
       <c r="R275" s="11"/>
-      <c r="S275" s="13"/>
-      <c r="T275" s="10"/>
+      <c r="S275" s="11"/>
+      <c r="T275" s="11"/>
+      <c r="U275" s="10"/>
+      <c r="V275" s="10"/>
+      <c r="W275" s="10"/>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="10"/>
@@ -6962,8 +7889,11 @@
       <c r="P276" s="10"/>
       <c r="Q276" s="10"/>
       <c r="R276" s="11"/>
-      <c r="S276" s="13"/>
-      <c r="T276" s="10"/>
+      <c r="S276" s="11"/>
+      <c r="T276" s="11"/>
+      <c r="U276" s="10"/>
+      <c r="V276" s="10"/>
+      <c r="W276" s="10"/>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="10"/>
@@ -6984,8 +7914,11 @@
       <c r="P277" s="10"/>
       <c r="Q277" s="10"/>
       <c r="R277" s="11"/>
-      <c r="S277" s="13"/>
-      <c r="T277" s="10"/>
+      <c r="S277" s="11"/>
+      <c r="T277" s="11"/>
+      <c r="U277" s="10"/>
+      <c r="V277" s="10"/>
+      <c r="W277" s="10"/>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="10"/>
@@ -7006,8 +7939,11 @@
       <c r="P278" s="10"/>
       <c r="Q278" s="10"/>
       <c r="R278" s="11"/>
-      <c r="S278" s="13"/>
-      <c r="T278" s="10"/>
+      <c r="S278" s="11"/>
+      <c r="T278" s="11"/>
+      <c r="U278" s="10"/>
+      <c r="V278" s="10"/>
+      <c r="W278" s="10"/>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="10"/>
@@ -7028,8 +7964,11 @@
       <c r="P279" s="10"/>
       <c r="Q279" s="10"/>
       <c r="R279" s="11"/>
-      <c r="S279" s="13"/>
-      <c r="T279" s="10"/>
+      <c r="S279" s="11"/>
+      <c r="T279" s="11"/>
+      <c r="U279" s="10"/>
+      <c r="V279" s="10"/>
+      <c r="W279" s="10"/>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="10"/>
@@ -7050,8 +7989,11 @@
       <c r="P280" s="10"/>
       <c r="Q280" s="10"/>
       <c r="R280" s="11"/>
-      <c r="S280" s="13"/>
-      <c r="T280" s="10"/>
+      <c r="S280" s="11"/>
+      <c r="T280" s="11"/>
+      <c r="U280" s="10"/>
+      <c r="V280" s="10"/>
+      <c r="W280" s="10"/>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="10"/>
@@ -7072,8 +8014,11 @@
       <c r="P281" s="10"/>
       <c r="Q281" s="10"/>
       <c r="R281" s="11"/>
-      <c r="S281" s="13"/>
-      <c r="T281" s="10"/>
+      <c r="S281" s="11"/>
+      <c r="T281" s="11"/>
+      <c r="U281" s="10"/>
+      <c r="V281" s="10"/>
+      <c r="W281" s="10"/>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="10"/>
@@ -7094,8 +8039,11 @@
       <c r="P282" s="10"/>
       <c r="Q282" s="10"/>
       <c r="R282" s="11"/>
-      <c r="S282" s="13"/>
-      <c r="T282" s="10"/>
+      <c r="S282" s="11"/>
+      <c r="T282" s="11"/>
+      <c r="U282" s="10"/>
+      <c r="V282" s="10"/>
+      <c r="W282" s="10"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="10"/>
@@ -7116,8 +8064,11 @@
       <c r="P283" s="10"/>
       <c r="Q283" s="10"/>
       <c r="R283" s="11"/>
-      <c r="S283" s="13"/>
-      <c r="T283" s="10"/>
+      <c r="S283" s="11"/>
+      <c r="T283" s="11"/>
+      <c r="U283" s="10"/>
+      <c r="V283" s="10"/>
+      <c r="W283" s="10"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="10"/>
@@ -7138,8 +8089,11 @@
       <c r="P284" s="10"/>
       <c r="Q284" s="10"/>
       <c r="R284" s="11"/>
-      <c r="S284" s="13"/>
-      <c r="T284" s="10"/>
+      <c r="S284" s="11"/>
+      <c r="T284" s="11"/>
+      <c r="U284" s="10"/>
+      <c r="V284" s="10"/>
+      <c r="W284" s="10"/>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="10"/>
@@ -7160,8 +8114,11 @@
       <c r="P285" s="10"/>
       <c r="Q285" s="10"/>
       <c r="R285" s="11"/>
-      <c r="S285" s="13"/>
-      <c r="T285" s="10"/>
+      <c r="S285" s="11"/>
+      <c r="T285" s="11"/>
+      <c r="U285" s="10"/>
+      <c r="V285" s="10"/>
+      <c r="W285" s="10"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="10"/>
@@ -7182,8 +8139,11 @@
       <c r="P286" s="10"/>
       <c r="Q286" s="10"/>
       <c r="R286" s="11"/>
-      <c r="S286" s="13"/>
-      <c r="T286" s="10"/>
+      <c r="S286" s="11"/>
+      <c r="T286" s="11"/>
+      <c r="U286" s="10"/>
+      <c r="V286" s="10"/>
+      <c r="W286" s="10"/>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="10"/>
@@ -7204,8 +8164,11 @@
       <c r="P287" s="10"/>
       <c r="Q287" s="10"/>
       <c r="R287" s="11"/>
-      <c r="S287" s="13"/>
-      <c r="T287" s="10"/>
+      <c r="S287" s="11"/>
+      <c r="T287" s="11"/>
+      <c r="U287" s="10"/>
+      <c r="V287" s="10"/>
+      <c r="W287" s="10"/>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="10"/>
@@ -7226,8 +8189,11 @@
       <c r="P288" s="10"/>
       <c r="Q288" s="10"/>
       <c r="R288" s="11"/>
-      <c r="S288" s="13"/>
-      <c r="T288" s="10"/>
+      <c r="S288" s="11"/>
+      <c r="T288" s="11"/>
+      <c r="U288" s="10"/>
+      <c r="V288" s="10"/>
+      <c r="W288" s="10"/>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="10"/>
@@ -7248,8 +8214,11 @@
       <c r="P289" s="10"/>
       <c r="Q289" s="10"/>
       <c r="R289" s="11"/>
-      <c r="S289" s="13"/>
-      <c r="T289" s="10"/>
+      <c r="S289" s="11"/>
+      <c r="T289" s="11"/>
+      <c r="U289" s="10"/>
+      <c r="V289" s="10"/>
+      <c r="W289" s="10"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="10"/>
@@ -7270,8 +8239,11 @@
       <c r="P290" s="10"/>
       <c r="Q290" s="10"/>
       <c r="R290" s="11"/>
-      <c r="S290" s="13"/>
-      <c r="T290" s="10"/>
+      <c r="S290" s="11"/>
+      <c r="T290" s="11"/>
+      <c r="U290" s="10"/>
+      <c r="V290" s="10"/>
+      <c r="W290" s="10"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="10"/>
@@ -7292,8 +8264,11 @@
       <c r="P291" s="10"/>
       <c r="Q291" s="10"/>
       <c r="R291" s="11"/>
-      <c r="S291" s="13"/>
-      <c r="T291" s="10"/>
+      <c r="S291" s="11"/>
+      <c r="T291" s="11"/>
+      <c r="U291" s="10"/>
+      <c r="V291" s="10"/>
+      <c r="W291" s="10"/>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="10"/>
@@ -7314,8 +8289,11 @@
       <c r="P292" s="10"/>
       <c r="Q292" s="10"/>
       <c r="R292" s="11"/>
-      <c r="S292" s="13"/>
-      <c r="T292" s="10"/>
+      <c r="S292" s="11"/>
+      <c r="T292" s="11"/>
+      <c r="U292" s="10"/>
+      <c r="V292" s="10"/>
+      <c r="W292" s="10"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="10"/>
@@ -7336,8 +8314,11 @@
       <c r="P293" s="10"/>
       <c r="Q293" s="10"/>
       <c r="R293" s="11"/>
-      <c r="S293" s="13"/>
-      <c r="T293" s="10"/>
+      <c r="S293" s="11"/>
+      <c r="T293" s="11"/>
+      <c r="U293" s="10"/>
+      <c r="V293" s="10"/>
+      <c r="W293" s="10"/>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="10"/>
@@ -7358,8 +8339,11 @@
       <c r="P294" s="10"/>
       <c r="Q294" s="10"/>
       <c r="R294" s="11"/>
-      <c r="S294" s="13"/>
-      <c r="T294" s="10"/>
+      <c r="S294" s="11"/>
+      <c r="T294" s="11"/>
+      <c r="U294" s="10"/>
+      <c r="V294" s="10"/>
+      <c r="W294" s="10"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="10"/>
@@ -7380,8 +8364,11 @@
       <c r="P295" s="10"/>
       <c r="Q295" s="10"/>
       <c r="R295" s="11"/>
-      <c r="S295" s="13"/>
-      <c r="T295" s="10"/>
+      <c r="S295" s="11"/>
+      <c r="T295" s="11"/>
+      <c r="U295" s="10"/>
+      <c r="V295" s="10"/>
+      <c r="W295" s="10"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="10"/>
@@ -7402,8 +8389,11 @@
       <c r="P296" s="10"/>
       <c r="Q296" s="10"/>
       <c r="R296" s="11"/>
-      <c r="S296" s="13"/>
-      <c r="T296" s="10"/>
+      <c r="S296" s="11"/>
+      <c r="T296" s="11"/>
+      <c r="U296" s="10"/>
+      <c r="V296" s="10"/>
+      <c r="W296" s="10"/>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="10"/>
@@ -7424,8 +8414,11 @@
       <c r="P297" s="10"/>
       <c r="Q297" s="10"/>
       <c r="R297" s="11"/>
-      <c r="S297" s="13"/>
-      <c r="T297" s="10"/>
+      <c r="S297" s="11"/>
+      <c r="T297" s="11"/>
+      <c r="U297" s="10"/>
+      <c r="V297" s="10"/>
+      <c r="W297" s="10"/>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="10"/>
@@ -7446,8 +8439,11 @@
       <c r="P298" s="10"/>
       <c r="Q298" s="10"/>
       <c r="R298" s="11"/>
-      <c r="S298" s="13"/>
-      <c r="T298" s="10"/>
+      <c r="S298" s="11"/>
+      <c r="T298" s="11"/>
+      <c r="U298" s="10"/>
+      <c r="V298" s="10"/>
+      <c r="W298" s="10"/>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="10"/>
@@ -7468,8 +8464,11 @@
       <c r="P299" s="10"/>
       <c r="Q299" s="10"/>
       <c r="R299" s="11"/>
-      <c r="S299" s="13"/>
-      <c r="T299" s="10"/>
+      <c r="S299" s="11"/>
+      <c r="T299" s="11"/>
+      <c r="U299" s="10"/>
+      <c r="V299" s="10"/>
+      <c r="W299" s="10"/>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="10"/>
@@ -7490,11 +8489,14 @@
       <c r="P300" s="10"/>
       <c r="Q300" s="10"/>
       <c r="R300" s="11"/>
-      <c r="S300" s="13"/>
-      <c r="T300" s="10"/>
+      <c r="S300" s="11"/>
+      <c r="T300" s="11"/>
+      <c r="U300" s="10"/>
+      <c r="V300" s="10"/>
+      <c r="W300" s="10"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="اختر قيمة من القائمة المنسدلة" errorStyle="stop" errorTitle="دورة سداد غير معروفة" operator="between" prompt="اختر من القائمة — لا تكتب يدويًا" promptTitle="دورة السداد" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D300" type="list">
       <formula1>"شهري,سنوي,نصف سنوي,كل 3 اشهر,اسبوعي,يومي"</formula1>
       <formula2>0</formula2>
@@ -7535,6 +8537,14 @@
       <formula1>"تلقائي,تُطبَّق,معفاة"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="T2:T300" type="list">
+      <formula1>"هجري,ميلادي"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="U2:U300" type="whole">
+      <formula1>1</formula1>
+      <formula2>120</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7552,94 +8562,128 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B17"/>
+  <dimension ref="B1:B23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="15" t="s">
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16" t="s">
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17" t="s">
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
